--- a/gemini8048/bin/87KLR951.xlsx
+++ b/gemini8048/bin/87KLR951.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mike/coding_projects/944/DME_sim/gemini8048/bin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6097D6-962B-2940-8DD9-568913FB064C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFA0F05-AC71-694D-9A54-DEA9E9F0CFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12960" yWindow="16720" windowWidth="47100" windowHeight="24480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37360" yWindow="8740" windowWidth="47100" windowHeight="24480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASM" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8127" uniqueCount="4400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8162" uniqueCount="4429">
   <si>
     <t>https://junctionbyte.com/8051-microcontroller-special-function-registers/</t>
   </si>
@@ -13247,6 +13247,93 @@
   </si>
   <si>
     <t>// END function table adc_map_sensor_read:</t>
+  </si>
+  <si>
+    <t>Long</t>
+  </si>
+  <si>
+    <t>interrupt_info</t>
+  </si>
+  <si>
+    <t>num_timer_ints</t>
+  </si>
+  <si>
+    <t>dec_interrupts</t>
+  </si>
+  <si>
+    <t>timer_period</t>
+  </si>
+  <si>
+    <t>battery_volts</t>
+  </si>
+  <si>
+    <t>knock_raw</t>
+  </si>
+  <si>
+    <t>knock_test_out</t>
+  </si>
+  <si>
+    <t>throttle_degrees</t>
+  </si>
+  <si>
+    <t>throttle_raw_sensor</t>
+  </si>
+  <si>
+    <t>WOT_angle</t>
+  </si>
+  <si>
+    <t>mac_knock_thresh</t>
+  </si>
+  <si>
+    <t>integrated_knock_val</t>
+  </si>
+  <si>
+    <t>knock_det_threshold</t>
+  </si>
+  <si>
+    <t>throttle_position_threshold</t>
+  </si>
+  <si>
+    <t>cycle_count_before_restore</t>
+  </si>
+  <si>
+    <t>max_timing_retart</t>
+  </si>
+  <si>
+    <t>boost_threshold</t>
+  </si>
+  <si>
+    <t>cycle_count_before_pulling_boost</t>
+  </si>
+  <si>
+    <t>cycle_count_before_restore_boost</t>
+  </si>
+  <si>
+    <t>TPS Voltage</t>
+  </si>
+  <si>
+    <t>TPS_Cycling</t>
+  </si>
+  <si>
+    <t>TPS_Scaling</t>
+  </si>
+  <si>
+    <t>//3bh - The scaling numerator 3B is initialized to 119 in the trigger/reset routine. So the nominal scaling factor is 119/256, or about 0.46</t>
+  </si>
+  <si>
+    <t>//value ranging from 0-27, used for cycling value control map lookups</t>
+  </si>
+  <si>
+    <t>throt_pos_thresh</t>
+  </si>
+  <si>
+    <t>boost_thresh</t>
+  </si>
+  <si>
+    <t>knk_thres_cyl</t>
+  </si>
+  <si>
+    <t>knock_thresh_coeef</t>
   </si>
 </sst>
 </file>
@@ -13350,7 +13437,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -13409,6 +13496,7 @@
     <xf numFmtId="6" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -40158,1267 +40246,1470 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="22"/>
   <cols>
     <col min="1" max="1" width="35.6640625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="37.83203125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="98.6640625" style="15" customWidth="1"/>
-    <col min="4" max="4" width="39.33203125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="9"/>
+    <col min="2" max="3" width="37.83203125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="98.6640625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="39.33203125" style="17" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="23" customHeight="1">
+    <row r="1" spans="1:11" ht="23" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>3787</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>3788</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="11" t="s">
         <v>3789</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
+        <v>4400</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>3790</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="46" customHeight="1">
+    <row r="2" spans="1:11" ht="46" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>3791</v>
       </c>
       <c r="B2" s="12">
         <v>0</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="9" t="s">
+        <v>4401</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>3792</v>
       </c>
-      <c r="D2" s="18">
+      <c r="E2" s="18">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="B3" s="12">
         <v>1</v>
       </c>
-      <c r="D3" s="18">
+      <c r="C3" s="9"/>
+      <c r="E3" s="18">
         <v>23</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>3793</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="23" customHeight="1">
+    <row r="4" spans="1:11" ht="23" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>3794</v>
       </c>
       <c r="B4" s="12">
         <v>2</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="9" t="s">
+        <v>4402</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>3795</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="E4" s="18" t="s">
         <v>3796</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="23" customHeight="1">
+    <row r="5" spans="1:11" ht="23" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>3797</v>
       </c>
       <c r="B5" s="12">
         <v>3</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="9" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>3798</v>
       </c>
-      <c r="D5" s="18">
+      <c r="E5" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="B6" s="12">
         <v>4</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="C6" s="9"/>
+      <c r="E6" s="18" t="s">
         <v>3799</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="23" customHeight="1">
+    <row r="7" spans="1:11" ht="23" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>3800</v>
       </c>
       <c r="B7" s="12">
         <v>5</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="9" t="s">
+        <v>4403</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>3801</v>
       </c>
-      <c r="D7" s="18">
+      <c r="E7" s="18">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="46" customHeight="1">
+    <row r="8" spans="1:11" ht="46" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>3802</v>
       </c>
       <c r="B8" s="12">
         <v>6</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="9" t="s">
+        <v>3802</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>3803</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="E8" s="18" t="s">
         <v>3804</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="92" customHeight="1">
+    <row r="9" spans="1:11" ht="92" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>3805</v>
       </c>
       <c r="B9" s="12">
         <v>7</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="9" t="s">
+        <v>4404</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>3806</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="E9" s="18" t="s">
         <v>1586</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="B10" s="12">
         <v>8</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="C10" s="9"/>
+      <c r="E10" s="18" t="s">
         <v>3807</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="B11" s="12">
         <v>9</v>
       </c>
-      <c r="D11" s="18">
+      <c r="C11" s="9"/>
+      <c r="E11" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="B12" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="C12" s="9"/>
+      <c r="E12" s="18" t="s">
         <v>3808</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="B13" s="12" t="s">
         <v>3809</v>
       </c>
-      <c r="D13" s="18">
+      <c r="C13" s="9"/>
+      <c r="E13" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:11">
       <c r="B14" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="C14" s="9"/>
+      <c r="E14" s="18" t="s">
         <v>3810</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:11">
       <c r="B15" s="12" t="s">
         <v>3811</v>
       </c>
-      <c r="D15" s="18">
+      <c r="C15" s="9"/>
+      <c r="E15" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="B16" s="12" t="s">
         <v>3812</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="C16" s="9"/>
+      <c r="E16" s="18" t="s">
         <v>3807</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:5">
       <c r="B17" s="12" t="s">
         <v>3813</v>
       </c>
-      <c r="D17" s="18">
+      <c r="C17" s="9"/>
+      <c r="E17" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="23" customHeight="1">
+    <row r="18" spans="2:5" ht="23" customHeight="1">
       <c r="B18" s="12">
         <v>10</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="9"/>
+      <c r="D18" s="15" t="s">
         <v>3814</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="E18" s="18" t="s">
         <v>3808</v>
       </c>
     </row>
-    <row r="19" spans="2:4">
+    <row r="19" spans="2:5">
       <c r="B19" s="12">
         <v>11</v>
       </c>
-      <c r="D19" s="18">
+      <c r="C19" s="9"/>
+      <c r="E19" s="18">
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:5">
       <c r="B20" s="12">
         <v>12</v>
       </c>
-      <c r="D20" s="18">
+      <c r="C20" s="9"/>
+      <c r="E20" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:5">
       <c r="B21" s="12">
         <v>13</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="C21" s="9"/>
+      <c r="E21" s="18" t="s">
         <v>3815</v>
       </c>
     </row>
-    <row r="22" spans="2:4">
+    <row r="22" spans="2:5">
       <c r="B22" s="12">
         <v>14</v>
       </c>
-      <c r="D22" s="18">
+      <c r="C22" s="9"/>
+      <c r="E22" s="18">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:5">
       <c r="B23" s="12">
         <v>15</v>
       </c>
-      <c r="D23" s="18">
+      <c r="C23" s="9"/>
+      <c r="E23" s="18">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
+    <row r="24" spans="2:5">
       <c r="B24" s="12">
         <v>16</v>
       </c>
-      <c r="D24" s="18">
+      <c r="C24" s="9"/>
+      <c r="E24" s="18">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="2:4">
+    <row r="25" spans="2:5">
       <c r="B25" s="12">
         <v>17</v>
       </c>
-      <c r="D25" s="18">
+      <c r="C25" s="9"/>
+      <c r="E25" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:4">
+    <row r="26" spans="2:5">
       <c r="B26" s="12">
         <v>18</v>
       </c>
-      <c r="D26" s="18">
+      <c r="C26" s="9"/>
+      <c r="E26" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:4">
+    <row r="27" spans="2:5">
       <c r="B27" s="12">
         <v>19</v>
       </c>
-      <c r="D27" s="18">
+      <c r="C27" s="9"/>
+      <c r="E27" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:4">
+    <row r="28" spans="2:5">
       <c r="B28" s="12" t="s">
         <v>3816</v>
       </c>
-      <c r="D28" s="18">
+      <c r="C28" s="9"/>
+      <c r="E28" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:4">
+    <row r="29" spans="2:5">
       <c r="B29" s="12" t="s">
         <v>3817</v>
       </c>
-      <c r="D29" s="18">
+      <c r="C29" s="9"/>
+      <c r="E29" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:4">
+    <row r="30" spans="2:5">
       <c r="B30" s="12" t="s">
         <v>3818</v>
       </c>
-      <c r="D30" s="18">
+      <c r="C30" s="9"/>
+      <c r="E30" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:4">
+    <row r="31" spans="2:5">
       <c r="B31" s="12" t="s">
         <v>3819</v>
       </c>
-      <c r="D31" s="18">
+      <c r="C31" s="9"/>
+      <c r="E31" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:4">
+    <row r="32" spans="2:5">
       <c r="B32" s="12" t="s">
         <v>3820</v>
       </c>
-      <c r="D32" s="18">
+      <c r="C32" s="9"/>
+      <c r="E32" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:12">
       <c r="B33" s="12" t="s">
         <v>3821</v>
       </c>
-      <c r="D33" s="18">
+      <c r="C33" s="9"/>
+      <c r="E33" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:12">
       <c r="B34" s="12">
         <v>20</v>
       </c>
-      <c r="D34" s="18">
+      <c r="C34" s="9"/>
+      <c r="E34" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:12">
       <c r="B35" s="12">
         <v>21</v>
       </c>
-      <c r="D35" s="18">
+      <c r="C35" s="9"/>
+      <c r="E35" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:12">
       <c r="B36" s="12">
         <v>22</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="C36" s="9"/>
+      <c r="E36" s="18" t="s">
         <v>3804</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:12">
       <c r="B37" s="12">
         <v>23</v>
       </c>
-      <c r="D37" s="18">
+      <c r="C37" s="9"/>
+      <c r="E37" s="18">
         <v>2</v>
       </c>
-      <c r="J37" s="10"/>
-    </row>
-    <row r="38" spans="1:11" ht="23" customHeight="1">
+      <c r="K37" s="10"/>
+    </row>
+    <row r="38" spans="1:12" ht="23" customHeight="1">
       <c r="A38" s="9" t="s">
         <v>3822</v>
       </c>
       <c r="B38" s="12">
         <v>24</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="9" t="s">
+        <v>3822</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>3823</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="E38" s="18" t="s">
         <v>3824</v>
       </c>
-      <c r="J38" s="10"/>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="K38" s="10"/>
+    </row>
+    <row r="39" spans="1:12">
       <c r="B39" s="12">
         <v>25</v>
       </c>
-      <c r="D39" s="18">
+      <c r="C39" s="9"/>
+      <c r="E39" s="18">
         <v>0</v>
       </c>
-      <c r="J39" s="10"/>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="K39" s="10"/>
+    </row>
+    <row r="40" spans="1:12">
       <c r="B40" s="12">
         <v>26</v>
       </c>
-      <c r="D40" s="18">
+      <c r="C40" s="9"/>
+      <c r="E40" s="18">
         <v>0</v>
       </c>
-      <c r="J40" s="10"/>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="K40" s="10"/>
+    </row>
+    <row r="41" spans="1:12">
       <c r="B41" s="12">
         <v>27</v>
       </c>
-      <c r="D41" s="18">
+      <c r="C41" s="9"/>
+      <c r="E41" s="18">
         <v>27</v>
       </c>
-      <c r="J41" s="10"/>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="K41" s="10"/>
+    </row>
+    <row r="42" spans="1:12">
       <c r="B42" s="12">
         <v>28</v>
       </c>
-      <c r="D42" s="18">
+      <c r="C42" s="9"/>
+      <c r="E42" s="18">
         <v>0</v>
       </c>
-      <c r="J42" s="10"/>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="K42" s="10"/>
+    </row>
+    <row r="43" spans="1:12">
       <c r="B43" s="12">
         <v>29</v>
       </c>
-      <c r="D43" s="18">
+      <c r="C43" s="9"/>
+      <c r="E43" s="18">
         <v>0</v>
       </c>
-      <c r="K43" s="10"/>
-    </row>
-    <row r="44" spans="1:11" ht="45" customHeight="1">
+      <c r="L43" s="10"/>
+    </row>
+    <row r="44" spans="1:12" ht="45" customHeight="1">
       <c r="B44" s="13" t="s">
         <v>3825</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="9"/>
+      <c r="D44" s="16" t="s">
         <v>3826</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="E44" s="18" t="s">
         <v>3827</v>
       </c>
-      <c r="K44" s="10"/>
-    </row>
-    <row r="45" spans="1:11" ht="23" customHeight="1">
+      <c r="L44" s="10"/>
+    </row>
+    <row r="45" spans="1:12" ht="23" customHeight="1">
       <c r="B45" s="13" t="s">
         <v>3828</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="9"/>
+      <c r="D45" s="16" t="s">
         <v>3829</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="E45" s="18" t="s">
         <v>3817</v>
       </c>
-      <c r="J45" s="10"/>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="K45" s="10"/>
+    </row>
+    <row r="46" spans="1:12">
       <c r="B46" s="12" t="s">
         <v>3830</v>
       </c>
-      <c r="D46" s="18">
+      <c r="C46" s="9"/>
+      <c r="E46" s="18">
         <v>0</v>
       </c>
-      <c r="J46" s="10"/>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="K46" s="10"/>
+    </row>
+    <row r="47" spans="1:12">
       <c r="B47" s="12" t="s">
         <v>3831</v>
       </c>
-      <c r="D47" s="18">
+      <c r="C47" s="9"/>
+      <c r="E47" s="18">
         <v>0</v>
       </c>
-      <c r="J47" s="10"/>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="K47" s="10"/>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48" s="9" t="s">
         <v>3832</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>3833</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="C48" s="9" t="s">
+        <v>4405</v>
+      </c>
+      <c r="E48" s="18" t="s">
         <v>3834</v>
       </c>
-      <c r="J48" s="10"/>
-    </row>
-    <row r="49" spans="1:10" ht="23" customHeight="1">
+      <c r="K48" s="10"/>
+    </row>
+    <row r="49" spans="1:11" ht="23" customHeight="1">
       <c r="A49" s="9" t="s">
         <v>3835</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>3836</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="9" t="s">
+        <v>4406</v>
+      </c>
+      <c r="D49" s="15" t="s">
         <v>3837</v>
       </c>
-      <c r="D49" s="18">
+      <c r="E49" s="18">
         <v>0</v>
       </c>
-      <c r="J49" s="10"/>
-    </row>
-    <row r="50" spans="1:10">
+      <c r="K49" s="10"/>
+    </row>
+    <row r="50" spans="1:11">
       <c r="B50" s="12">
         <v>30</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="C50" s="9"/>
+      <c r="E50" s="18" t="s">
         <v>3834</v>
       </c>
-      <c r="J50" s="10"/>
-    </row>
-    <row r="51" spans="1:10">
+      <c r="K50" s="10"/>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" s="9" t="s">
         <v>3838</v>
       </c>
       <c r="B51" s="12">
         <v>31</v>
       </c>
-      <c r="D51" s="18">
+      <c r="C51" s="9" t="s">
+        <v>4407</v>
+      </c>
+      <c r="E51" s="18">
         <v>0</v>
       </c>
-      <c r="J51" s="10"/>
-    </row>
-    <row r="52" spans="1:10">
+      <c r="K51" s="10"/>
+    </row>
+    <row r="52" spans="1:11">
       <c r="B52" s="12">
         <v>32</v>
       </c>
-      <c r="D52" s="18">
+      <c r="C52" s="9"/>
+      <c r="E52" s="18">
         <v>0</v>
       </c>
-      <c r="J52" s="10"/>
-    </row>
-    <row r="53" spans="1:10" ht="23" customHeight="1">
+      <c r="K52" s="10"/>
+    </row>
+    <row r="53" spans="1:11" ht="23" customHeight="1">
       <c r="A53" s="9" t="s">
         <v>3839</v>
       </c>
       <c r="B53" s="12">
         <v>33</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="9" t="s">
+        <v>3839</v>
+      </c>
+      <c r="D53" s="15" t="s">
         <v>3840</v>
       </c>
-      <c r="D53" s="18">
+      <c r="E53" s="18">
         <v>0</v>
       </c>
-      <c r="J53" s="10"/>
-    </row>
-    <row r="54" spans="1:10">
+      <c r="K53" s="10"/>
+    </row>
+    <row r="54" spans="1:11">
       <c r="B54" s="12">
         <v>34</v>
       </c>
-      <c r="D54" s="18">
+      <c r="C54" s="9"/>
+      <c r="E54" s="18">
         <v>6</v>
       </c>
-      <c r="J54" s="10"/>
-    </row>
-    <row r="55" spans="1:10">
+      <c r="K54" s="10"/>
+    </row>
+    <row r="55" spans="1:11">
       <c r="B55" s="12">
         <v>35</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="C55" s="9"/>
+      <c r="E55" s="18" t="s">
         <v>3834</v>
       </c>
-      <c r="J55" s="10"/>
-    </row>
-    <row r="56" spans="1:10">
+      <c r="K55" s="10"/>
+    </row>
+    <row r="56" spans="1:11">
       <c r="B56" s="12">
         <v>36</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="C56" s="9"/>
+      <c r="E56" s="18" t="s">
         <v>3834</v>
       </c>
-      <c r="J56" s="10"/>
-    </row>
-    <row r="57" spans="1:10">
+      <c r="K56" s="10"/>
+    </row>
+    <row r="57" spans="1:11">
       <c r="B57" s="12">
         <v>37</v>
       </c>
-      <c r="D57" s="18">
+      <c r="C57" s="9"/>
+      <c r="E57" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="46" customHeight="1">
+    <row r="58" spans="1:11" ht="46" customHeight="1">
       <c r="A58" s="9" t="s">
         <v>3841</v>
       </c>
       <c r="B58" s="12">
         <v>38</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="9" t="s">
+        <v>3841</v>
+      </c>
+      <c r="D58" s="15" t="s">
         <v>3842</v>
       </c>
-      <c r="D58" s="18">
+      <c r="E58" s="18">
         <v>71</v>
       </c>
-      <c r="J58" s="10"/>
-    </row>
-    <row r="59" spans="1:10" ht="23" customHeight="1">
+      <c r="K58" s="10"/>
+    </row>
+    <row r="59" spans="1:11" ht="23" customHeight="1">
       <c r="A59" s="9" t="s">
         <v>3843</v>
       </c>
       <c r="B59" s="12">
         <v>39</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C59" s="9" t="s">
+        <v>4420</v>
+      </c>
+      <c r="D59" s="15" t="s">
         <v>3844</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="E59" s="18" t="s">
         <v>3845</v>
       </c>
-      <c r="J59" s="10"/>
-    </row>
-    <row r="60" spans="1:10" ht="23" customHeight="1">
+      <c r="K59" s="10"/>
+    </row>
+    <row r="60" spans="1:11" ht="23" customHeight="1">
       <c r="A60" s="9" t="s">
         <v>3846</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>3847</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" s="9" t="s">
+        <v>4408</v>
+      </c>
+      <c r="D60" s="15" t="s">
         <v>3848</v>
       </c>
-      <c r="D60" s="18">
+      <c r="E60" s="18">
         <v>0</v>
       </c>
-      <c r="J60" s="10"/>
-    </row>
-    <row r="61" spans="1:10">
+      <c r="K60" s="10"/>
+    </row>
+    <row r="61" spans="1:11" ht="46">
       <c r="B61" s="12" t="s">
         <v>3849</v>
       </c>
-      <c r="D61" s="18">
+      <c r="C61" s="9" t="s">
+        <v>4422</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>4423</v>
+      </c>
+      <c r="E61" s="18">
         <v>77</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="23" customHeight="1">
+    <row r="62" spans="1:11" ht="23" customHeight="1">
       <c r="A62" s="9" t="s">
         <v>3850</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>3851</v>
       </c>
-      <c r="C62" s="15" t="s">
+      <c r="C62" s="9" t="s">
+        <v>4409</v>
+      </c>
+      <c r="D62" s="15" t="s">
         <v>3852</v>
       </c>
-      <c r="D62" s="18">
+      <c r="E62" s="18">
         <v>77</v>
       </c>
-      <c r="J62" s="10"/>
-    </row>
-    <row r="63" spans="1:10">
+      <c r="K62" s="10"/>
+    </row>
+    <row r="63" spans="1:11">
       <c r="B63" s="12" t="s">
         <v>3853</v>
       </c>
-      <c r="D63" s="18">
+      <c r="C63" s="9"/>
+      <c r="E63" s="18">
         <v>77</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="23" customHeight="1">
+    <row r="64" spans="1:11" ht="23" customHeight="1">
       <c r="B64" s="13" t="s">
         <v>3854</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C64" s="9" t="s">
+        <v>4410</v>
+      </c>
+      <c r="D64" s="16" t="s">
         <v>3855</v>
       </c>
-      <c r="D64" s="18">
+      <c r="E64" s="18">
         <v>77</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:11">
       <c r="B65" s="12" t="s">
         <v>3856</v>
       </c>
-      <c r="D65" s="18">
+      <c r="C65" s="9"/>
+      <c r="E65" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:11">
       <c r="B66" s="12">
         <v>40</v>
       </c>
-      <c r="D66" s="18">
+      <c r="C66" s="9"/>
+      <c r="E66" s="18">
         <v>77</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:11">
       <c r="B67" s="12">
         <v>41</v>
       </c>
-      <c r="D67" s="18">
+      <c r="C67" s="9"/>
+      <c r="E67" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:11">
       <c r="B68" s="12">
         <v>42</v>
       </c>
-      <c r="D68" s="18">
+      <c r="C68" s="9"/>
+      <c r="E68" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:11">
       <c r="B69" s="12">
         <v>43</v>
       </c>
-      <c r="D69" s="18">
+      <c r="C69" s="9" t="s">
+        <v>4421</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>4424</v>
+      </c>
+      <c r="E69" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="23" customHeight="1">
+    <row r="70" spans="1:11" ht="23" customHeight="1">
       <c r="A70" s="9" t="s">
         <v>3857</v>
       </c>
       <c r="B70" s="12">
         <v>44</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="C70" s="9" t="s">
+        <v>3857</v>
+      </c>
+      <c r="D70" s="15" t="s">
         <v>3858</v>
       </c>
-      <c r="D70" s="18">
+      <c r="E70" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="69" customHeight="1">
+    <row r="71" spans="1:11" ht="69" customHeight="1">
       <c r="A71" s="9" t="s">
         <v>3859</v>
       </c>
       <c r="B71" s="12">
         <v>45</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="C71" s="9" t="s">
+        <v>4411</v>
+      </c>
+      <c r="D71" s="15" t="s">
         <v>3860</v>
       </c>
-      <c r="D71" s="18">
+      <c r="E71" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="23" customHeight="1">
+    <row r="72" spans="1:11" ht="23" customHeight="1">
       <c r="A72" s="9" t="s">
         <v>3861</v>
       </c>
       <c r="B72" s="12">
         <v>46</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C72" s="9" t="s">
+        <v>4412</v>
+      </c>
+      <c r="D72" s="15" t="s">
         <v>3862</v>
       </c>
-      <c r="D72" s="18">
+      <c r="E72" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="45" customHeight="1">
+    <row r="73" spans="1:11" ht="45" customHeight="1">
+      <c r="A73" s="9" t="s">
+        <v>4428</v>
+      </c>
       <c r="B73" s="13">
         <v>47</v>
       </c>
-      <c r="C73" s="16" t="s">
+      <c r="C73" s="9" t="s">
+        <v>4413</v>
+      </c>
+      <c r="D73" s="16" t="s">
         <v>3863</v>
       </c>
-      <c r="D73" s="18">
+      <c r="E73" s="18">
         <v>0</v>
       </c>
-      <c r="J73" s="10"/>
-    </row>
-    <row r="74" spans="1:10" ht="23" customHeight="1">
+      <c r="K73" s="10"/>
+    </row>
+    <row r="74" spans="1:11" ht="23" customHeight="1">
+      <c r="A74" s="9" t="s">
+        <v>4425</v>
+      </c>
       <c r="B74" s="13">
         <v>48</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="C74" s="9" t="s">
+        <v>4414</v>
+      </c>
+      <c r="D74" s="16" t="s">
         <v>3864</v>
       </c>
-      <c r="D74" s="18">
+      <c r="E74" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:11">
       <c r="B75" s="13">
         <v>49</v>
       </c>
-      <c r="C75" s="16"/>
-      <c r="D75" s="18">
+      <c r="C75" s="9"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="45" customHeight="1">
+    <row r="76" spans="1:11" ht="45" customHeight="1">
       <c r="B76" s="13" t="s">
         <v>3865</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C76" s="9" t="s">
+        <v>4415</v>
+      </c>
+      <c r="D76" s="16" t="s">
         <v>3866</v>
       </c>
-      <c r="D76" s="18">
+      <c r="E76" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="45" customHeight="1">
+    <row r="77" spans="1:11" ht="45" customHeight="1">
       <c r="B77" s="13" t="s">
         <v>3867</v>
       </c>
-      <c r="C77" s="16" t="s">
+      <c r="C77" s="9" t="s">
+        <v>4416</v>
+      </c>
+      <c r="D77" s="16" t="s">
         <v>3868</v>
       </c>
-      <c r="D77" s="18">
+      <c r="E77" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="23" customHeight="1">
+    <row r="78" spans="1:11" ht="23" customHeight="1">
+      <c r="A78" s="9" t="s">
+        <v>4426</v>
+      </c>
       <c r="B78" s="13" t="s">
         <v>3869</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C78" s="9" t="s">
+        <v>4417</v>
+      </c>
+      <c r="D78" s="16" t="s">
         <v>3870</v>
       </c>
-      <c r="D78" s="18">
+      <c r="E78" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:11">
       <c r="B79" s="13" t="s">
         <v>3871</v>
       </c>
-      <c r="C79" s="16"/>
-      <c r="D79" s="18">
+      <c r="C79" s="9"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="23" customHeight="1">
+    <row r="80" spans="1:11" ht="23" customHeight="1">
       <c r="B80" s="13" t="s">
         <v>3872</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="C80" s="9" t="s">
+        <v>4418</v>
+      </c>
+      <c r="D80" s="16" t="s">
         <v>3873</v>
       </c>
-      <c r="D80" s="18">
+      <c r="E80" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:4">
+    <row r="81" spans="2:5">
       <c r="B81" s="13" t="s">
         <v>3874</v>
       </c>
-      <c r="C81" s="16"/>
-      <c r="D81" s="18">
+      <c r="C81" s="9"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:4" ht="23" customHeight="1">
+    <row r="82" spans="2:5" ht="23" customHeight="1">
       <c r="B82" s="13">
         <v>50</v>
       </c>
-      <c r="C82" s="16" t="s">
+      <c r="C82" s="9" t="s">
+        <v>4419</v>
+      </c>
+      <c r="D82" s="16" t="s">
         <v>3875</v>
       </c>
-      <c r="D82" s="18">
+      <c r="E82" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:4">
+    <row r="83" spans="2:5">
       <c r="B83" s="13">
         <v>51</v>
       </c>
-      <c r="C83" s="16"/>
-      <c r="D83" s="18">
+      <c r="C83" s="9"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:4">
+    <row r="84" spans="2:5">
       <c r="B84" s="13">
         <v>52</v>
       </c>
-      <c r="C84" s="16"/>
-      <c r="D84" s="18">
+      <c r="C84" s="9"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:4">
+    <row r="85" spans="2:5">
       <c r="B85" s="13">
         <v>53</v>
       </c>
-      <c r="C85" s="16"/>
-      <c r="D85" s="18">
+      <c r="C85" s="9"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:4">
+    <row r="86" spans="2:5">
       <c r="B86" s="13">
         <v>54</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="18">
+      <c r="C86" s="9"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:4">
+    <row r="87" spans="2:5">
       <c r="B87" s="13">
         <v>55</v>
       </c>
-      <c r="C87" s="16"/>
-      <c r="D87" s="18">
+      <c r="C87" s="9"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:4">
+    <row r="88" spans="2:5">
       <c r="B88" s="13">
         <v>56</v>
       </c>
-      <c r="C88" s="16"/>
-      <c r="D88" s="18">
+      <c r="C88" s="9"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:4">
+    <row r="89" spans="2:5">
       <c r="B89" s="13">
         <v>57</v>
       </c>
-      <c r="C89" s="16"/>
-      <c r="D89" s="18">
+      <c r="C89" s="9"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:4">
+    <row r="90" spans="2:5">
       <c r="B90" s="13">
         <v>58</v>
       </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="18">
+      <c r="C90" s="9"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:4">
+    <row r="91" spans="2:5">
       <c r="B91" s="13">
         <v>59</v>
       </c>
-      <c r="C91" s="16"/>
-      <c r="D91" s="18">
+      <c r="C91" s="9"/>
+      <c r="D91" s="16"/>
+      <c r="E91" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:4">
+    <row r="92" spans="2:5">
       <c r="B92" s="13" t="s">
         <v>3876</v>
       </c>
-      <c r="C92" s="16"/>
-      <c r="D92" s="18">
+      <c r="C92" s="9"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:4">
+    <row r="93" spans="2:5">
       <c r="B93" s="13" t="s">
         <v>3877</v>
       </c>
-      <c r="C93" s="16"/>
-      <c r="D93" s="18">
+      <c r="C93" s="9"/>
+      <c r="D93" s="16"/>
+      <c r="E93" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:4">
+    <row r="94" spans="2:5">
       <c r="B94" s="13" t="s">
         <v>3878</v>
       </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="18">
+      <c r="C94" s="9"/>
+      <c r="D94" s="16"/>
+      <c r="E94" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:4">
+    <row r="95" spans="2:5">
       <c r="B95" s="13" t="s">
         <v>3879</v>
       </c>
-      <c r="C95" s="16"/>
-      <c r="D95" s="18">
+      <c r="C95" s="9"/>
+      <c r="D95" s="16"/>
+      <c r="E95" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:4">
+    <row r="96" spans="2:5">
       <c r="B96" s="13" t="s">
         <v>3880</v>
       </c>
-      <c r="C96" s="16"/>
-      <c r="D96" s="18">
+      <c r="C96" s="9"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:4">
+    <row r="97" spans="2:5">
       <c r="B97" s="13" t="s">
         <v>3881</v>
       </c>
-      <c r="C97" s="16"/>
-      <c r="D97" s="18">
+      <c r="C97" s="9"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:4">
+    <row r="98" spans="2:5">
       <c r="B98" s="13">
         <v>60</v>
       </c>
-      <c r="C98" s="16"/>
-      <c r="D98" s="18">
+      <c r="C98" s="9"/>
+      <c r="D98" s="16"/>
+      <c r="E98" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:4">
+    <row r="99" spans="2:5">
       <c r="B99" s="13">
         <v>61</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="18">
+      <c r="C99" s="9"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:4">
+    <row r="100" spans="2:5">
       <c r="B100" s="13">
         <v>62</v>
       </c>
-      <c r="C100" s="16"/>
-      <c r="D100" s="18">
+      <c r="C100" s="9"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:4">
+    <row r="101" spans="2:5">
       <c r="B101" s="13">
         <v>63</v>
       </c>
-      <c r="C101" s="16"/>
-      <c r="D101" s="18">
+      <c r="C101" s="9"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:4">
+    <row r="102" spans="2:5">
       <c r="B102" s="13">
         <v>64</v>
       </c>
-      <c r="C102" s="16"/>
-      <c r="D102" s="18">
+      <c r="C102" s="9"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:4">
+    <row r="103" spans="2:5">
       <c r="B103" s="13">
         <v>65</v>
       </c>
-      <c r="C103" s="16"/>
-      <c r="D103" s="18">
+      <c r="C103" s="9"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:4">
+    <row r="104" spans="2:5">
       <c r="B104" s="13">
         <v>66</v>
       </c>
-      <c r="C104" s="16"/>
-      <c r="D104" s="18">
+      <c r="C104" s="9"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:4">
+    <row r="105" spans="2:5">
       <c r="B105" s="13">
         <v>67</v>
       </c>
-      <c r="C105" s="16"/>
-      <c r="D105" s="18">
+      <c r="C105" s="9"/>
+      <c r="D105" s="16"/>
+      <c r="E105" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="2:4">
+    <row r="106" spans="2:5">
       <c r="B106" s="13">
         <v>68</v>
       </c>
-      <c r="C106" s="16"/>
-      <c r="D106" s="18">
+      <c r="C106" s="9"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="2:4" ht="23" customHeight="1">
+    <row r="107" spans="2:5" ht="23" customHeight="1">
       <c r="B107" s="13">
         <v>69</v>
       </c>
-      <c r="C107" s="16" t="s">
+      <c r="C107" s="9"/>
+      <c r="D107" s="16" t="s">
         <v>3882</v>
       </c>
-      <c r="D107" s="18">
+      <c r="E107" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="2:4">
+    <row r="108" spans="2:5">
       <c r="B108" s="13" t="s">
         <v>3883</v>
       </c>
-      <c r="C108" s="16"/>
-      <c r="D108" s="18">
+      <c r="C108" s="9"/>
+      <c r="D108" s="16"/>
+      <c r="E108" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="2:4">
+    <row r="109" spans="2:5">
       <c r="B109" s="13" t="s">
         <v>3884</v>
       </c>
-      <c r="C109" s="16"/>
-      <c r="D109" s="18">
+      <c r="C109" s="9"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="2:4">
+    <row r="110" spans="2:5">
       <c r="B110" s="13" t="s">
         <v>3885</v>
       </c>
-      <c r="C110" s="16"/>
-      <c r="D110" s="18">
+      <c r="C110" s="9"/>
+      <c r="D110" s="16"/>
+      <c r="E110" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="2:4">
+    <row r="111" spans="2:5">
       <c r="B111" s="13" t="s">
         <v>3886</v>
       </c>
-      <c r="C111" s="16"/>
-      <c r="D111" s="18">
+      <c r="C111" s="9"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="2:4">
+    <row r="112" spans="2:5">
       <c r="B112" s="13" t="s">
         <v>3887</v>
       </c>
-      <c r="C112" s="16"/>
-      <c r="D112" s="18">
+      <c r="C112" s="9"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:5">
       <c r="B113" s="13" t="s">
         <v>3810</v>
       </c>
-      <c r="C113" s="16"/>
-      <c r="D113" s="18">
+      <c r="C113" s="9"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:5">
       <c r="B114" s="13">
         <v>70</v>
       </c>
-      <c r="C114" s="16"/>
-      <c r="D114" s="18">
+      <c r="C114" s="9"/>
+      <c r="D114" s="16"/>
+      <c r="E114" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:5">
       <c r="B115" s="13">
         <v>71</v>
       </c>
-      <c r="C115" s="16"/>
-      <c r="D115" s="18">
+      <c r="C115" s="9"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:5">
       <c r="B116" s="13">
         <v>72</v>
       </c>
-      <c r="C116" s="16"/>
-      <c r="D116" s="18">
+      <c r="C116" s="9"/>
+      <c r="D116" s="16"/>
+      <c r="E116" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:5">
       <c r="B117" s="13">
         <v>73</v>
       </c>
-      <c r="C117" s="16"/>
-      <c r="D117" s="18">
+      <c r="C117" s="9"/>
+      <c r="D117" s="16"/>
+      <c r="E117" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:5">
       <c r="B118" s="13">
         <v>74</v>
       </c>
-      <c r="C118" s="16"/>
-      <c r="D118" s="18">
+      <c r="C118" s="9"/>
+      <c r="D118" s="16"/>
+      <c r="E118" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:5">
       <c r="B119" s="13">
         <v>75</v>
       </c>
-      <c r="C119" s="16"/>
-      <c r="D119" s="18">
+      <c r="C119" s="9"/>
+      <c r="D119" s="16"/>
+      <c r="E119" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:5">
       <c r="B120" s="13">
         <v>76</v>
       </c>
-      <c r="C120" s="16"/>
-      <c r="D120" s="18">
+      <c r="C120" s="9"/>
+      <c r="D120" s="16"/>
+      <c r="E120" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:5">
       <c r="B121" s="13">
         <v>77</v>
       </c>
-      <c r="C121" s="16"/>
-      <c r="D121" s="18">
+      <c r="C121" s="9"/>
+      <c r="D121" s="16"/>
+      <c r="E121" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:5">
       <c r="B122" s="13">
         <v>78</v>
       </c>
-      <c r="C122" s="16"/>
-      <c r="D122" s="18">
+      <c r="C122" s="9"/>
+      <c r="D122" s="16"/>
+      <c r="E122" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:5">
       <c r="B123" s="13">
         <v>79</v>
       </c>
-      <c r="C123" s="16"/>
-      <c r="D123" s="18">
+      <c r="C123" s="9"/>
+      <c r="D123" s="16"/>
+      <c r="E123" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="23" customHeight="1">
+    <row r="124" spans="1:5" ht="23" customHeight="1">
       <c r="A124" s="9" t="s">
-        <v>3888</v>
+        <v>4427</v>
       </c>
       <c r="B124" s="12" t="s">
         <v>3889</v>
       </c>
-      <c r="C124" s="15" t="s">
+      <c r="C124" s="9" t="s">
+        <v>3888</v>
+      </c>
+      <c r="D124" s="15" t="s">
         <v>3890</v>
       </c>
-      <c r="D124" s="18">
+      <c r="E124" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:5">
       <c r="B125" s="12" t="s">
         <v>3891</v>
       </c>
-      <c r="D125" s="18">
+      <c r="C125" s="9"/>
+      <c r="E125" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:5">
       <c r="B126" s="12" t="s">
         <v>3892</v>
       </c>
-      <c r="D126" s="18">
+      <c r="C126" s="9"/>
+      <c r="E126" s="18">
         <v>43</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:5">
       <c r="B127" s="12" t="s">
         <v>3893</v>
       </c>
-      <c r="D127" s="18">
+      <c r="C127" s="9"/>
+      <c r="E127" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:5">
       <c r="B128" s="12" t="s">
         <v>3894</v>
       </c>
-      <c r="D128" s="18">
+      <c r="C128" s="9"/>
+      <c r="E128" s="18">
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="2:4">
+    <row r="129" spans="2:5">
       <c r="B129" s="12" t="s">
         <v>3824</v>
       </c>
-      <c r="D129" s="18" t="s">
+      <c r="E129" s="18" t="s">
         <v>1586</v>
       </c>
     </row>

--- a/gemini8048/bin/87KLR951.xlsx
+++ b/gemini8048/bin/87KLR951.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mike/coding_projects/944/DME_sim/gemini8048/bin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFA0F05-AC71-694D-9A54-DEA9E9F0CFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8A813D-1549-B249-90FC-10D2045F3EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37360" yWindow="8740" windowWidth="47100" windowHeight="24480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3920" yWindow="18100" windowWidth="47100" windowHeight="24480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASM" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8162" uniqueCount="4429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8163" uniqueCount="4429">
   <si>
     <t>https://junctionbyte.com/8051-microcontroller-special-function-registers/</t>
   </si>
@@ -13437,7 +13437,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -13497,6 +13497,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -13841,7 +13844,7 @@
     <col min="4" max="4" width="14.5" customWidth="1"/>
     <col min="5" max="5" width="25.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="26.6640625" customWidth="1"/>
-    <col min="7" max="7" width="80.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="59" customWidth="1"/>
     <col min="8" max="8" width="61.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="80.6640625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="72" customWidth="1"/>
@@ -26813,6 +26816,9 @@
     <row r="701" spans="1:34">
       <c r="A701" t="s">
         <v>2166</v>
+      </c>
+      <c r="B701" s="27" t="s">
+        <v>117</v>
       </c>
       <c r="C701" s="1" t="s">
         <v>2167</v>

--- a/gemini8048/bin/87KLR951.xlsx
+++ b/gemini8048/bin/87KLR951.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mike/coding_projects/944/DME_sim/gemini8048/bin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C2AEDB-3118-744F-91F3-05DB9B46F31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1C6CC1-E034-104A-A412-2F5E561912E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12760" yWindow="11380" windowWidth="39200" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12760" yWindow="11380" windowWidth="48760" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASM" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8144" uniqueCount="4410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8147" uniqueCount="4413">
   <si>
     <t>https://junctionbyte.com/8051-microcontroller-special-function-registers/</t>
   </si>
@@ -13264,9 +13264,6 @@
     <t>knock_thresh_coeef</t>
   </si>
   <si>
-    <t>// get value from map addr = 925 (2AH)</t>
-  </si>
-  <si>
     <t>// r2 gets 2eH</t>
   </si>
   <si>
@@ -13277,6 +13274,18 @@
   </si>
   <si>
     <t>// store 7f into mem[2a]</t>
+  </si>
+  <si>
+    <t>// 1st pass: get value from map addr = 925 (2AH), 2nd pass from 92eh (2bh)</t>
+  </si>
+  <si>
+    <t>eventually exits loop at map addr 991</t>
+  </si>
+  <si>
+    <t>//get byte from addr 9B1 (e3H)</t>
+  </si>
+  <si>
+    <t>data at end of map lookup gets stored here (code addr = 923)</t>
   </si>
 </sst>
 </file>
@@ -26756,7 +26765,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="705" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
         <v>2154</v>
       </c>
@@ -26773,7 +26782,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="706" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A706" t="s">
         <v>2155</v>
       </c>
@@ -26790,7 +26799,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="707" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A707" t="s">
         <v>2156</v>
       </c>
@@ -26807,7 +26816,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="708" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A708" t="s">
         <v>2157</v>
       </c>
@@ -26824,7 +26833,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="709" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A709" t="s">
         <v>2158</v>
       </c>
@@ -26841,7 +26850,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="710" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A710" t="s">
         <v>2159</v>
       </c>
@@ -26858,7 +26867,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="711" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A711" t="s">
         <v>2160</v>
       </c>
@@ -26875,7 +26884,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="712" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A712" t="s">
         <v>2164</v>
       </c>
@@ -26895,7 +26904,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="713" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A713" t="s">
         <v>2166</v>
       </c>
@@ -26912,10 +26921,13 @@
         <v>630</v>
       </c>
       <c r="G713" s="1" t="s">
-        <v>4405</v>
-      </c>
-    </row>
-    <row r="714" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4409</v>
+      </c>
+      <c r="H713" t="s">
+        <v>4410</v>
+      </c>
+    </row>
+    <row r="714" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A714" t="s">
         <v>2167</v>
       </c>
@@ -26932,7 +26944,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="715" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A715" t="s">
         <v>2171</v>
       </c>
@@ -26949,7 +26961,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="716" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A716" t="s">
         <v>2172</v>
       </c>
@@ -26966,7 +26978,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="717" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A717" t="s">
         <v>2173</v>
       </c>
@@ -26984,7 +26996,7 @@
       </c>
       <c r="G717" s="1"/>
     </row>
-    <row r="718" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
         <v>2177</v>
       </c>
@@ -27001,10 +27013,10 @@
         <v>149</v>
       </c>
       <c r="G718" s="1" t="s">
-        <v>4406</v>
-      </c>
-    </row>
-    <row r="719" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4405</v>
+      </c>
+    </row>
+    <row r="719" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A719" t="s">
         <v>2178</v>
       </c>
@@ -27021,10 +27033,10 @@
         <v>2181</v>
       </c>
       <c r="G719" s="1" t="s">
-        <v>4407</v>
-      </c>
-    </row>
-    <row r="720" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4406</v>
+      </c>
+    </row>
+    <row r="720" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A720" t="s">
         <v>2182</v>
       </c>
@@ -27041,7 +27053,7 @@
         <v>630</v>
       </c>
       <c r="G720" s="1" t="s">
-        <v>4408</v>
+        <v>4407</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.2">
@@ -27061,7 +27073,7 @@
         <v>387</v>
       </c>
       <c r="G721" s="1" t="s">
-        <v>4409</v>
+        <v>4408</v>
       </c>
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.2">
@@ -27187,6 +27199,9 @@
       </c>
       <c r="F728" t="s">
         <v>630</v>
+      </c>
+      <c r="G728" s="1" t="s">
+        <v>4411</v>
       </c>
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.2">
@@ -41393,12 +41408,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:5" ht="23" x14ac:dyDescent="0.3">
       <c r="B109" s="13" t="s">
         <v>3860</v>
       </c>
       <c r="C109" s="9"/>
-      <c r="D109" s="16"/>
+      <c r="D109" s="16" t="s">
+        <v>4412</v>
+      </c>
       <c r="E109" s="18">
         <v>0</v>
       </c>

--- a/gemini8048/bin/87KLR951.xlsx
+++ b/gemini8048/bin/87KLR951.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mike/coding_projects/944/DME_sim/gemini8048/bin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1C6CC1-E034-104A-A412-2F5E561912E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EBECBC-8B97-944C-A509-9307ABBADC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12760" yWindow="11380" windowWidth="48760" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16140" yWindow="12620" windowWidth="48760" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASM" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8147" uniqueCount="4413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8149" uniqueCount="4416">
   <si>
     <t>https://junctionbyte.com/8051-microcontroller-special-function-registers/</t>
   </si>
@@ -13286,6 +13286,15 @@
   </si>
   <si>
     <t>data at end of map lookup gets stored here (code addr = 923)</t>
+  </si>
+  <si>
+    <t>//wrong call - goes to C80 not 480</t>
+  </si>
+  <si>
+    <t>labelb80:</t>
+  </si>
+  <si>
+    <t>label0b80</t>
   </si>
 </sst>
 </file>
@@ -13791,7 +13800,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.5" customWidth="1"/>
     <col min="5" max="5" width="25.33203125" style="1" customWidth="1"/>
@@ -29058,6 +29067,9 @@
       <c r="F829" t="s">
         <v>2434</v>
       </c>
+      <c r="G829" s="1" t="s">
+        <v>4413</v>
+      </c>
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A830" t="s">
@@ -29232,7 +29244,7 @@
         <v>323</v>
       </c>
       <c r="E839" s="1" t="s">
-        <v>2459</v>
+        <v>4415</v>
       </c>
       <c r="F839" t="s">
         <v>2460</v>
@@ -29403,6 +29415,9 @@
     <row r="849" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A849" t="s">
         <v>2481</v>
+      </c>
+      <c r="B849" t="s">
+        <v>4414</v>
       </c>
       <c r="C849" s="1" t="s">
         <v>130</v>

--- a/gemini8048/bin/87KLR951.xlsx
+++ b/gemini8048/bin/87KLR951.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mike/coding_projects/944/DME_sim/gemini8048/bin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EBECBC-8B97-944C-A509-9307ABBADC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF0E645-6EEC-734C-B36B-605E80B71C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16140" yWindow="12620" windowWidth="48760" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="49000" yWindow="17460" windowWidth="48760" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASM" sheetId="1" r:id="rId1"/>

--- a/gemini8048/bin/87KLR951.xlsx
+++ b/gemini8048/bin/87KLR951.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mike/coding_projects/944/DME_sim/gemini8048/bin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29040BDC-1EC8-E246-8B44-CC942A81796C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC48498-4E86-3044-BF70-F15395387878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15680" yWindow="7840" windowWidth="54880" windowHeight="24240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7400" yWindow="15820" windowWidth="54880" windowHeight="24240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASM" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8248" uniqueCount="4503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8248" uniqueCount="4502">
   <si>
     <t>https://junctionbyte.com/8051-microcontroller-special-function-registers/</t>
   </si>
@@ -10685,9 +10685,6 @@
   </si>
   <si>
     <t>0x0F60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">r1,#33 </t>
   </si>
   <si>
     <t xml:space="preserve">mov r1,#33 </t>
@@ -15447,7 +15444,7 @@
         <v>310</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>4400</v>
+        <v>4399</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -18562,7 +18559,7 @@
         <v>809</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>4347</v>
+        <v>4346</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.2">
@@ -18636,7 +18633,7 @@
         <v>820</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>4348</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.2">
@@ -18696,7 +18693,7 @@
         <v>592</v>
       </c>
       <c r="G253" t="s">
-        <v>4349</v>
+        <v>4348</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.2">
@@ -21551,14 +21548,14 @@
         <v>59</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>4397</v>
+        <v>4396</v>
       </c>
       <c r="F408" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">mov r2,#41 </v>
       </c>
       <c r="G408" t="s">
-        <v>4501</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
@@ -21636,7 +21633,7 @@
         <v>inc r2</v>
       </c>
       <c r="G412" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
@@ -24323,7 +24320,7 @@
         <v>1730</v>
       </c>
       <c r="G558" t="s">
-        <v>4353</v>
+        <v>4352</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.2">
@@ -24343,7 +24340,7 @@
         <v>1734</v>
       </c>
       <c r="G559" s="1" t="s">
-        <v>4354</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.2">
@@ -24363,7 +24360,7 @@
         <v>1734</v>
       </c>
       <c r="G560" s="1" t="s">
-        <v>4354</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.2">
@@ -24383,7 +24380,7 @@
         <v>1734</v>
       </c>
       <c r="G561" s="1" t="s">
-        <v>4354</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.2">
@@ -24403,7 +24400,7 @@
         <v>1739</v>
       </c>
       <c r="G562" s="1" t="s">
-        <v>4355</v>
+        <v>4354</v>
       </c>
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.2">
@@ -24423,7 +24420,7 @@
         <v>1743</v>
       </c>
       <c r="G563" s="1" t="s">
-        <v>4351</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.2">
@@ -24443,7 +24440,7 @@
         <v>1747</v>
       </c>
       <c r="G564" s="1" t="s">
-        <v>4352</v>
+        <v>4351</v>
       </c>
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.2">
@@ -24463,7 +24460,7 @@
         <v>1750</v>
       </c>
       <c r="G565" t="s">
-        <v>4356</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.2">
@@ -26217,7 +26214,7 @@
         <v>287</v>
       </c>
       <c r="G659" s="1" t="s">
-        <v>4498</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.2">
@@ -27204,10 +27201,10 @@
         <v>630</v>
       </c>
       <c r="G713" s="1" t="s">
+        <v>4389</v>
+      </c>
+      <c r="H713" t="s">
         <v>4390</v>
-      </c>
-      <c r="H713" t="s">
-        <v>4391</v>
       </c>
     </row>
     <row r="714" spans="1:8" x14ac:dyDescent="0.2">
@@ -27296,7 +27293,7 @@
         <v>149</v>
       </c>
       <c r="G718" s="1" t="s">
-        <v>4386</v>
+        <v>4385</v>
       </c>
     </row>
     <row r="719" spans="1:8" x14ac:dyDescent="0.2">
@@ -27316,7 +27313,7 @@
         <v>2178</v>
       </c>
       <c r="G719" s="1" t="s">
-        <v>4387</v>
+        <v>4386</v>
       </c>
     </row>
     <row r="720" spans="1:8" x14ac:dyDescent="0.2">
@@ -27336,7 +27333,7 @@
         <v>630</v>
       </c>
       <c r="G720" s="1" t="s">
-        <v>4388</v>
+        <v>4387</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.2">
@@ -27356,7 +27353,7 @@
         <v>387</v>
       </c>
       <c r="G721" s="1" t="s">
-        <v>4389</v>
+        <v>4388</v>
       </c>
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.2">
@@ -27484,7 +27481,7 @@
         <v>630</v>
       </c>
       <c r="G728" s="1" t="s">
-        <v>4392</v>
+        <v>4391</v>
       </c>
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.2">
@@ -29342,7 +29339,7 @@
         <v>2431</v>
       </c>
       <c r="G829" s="1" t="s">
-        <v>4394</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.2">
@@ -29518,7 +29515,7 @@
         <v>323</v>
       </c>
       <c r="E839" s="1" t="s">
-        <v>4396</v>
+        <v>4395</v>
       </c>
       <c r="F839" t="s">
         <v>2457</v>
@@ -29691,7 +29688,7 @@
         <v>2478</v>
       </c>
       <c r="B849" t="s">
-        <v>4395</v>
+        <v>4394</v>
       </c>
       <c r="C849" s="1" t="s">
         <v>130</v>
@@ -31261,7 +31258,7 @@
         <v>2661</v>
       </c>
       <c r="G935" s="1" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
     </row>
     <row r="936" spans="1:8" x14ac:dyDescent="0.2">
@@ -31298,7 +31295,7 @@
         <v>287</v>
       </c>
       <c r="G937" s="1" t="s">
-        <v>4489</v>
+        <v>4488</v>
       </c>
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.2">
@@ -31321,7 +31318,7 @@
         <v>2668</v>
       </c>
       <c r="G938" t="s">
-        <v>4490</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="939" spans="1:8" x14ac:dyDescent="0.2">
@@ -31392,7 +31389,7 @@
         <v>1462</v>
       </c>
       <c r="G942" s="1" t="s">
-        <v>4494</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="943" spans="1:8" x14ac:dyDescent="0.2">
@@ -31412,7 +31409,7 @@
         <v>154</v>
       </c>
       <c r="G943" s="1" t="s">
-        <v>4491</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="944" spans="1:8" x14ac:dyDescent="0.2">
@@ -31432,7 +31429,7 @@
         <v>2680</v>
       </c>
       <c r="G944" s="1" t="s">
-        <v>4471</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.2">
@@ -31452,7 +31449,7 @@
         <v>2680</v>
       </c>
       <c r="G945" s="1" t="s">
-        <v>4471</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.2">
@@ -31472,7 +31469,7 @@
         <v>2685</v>
       </c>
       <c r="G946" s="1" t="s">
-        <v>4472</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="947" spans="1:8" x14ac:dyDescent="0.2">
@@ -31492,7 +31489,7 @@
         <v>2685</v>
       </c>
       <c r="G947" s="1" t="s">
-        <v>4472</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="948" spans="1:8" x14ac:dyDescent="0.2">
@@ -31552,7 +31549,7 @@
         <v>427</v>
       </c>
       <c r="G950" s="1" t="s">
-        <v>4402</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="951" spans="1:8" x14ac:dyDescent="0.2">
@@ -31589,7 +31586,7 @@
         <v>366</v>
       </c>
       <c r="G952" s="1" t="s">
-        <v>4495</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.2">
@@ -31626,7 +31623,7 @@
         <v>2357</v>
       </c>
       <c r="G954" s="1" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="955" spans="1:8" x14ac:dyDescent="0.2">
@@ -31646,7 +31643,7 @@
         <v>2697</v>
       </c>
       <c r="G955" s="1" t="s">
-        <v>4497</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.2">
@@ -31666,7 +31663,7 @@
         <v>2701</v>
       </c>
       <c r="G956" t="s">
-        <v>4473</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.2">
@@ -31825,7 +31822,7 @@
         <v>323</v>
       </c>
       <c r="E965" s="1" t="s">
-        <v>4465</v>
+        <v>4464</v>
       </c>
       <c r="F965" t="s">
         <v>2722</v>
@@ -32008,7 +32005,7 @@
         <v>2743</v>
       </c>
       <c r="G975" s="1" t="s">
-        <v>4403</v>
+        <v>4402</v>
       </c>
     </row>
     <row r="976" spans="1:8" x14ac:dyDescent="0.2">
@@ -32028,7 +32025,7 @@
         <v>659</v>
       </c>
       <c r="G976" t="s">
-        <v>4404</v>
+        <v>4403</v>
       </c>
     </row>
     <row r="977" spans="1:8" x14ac:dyDescent="0.2">
@@ -32085,7 +32082,7 @@
         <v>2752</v>
       </c>
       <c r="G979" s="1" t="s">
-        <v>4405</v>
+        <v>4404</v>
       </c>
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.2">
@@ -32105,7 +32102,7 @@
         <v>387</v>
       </c>
       <c r="G980" s="1" t="s">
-        <v>4406</v>
+        <v>4405</v>
       </c>
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.2">
@@ -32128,7 +32125,7 @@
         <v>2758</v>
       </c>
       <c r="G981" t="s">
-        <v>4407</v>
+        <v>4406</v>
       </c>
       <c r="H981" t="s">
         <v>2759</v>
@@ -32185,7 +32182,7 @@
         <v>2178</v>
       </c>
       <c r="G984" s="1" t="s">
-        <v>4484</v>
+        <v>4483</v>
       </c>
     </row>
     <row r="985" spans="1:8" x14ac:dyDescent="0.2">
@@ -32222,7 +32219,7 @@
         <v>366</v>
       </c>
       <c r="G986" s="1" t="s">
-        <v>4401</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.2">
@@ -32259,7 +32256,7 @@
         <v>2769</v>
       </c>
       <c r="G988" s="1" t="s">
-        <v>4409</v>
+        <v>4408</v>
       </c>
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.2">
@@ -32364,7 +32361,7 @@
         <v>2784</v>
       </c>
       <c r="G994" s="1" t="s">
-        <v>4487</v>
+        <v>4486</v>
       </c>
     </row>
     <row r="995" spans="1:8" x14ac:dyDescent="0.2">
@@ -32637,7 +32634,7 @@
         <v>2825</v>
       </c>
       <c r="G1009" s="1" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
     </row>
     <row r="1010" spans="1:7" x14ac:dyDescent="0.2">
@@ -32657,7 +32654,7 @@
         <v>2162</v>
       </c>
       <c r="G1010" s="1" t="s">
-        <v>4485</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="1011" spans="1:7" x14ac:dyDescent="0.2">
@@ -32677,7 +32674,7 @@
         <v>2830</v>
       </c>
       <c r="G1011" s="1" t="s">
-        <v>4486</v>
+        <v>4485</v>
       </c>
     </row>
     <row r="1012" spans="1:7" x14ac:dyDescent="0.2">
@@ -32697,7 +32694,7 @@
         <v>2834</v>
       </c>
       <c r="G1012" s="1" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="1013" spans="1:7" x14ac:dyDescent="0.2">
@@ -32842,7 +32839,7 @@
         <v>2853</v>
       </c>
       <c r="G1020" s="1" t="s">
-        <v>4499</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="1021" spans="1:7" x14ac:dyDescent="0.2">
@@ -32930,7 +32927,7 @@
         <v>2853</v>
       </c>
       <c r="G1025" s="1" t="s">
-        <v>4499</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="1026" spans="1:7" x14ac:dyDescent="0.2">
@@ -34064,7 +34061,7 @@
         <v>323</v>
       </c>
       <c r="E1091" s="1" t="s">
-        <v>4439</v>
+        <v>4438</v>
       </c>
       <c r="F1091" t="s">
         <v>3007</v>
@@ -34278,7 +34275,7 @@
         <v>3023</v>
       </c>
       <c r="B1105" t="s">
-        <v>4350</v>
+        <v>4349</v>
       </c>
       <c r="C1105" s="1" t="s">
         <v>3024</v>
@@ -34363,7 +34360,7 @@
         <v>3038</v>
       </c>
       <c r="B1110" t="s">
-        <v>4438</v>
+        <v>4437</v>
       </c>
       <c r="C1110" s="1" t="s">
         <v>64</v>
@@ -34378,7 +34375,7 @@
         <v>66</v>
       </c>
       <c r="G1110" s="28" t="s">
-        <v>4437</v>
+        <v>4436</v>
       </c>
     </row>
     <row r="1111" spans="1:7" x14ac:dyDescent="0.2">
@@ -34415,7 +34412,7 @@
         <v>132</v>
       </c>
       <c r="G1112" s="1" t="s">
-        <v>4418</v>
+        <v>4417</v>
       </c>
     </row>
     <row r="1113" spans="1:7" x14ac:dyDescent="0.2">
@@ -34486,7 +34483,7 @@
         <v>937</v>
       </c>
       <c r="G1116" s="1" t="s">
-        <v>4419</v>
+        <v>4418</v>
       </c>
     </row>
     <row r="1117" spans="1:7" x14ac:dyDescent="0.2">
@@ -34506,7 +34503,7 @@
         <v>3048</v>
       </c>
       <c r="G1117" s="1" t="s">
-        <v>4410</v>
+        <v>4409</v>
       </c>
     </row>
     <row r="1118" spans="1:7" x14ac:dyDescent="0.2">
@@ -34526,7 +34523,7 @@
         <v>1639</v>
       </c>
       <c r="G1118" s="1" t="s">
-        <v>4411</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="1119" spans="1:7" x14ac:dyDescent="0.2">
@@ -34546,7 +34543,7 @@
         <v>511</v>
       </c>
       <c r="G1119" s="1" t="s">
-        <v>4411</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="1120" spans="1:7" x14ac:dyDescent="0.2">
@@ -34583,7 +34580,7 @@
         <v>257</v>
       </c>
       <c r="G1121" s="1" t="s">
-        <v>4412</v>
+        <v>4411</v>
       </c>
     </row>
     <row r="1122" spans="1:7" x14ac:dyDescent="0.2">
@@ -34620,7 +34617,7 @@
         <v>271</v>
       </c>
       <c r="G1123" s="1" t="s">
-        <v>4414</v>
+        <v>4413</v>
       </c>
     </row>
     <row r="1124" spans="1:7" x14ac:dyDescent="0.2">
@@ -34674,7 +34671,7 @@
         <v>3061</v>
       </c>
       <c r="G1126" s="1" t="s">
-        <v>4413</v>
+        <v>4412</v>
       </c>
     </row>
     <row r="1127" spans="1:7" x14ac:dyDescent="0.2">
@@ -34694,7 +34691,7 @@
         <v>1462</v>
       </c>
       <c r="G1127" s="1" t="s">
-        <v>4415</v>
+        <v>4414</v>
       </c>
     </row>
     <row r="1128" spans="1:7" x14ac:dyDescent="0.2">
@@ -34714,7 +34711,7 @@
         <v>366</v>
       </c>
       <c r="G1128" s="1" t="s">
-        <v>4416</v>
+        <v>4415</v>
       </c>
     </row>
     <row r="1129" spans="1:7" x14ac:dyDescent="0.2">
@@ -34734,7 +34731,7 @@
         <v>139</v>
       </c>
       <c r="G1129" s="1" t="s">
-        <v>4417</v>
+        <v>4416</v>
       </c>
     </row>
     <row r="1130" spans="1:7" x14ac:dyDescent="0.2">
@@ -34771,7 +34768,7 @@
         <v>3048</v>
       </c>
       <c r="G1131" s="1" t="s">
-        <v>4420</v>
+        <v>4419</v>
       </c>
     </row>
     <row r="1132" spans="1:7" x14ac:dyDescent="0.2">
@@ -34791,7 +34788,7 @@
         <v>132</v>
       </c>
       <c r="G1132" s="1" t="s">
-        <v>4422</v>
+        <v>4421</v>
       </c>
     </row>
     <row r="1133" spans="1:7" x14ac:dyDescent="0.2">
@@ -34811,7 +34808,7 @@
         <v>2178</v>
       </c>
       <c r="G1133" s="1" t="s">
-        <v>4423</v>
+        <v>4422</v>
       </c>
     </row>
     <row r="1134" spans="1:7" x14ac:dyDescent="0.2">
@@ -34831,7 +34828,7 @@
         <v>271</v>
       </c>
       <c r="G1134" s="1" t="s">
-        <v>4414</v>
+        <v>4413</v>
       </c>
     </row>
     <row r="1135" spans="1:7" x14ac:dyDescent="0.2">
@@ -34868,7 +34865,7 @@
         <v>132</v>
       </c>
       <c r="G1136" s="1" t="s">
-        <v>4421</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="1137" spans="1:7" x14ac:dyDescent="0.2">
@@ -34888,7 +34885,7 @@
         <v>3077</v>
       </c>
       <c r="G1137" s="27" t="s">
-        <v>4424</v>
+        <v>4423</v>
       </c>
     </row>
     <row r="1138" spans="1:7" x14ac:dyDescent="0.2">
@@ -34908,7 +34905,7 @@
         <v>1462</v>
       </c>
       <c r="G1138" s="1" t="s">
-        <v>4415</v>
+        <v>4414</v>
       </c>
     </row>
     <row r="1139" spans="1:7" x14ac:dyDescent="0.2">
@@ -34928,7 +34925,7 @@
         <v>3081</v>
       </c>
       <c r="G1139" s="1" t="s">
-        <v>4425</v>
+        <v>4424</v>
       </c>
     </row>
     <row r="1140" spans="1:7" x14ac:dyDescent="0.2">
@@ -34948,7 +34945,7 @@
         <v>1596</v>
       </c>
       <c r="G1140" s="1" t="s">
-        <v>4427</v>
+        <v>4426</v>
       </c>
     </row>
     <row r="1141" spans="1:7" x14ac:dyDescent="0.2">
@@ -34968,7 +34965,7 @@
         <v>937</v>
       </c>
       <c r="G1141" s="1" t="s">
-        <v>4426</v>
+        <v>4425</v>
       </c>
     </row>
     <row r="1142" spans="1:7" x14ac:dyDescent="0.2">
@@ -34988,7 +34985,7 @@
         <v>1639</v>
       </c>
       <c r="G1142" s="1" t="s">
-        <v>4428</v>
+        <v>4427</v>
       </c>
     </row>
     <row r="1143" spans="1:7" x14ac:dyDescent="0.2">
@@ -35008,7 +35005,7 @@
         <v>3088</v>
       </c>
       <c r="G1143" s="1" t="s">
-        <v>4432</v>
+        <v>4431</v>
       </c>
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.2">
@@ -38495,7 +38492,7 @@
         <v>3503</v>
       </c>
       <c r="G1343" s="1" t="s">
-        <v>4446</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="1344" spans="1:7" x14ac:dyDescent="0.2">
@@ -38535,7 +38532,7 @@
         <v>366</v>
       </c>
       <c r="G1345" s="1" t="s">
-        <v>4456</v>
+        <v>4455</v>
       </c>
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.2">
@@ -38555,7 +38552,7 @@
         <v>3510</v>
       </c>
       <c r="G1346" s="1" t="s">
-        <v>4459</v>
+        <v>4458</v>
       </c>
     </row>
     <row r="1347" spans="1:7" x14ac:dyDescent="0.2">
@@ -38575,7 +38572,7 @@
         <v>3513</v>
       </c>
       <c r="G1347" s="1" t="s">
-        <v>4457</v>
+        <v>4456</v>
       </c>
     </row>
     <row r="1348" spans="1:7" x14ac:dyDescent="0.2">
@@ -38595,7 +38592,7 @@
         <v>3517</v>
       </c>
       <c r="G1348" s="1" t="s">
-        <v>4458</v>
+        <v>4457</v>
       </c>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.2">
@@ -38791,7 +38788,7 @@
         <v>3542</v>
       </c>
       <c r="G1359" s="1" t="s">
-        <v>4450</v>
+        <v>4449</v>
       </c>
     </row>
     <row r="1360" spans="1:7" x14ac:dyDescent="0.2">
@@ -38811,7 +38808,7 @@
         <v>366</v>
       </c>
       <c r="G1360" s="1" t="s">
-        <v>4440</v>
+        <v>4439</v>
       </c>
     </row>
     <row r="1361" spans="1:7" x14ac:dyDescent="0.2">
@@ -38831,7 +38828,7 @@
         <v>139</v>
       </c>
       <c r="G1361" s="1" t="s">
-        <v>4451</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="1362" spans="1:7" x14ac:dyDescent="0.2">
@@ -38845,15 +38842,15 @@
         <v>59</v>
       </c>
       <c r="E1362" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="F1362" t="s">
         <v>3546</v>
-      </c>
-      <c r="F1362" t="s">
-        <v>3547</v>
       </c>
     </row>
     <row r="1363" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1363" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="C1363" s="1" t="s">
         <v>364</v>
@@ -38868,32 +38865,32 @@
         <v>366</v>
       </c>
       <c r="G1363" s="1" t="s">
-        <v>4452</v>
+        <v>4451</v>
       </c>
     </row>
     <row r="1364" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1364" t="s">
+        <v>3548</v>
+      </c>
+      <c r="C1364" s="1" t="s">
         <v>3549</v>
-      </c>
-      <c r="C1364" s="1" t="s">
-        <v>3550</v>
       </c>
       <c r="D1364" t="s">
         <v>229</v>
       </c>
       <c r="E1364" s="1" t="s">
+        <v>3550</v>
+      </c>
+      <c r="F1364" t="s">
         <v>3551</v>
       </c>
-      <c r="F1364" t="s">
-        <v>3552</v>
-      </c>
       <c r="G1364" s="1" t="s">
-        <v>4453</v>
+        <v>4452</v>
       </c>
     </row>
     <row r="1365" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1365" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="C1365" s="1" t="s">
         <v>2747</v>
@@ -38902,21 +38899,21 @@
         <v>260</v>
       </c>
       <c r="E1365" s="1" t="s">
+        <v>3553</v>
+      </c>
+      <c r="F1365" t="s">
         <v>3554</v>
       </c>
-      <c r="F1365" t="s">
-        <v>3555</v>
-      </c>
       <c r="G1365" s="1" t="s">
-        <v>4454</v>
+        <v>4453</v>
       </c>
     </row>
     <row r="1366" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1366" t="s">
+        <v>3555</v>
+      </c>
+      <c r="C1366" s="1" t="s">
         <v>3556</v>
-      </c>
-      <c r="C1366" s="1" t="s">
-        <v>3557</v>
       </c>
       <c r="D1366" t="s">
         <v>653</v>
@@ -38925,18 +38922,18 @@
         <v>3509</v>
       </c>
       <c r="F1366" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="G1366" s="1" t="s">
-        <v>4455</v>
+        <v>4454</v>
       </c>
     </row>
     <row r="1367" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1367" t="s">
+        <v>3558</v>
+      </c>
+      <c r="B1367" t="s">
         <v>3559</v>
-      </c>
-      <c r="B1367" t="s">
-        <v>3560</v>
       </c>
       <c r="C1367" s="1" t="s">
         <v>1637</v>
@@ -38953,10 +38950,10 @@
     </row>
     <row r="1368" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1368" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="B1368" t="s">
-        <v>4398</v>
+        <v>4397</v>
       </c>
       <c r="C1368" s="1" t="s">
         <v>58</v>
@@ -38973,7 +38970,7 @@
     </row>
     <row r="1369" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1369" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="C1369" s="1" t="s">
         <v>1992</v>
@@ -38990,7 +38987,7 @@
     </row>
     <row r="1370" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1370" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="C1370" s="1" t="s">
         <v>2526</v>
@@ -39007,10 +39004,10 @@
     </row>
     <row r="1371" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1371" t="s">
+        <v>3563</v>
+      </c>
+      <c r="B1371" t="s">
         <v>3564</v>
-      </c>
-      <c r="B1371" t="s">
-        <v>3565</v>
       </c>
       <c r="C1371" s="1">
         <v>18</v>
@@ -39025,12 +39022,12 @@
         <v>220</v>
       </c>
       <c r="G1371" s="1" t="s">
-        <v>4447</v>
+        <v>4446</v>
       </c>
     </row>
     <row r="1372" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1372" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="C1372" s="1" t="s">
         <v>130</v>
@@ -39047,7 +39044,7 @@
     </row>
     <row r="1373" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1373" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="C1373" s="1">
         <v>37</v>
@@ -39064,7 +39061,7 @@
     </row>
     <row r="1374" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1374" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="C1374" s="1" t="s">
         <v>1633</v>
@@ -39079,32 +39076,32 @@
         <v>1634</v>
       </c>
       <c r="G1374" s="1" t="s">
-        <v>4448</v>
+        <v>4447</v>
       </c>
     </row>
     <row r="1375" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1375" t="s">
+        <v>3568</v>
+      </c>
+      <c r="C1375" s="1" t="s">
         <v>3569</v>
-      </c>
-      <c r="C1375" s="1" t="s">
-        <v>3570</v>
       </c>
       <c r="D1375" t="s">
         <v>471</v>
       </c>
       <c r="E1375" s="1" t="s">
+        <v>3570</v>
+      </c>
+      <c r="F1375" t="s">
         <v>3571</v>
       </c>
-      <c r="F1375" t="s">
-        <v>3572</v>
-      </c>
       <c r="G1375" s="1" t="s">
-        <v>4449</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="1376" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1376" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="C1376" s="1" t="s">
         <v>1495</v>
@@ -39119,12 +39116,12 @@
         <v>2162</v>
       </c>
       <c r="G1376" s="1" t="s">
-        <v>4440</v>
+        <v>4439</v>
       </c>
     </row>
     <row r="1377" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1377" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="C1377" s="1" t="s">
         <v>58</v>
@@ -39139,12 +39136,12 @@
         <v>287</v>
       </c>
       <c r="G1377" s="1" t="s">
-        <v>4441</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="1378" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1378" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="C1378" s="1" t="s">
         <v>657</v>
@@ -39161,7 +39158,7 @@
     </row>
     <row r="1379" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1379" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="C1379" s="1" t="s">
         <v>364</v>
@@ -39176,72 +39173,72 @@
         <v>366</v>
       </c>
       <c r="G1379" s="1" t="s">
-        <v>4442</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="1380" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1380" t="s">
+        <v>3576</v>
+      </c>
+      <c r="C1380" s="1" t="s">
         <v>3577</v>
-      </c>
-      <c r="C1380" s="1" t="s">
-        <v>3578</v>
       </c>
       <c r="D1380" t="s">
         <v>653</v>
       </c>
       <c r="E1380" s="1" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="F1380" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="G1380" s="1" t="s">
-        <v>4443</v>
+        <v>4442</v>
       </c>
     </row>
     <row r="1381" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1381" t="s">
+        <v>3579</v>
+      </c>
+      <c r="C1381" s="1" t="s">
         <v>3580</v>
       </c>
-      <c r="C1381" s="1" t="s">
+      <c r="D1381" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1381" s="1" t="s">
         <v>3581</v>
       </c>
-      <c r="D1381" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1381" s="1" t="s">
+      <c r="F1381" t="s">
         <v>3582</v>
       </c>
-      <c r="F1381" t="s">
-        <v>3583</v>
-      </c>
       <c r="G1381" s="1" t="s">
-        <v>4444</v>
+        <v>4443</v>
       </c>
     </row>
     <row r="1382" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1382" t="s">
+        <v>3583</v>
+      </c>
+      <c r="B1382" t="s">
         <v>3584</v>
       </c>
-      <c r="B1382" t="s">
+      <c r="C1382" s="1" t="s">
         <v>3585</v>
-      </c>
-      <c r="C1382" s="1" t="s">
-        <v>3586</v>
       </c>
       <c r="D1382" t="s">
         <v>72</v>
       </c>
       <c r="E1382" s="1" t="s">
+        <v>3586</v>
+      </c>
+      <c r="F1382" t="s">
         <v>3587</v>
-      </c>
-      <c r="F1382" t="s">
-        <v>3588</v>
       </c>
     </row>
     <row r="1383" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1383" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="C1383" s="1">
         <v>83</v>
@@ -39255,10 +39252,10 @@
     </row>
     <row r="1384" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1384" t="s">
+        <v>3589</v>
+      </c>
+      <c r="B1384" t="s">
         <v>3590</v>
-      </c>
-      <c r="B1384" t="s">
-        <v>3591</v>
       </c>
       <c r="C1384" s="1">
         <v>27</v>
@@ -39273,29 +39270,29 @@
         <v>486</v>
       </c>
       <c r="G1384" s="1" t="s">
-        <v>4460</v>
+        <v>4459</v>
       </c>
     </row>
     <row r="1385" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1385" t="s">
+        <v>3591</v>
+      </c>
+      <c r="C1385" s="1" t="s">
         <v>3592</v>
       </c>
-      <c r="C1385" s="1" t="s">
+      <c r="D1385" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1385" s="1" t="s">
         <v>3593</v>
       </c>
-      <c r="D1385" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1385" s="1" t="s">
+      <c r="F1385" t="s">
         <v>3594</v>
-      </c>
-      <c r="F1385" t="s">
-        <v>3595</v>
       </c>
     </row>
     <row r="1386" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1386" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="C1386" s="1" t="s">
         <v>2434</v>
@@ -39312,10 +39309,10 @@
     </row>
     <row r="1387" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1387" t="s">
+        <v>3596</v>
+      </c>
+      <c r="B1387" t="s">
         <v>3597</v>
-      </c>
-      <c r="B1387" t="s">
-        <v>3598</v>
       </c>
       <c r="C1387" s="1" t="s">
         <v>385</v>
@@ -39332,7 +39329,7 @@
     </row>
     <row r="1388" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1388" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="C1388" s="1">
         <v>19</v>
@@ -39349,81 +39346,81 @@
     </row>
     <row r="1389" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1389" t="s">
+        <v>3599</v>
+      </c>
+      <c r="C1389" s="1" t="s">
         <v>3600</v>
-      </c>
-      <c r="C1389" s="1" t="s">
-        <v>3601</v>
       </c>
       <c r="D1389" t="s">
         <v>72</v>
       </c>
       <c r="E1389" s="1" t="s">
+        <v>3601</v>
+      </c>
+      <c r="F1389" t="s">
         <v>3602</v>
-      </c>
-      <c r="F1389" t="s">
-        <v>3603</v>
       </c>
     </row>
     <row r="1390" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1390" t="s">
+        <v>3603</v>
+      </c>
+      <c r="C1390" s="1" t="s">
         <v>3604</v>
       </c>
-      <c r="C1390" s="1" t="s">
+      <c r="D1390" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1390" s="1" t="s">
         <v>3605</v>
       </c>
-      <c r="D1390" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1390" s="1" t="s">
+      <c r="F1390" t="s">
         <v>3606</v>
       </c>
-      <c r="F1390" t="s">
-        <v>3607</v>
-      </c>
       <c r="G1390" s="1" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="1391" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1391" t="s">
+        <v>3607</v>
+      </c>
+      <c r="C1391" s="1" t="s">
         <v>3608</v>
       </c>
-      <c r="C1391" s="1" t="s">
+      <c r="D1391" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1391" s="1" t="s">
         <v>3609</v>
       </c>
-      <c r="D1391" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1391" s="1" t="s">
+      <c r="F1391" t="s">
         <v>3610</v>
-      </c>
-      <c r="F1391" t="s">
-        <v>3611</v>
       </c>
     </row>
     <row r="1392" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1392" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="C1392" s="1" t="s">
+        <v>3604</v>
+      </c>
+      <c r="D1392" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1392" s="1" t="s">
         <v>3605</v>
       </c>
-      <c r="D1392" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1392" s="1" t="s">
+      <c r="F1392" t="s">
         <v>3606</v>
       </c>
-      <c r="F1392" t="s">
-        <v>3607</v>
-      </c>
       <c r="G1392" s="1" t="s">
-        <v>4462</v>
+        <v>4461</v>
       </c>
     </row>
     <row r="1393" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1393" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="C1393" s="1" t="s">
         <v>3092</v>
@@ -39440,7 +39437,7 @@
     </row>
     <row r="1394" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1394" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="C1394" s="1" t="s">
         <v>364</v>
@@ -39455,12 +39452,12 @@
         <v>366</v>
       </c>
       <c r="G1394" s="1" t="s">
-        <v>4463</v>
+        <v>4462</v>
       </c>
     </row>
     <row r="1395" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1395" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="C1395" s="1">
         <v>19</v>
@@ -39478,7 +39475,7 @@
     </row>
     <row r="1396" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1396" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="C1396" s="1" t="s">
         <v>385</v>
@@ -39493,12 +39490,12 @@
         <v>387</v>
       </c>
       <c r="G1396" s="1" t="s">
-        <v>4464</v>
+        <v>4463</v>
       </c>
     </row>
     <row r="1397" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1397" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="C1397" s="1">
         <v>27</v>
@@ -39515,27 +39512,27 @@
     </row>
     <row r="1398" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1398" t="s">
+        <v>3617</v>
+      </c>
+      <c r="C1398" s="1" t="s">
         <v>3618</v>
-      </c>
-      <c r="C1398" s="1" t="s">
-        <v>3619</v>
       </c>
       <c r="D1398" t="s">
         <v>35</v>
       </c>
       <c r="E1398" s="1" t="s">
-        <v>4399</v>
+        <v>4398</v>
       </c>
       <c r="F1398" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="1399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1399" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="B1399" t="s">
-        <v>4466</v>
+        <v>4465</v>
       </c>
       <c r="C1399" s="1">
         <v>11</v>
@@ -39550,12 +39547,12 @@
         <v>610</v>
       </c>
       <c r="G1399" s="1" t="s">
-        <v>4474</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="1400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1400" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="C1400" s="1" t="s">
         <v>364</v>
@@ -39570,32 +39567,32 @@
         <v>366</v>
       </c>
       <c r="G1400" s="1" t="s">
-        <v>4475</v>
+        <v>4474</v>
       </c>
     </row>
     <row r="1401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1401" t="s">
+        <v>3622</v>
+      </c>
+      <c r="C1401" s="1" t="s">
         <v>3623</v>
-      </c>
-      <c r="C1401" s="1" t="s">
-        <v>3624</v>
       </c>
       <c r="D1401" t="s">
         <v>653</v>
       </c>
       <c r="E1401" s="1" t="s">
+        <v>3624</v>
+      </c>
+      <c r="F1401" t="s">
         <v>3625</v>
       </c>
-      <c r="F1401" t="s">
-        <v>3626</v>
-      </c>
       <c r="G1401" s="1" t="s">
-        <v>4476</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="1402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1402" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="C1402" s="1">
         <v>19</v>
@@ -39610,12 +39607,12 @@
         <v>455</v>
       </c>
       <c r="G1402" s="1" t="s">
-        <v>4477</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="1403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1403" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="C1403" s="1" t="s">
         <v>364</v>
@@ -39630,12 +39627,12 @@
         <v>366</v>
       </c>
       <c r="G1403" s="1" t="s">
-        <v>4478</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="1404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1404" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="C1404" s="1">
         <v>37</v>
@@ -39650,12 +39647,12 @@
         <v>257</v>
       </c>
       <c r="G1404" s="1" t="s">
-        <v>4479</v>
+        <v>4478</v>
       </c>
     </row>
     <row r="1405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1405" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="C1405" s="1" t="s">
         <v>373</v>
@@ -39670,12 +39667,12 @@
         <v>592</v>
       </c>
       <c r="G1405" s="1" t="s">
-        <v>4480</v>
+        <v>4479</v>
       </c>
     </row>
     <row r="1406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1406" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="C1406" s="1" t="s">
         <v>385</v>
@@ -39690,15 +39687,15 @@
         <v>387</v>
       </c>
       <c r="G1406" s="1" t="s">
-        <v>4481</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="1407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1407" t="s">
+        <v>3631</v>
+      </c>
+      <c r="B1407" t="s">
         <v>3632</v>
-      </c>
-      <c r="B1407" t="s">
-        <v>3633</v>
       </c>
       <c r="C1407" s="1" t="s">
         <v>1595</v>
@@ -39715,7 +39712,7 @@
     </row>
     <row r="1408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1408" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="C1408" s="1" t="s">
         <v>130</v>
@@ -39732,7 +39729,7 @@
     </row>
     <row r="1409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1409" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="C1409" s="1" t="s">
         <v>2558</v>
@@ -39741,32 +39738,32 @@
         <v>159</v>
       </c>
       <c r="E1409" s="1" t="s">
+        <v>3635</v>
+      </c>
+      <c r="F1409" t="s">
         <v>3636</v>
-      </c>
-      <c r="F1409" t="s">
-        <v>3637</v>
       </c>
     </row>
     <row r="1410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1410" t="s">
+        <v>3637</v>
+      </c>
+      <c r="C1410" s="1" t="s">
         <v>3638</v>
-      </c>
-      <c r="C1410" s="1" t="s">
-        <v>3639</v>
       </c>
       <c r="D1410" t="s">
         <v>229</v>
       </c>
       <c r="E1410" s="1" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="F1410" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
     </row>
     <row r="1411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1411" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="C1411" s="1">
         <v>7</v>
@@ -39783,10 +39780,10 @@
     </row>
     <row r="1412" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1412" t="s">
+        <v>3641</v>
+      </c>
+      <c r="B1412" t="s">
         <v>3642</v>
-      </c>
-      <c r="B1412" t="s">
-        <v>3643</v>
       </c>
       <c r="C1412" s="1">
         <v>83</v>
@@ -39798,15 +39795,15 @@
         <v>632</v>
       </c>
       <c r="G1412" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="1413" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1413" t="s">
+        <v>3644</v>
+      </c>
+      <c r="B1413" t="s">
         <v>3645</v>
-      </c>
-      <c r="B1413" t="s">
-        <v>3646</v>
       </c>
       <c r="C1413" s="1" t="s">
         <v>3006</v>
@@ -39815,58 +39812,58 @@
         <v>323</v>
       </c>
       <c r="E1413" t="s">
-        <v>4439</v>
+        <v>4438</v>
       </c>
       <c r="F1413" t="s">
         <v>3007</v>
       </c>
       <c r="G1413" s="27" t="s">
-        <v>4432</v>
+        <v>4431</v>
       </c>
     </row>
     <row r="1414" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1414" t="s">
+        <v>3646</v>
+      </c>
+      <c r="C1414" s="1" t="s">
         <v>3647</v>
-      </c>
-      <c r="C1414" s="1" t="s">
-        <v>3648</v>
       </c>
       <c r="D1414" t="s">
         <v>323</v>
       </c>
       <c r="E1414" t="s">
+        <v>3648</v>
+      </c>
+      <c r="F1414" t="s">
         <v>3649</v>
       </c>
-      <c r="F1414" t="s">
-        <v>3650</v>
-      </c>
       <c r="G1414" t="s">
-        <v>4433</v>
+        <v>4432</v>
       </c>
     </row>
     <row r="1415" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1415" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="C1415" s="1" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
       <c r="D1415" t="s">
         <v>323</v>
       </c>
       <c r="E1415" t="s">
+        <v>3648</v>
+      </c>
+      <c r="F1415" t="s">
         <v>3649</v>
       </c>
-      <c r="F1415" t="s">
-        <v>3650</v>
-      </c>
       <c r="G1415" t="s">
-        <v>4434</v>
+        <v>4433</v>
       </c>
     </row>
     <row r="1416" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1416" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="C1416" s="1">
         <v>83</v>
@@ -39880,10 +39877,10 @@
     </row>
     <row r="1417" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1417" t="s">
+        <v>3652</v>
+      </c>
+      <c r="B1417" t="s">
         <v>3653</v>
-      </c>
-      <c r="B1417" t="s">
-        <v>3654</v>
       </c>
       <c r="C1417" s="1" t="s">
         <v>488</v>
@@ -39898,12 +39895,12 @@
         <v>2399</v>
       </c>
       <c r="G1417" s="1" t="s">
-        <v>4431</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="1418" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1418" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="C1418" s="1" t="s">
         <v>1443</v>
@@ -39920,7 +39917,7 @@
     </row>
     <row r="1419" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1419" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="C1419" s="1" t="s">
         <v>488</v>
@@ -39937,7 +39934,7 @@
     </row>
     <row r="1420" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1420" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="C1420" s="1" t="s">
         <v>1400</v>
@@ -39952,12 +39949,12 @@
         <v>1401</v>
       </c>
       <c r="G1420" s="1" t="s">
-        <v>4429</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="1421" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1421" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C1421" s="1" t="s">
         <v>2847</v>
@@ -39972,15 +39969,15 @@
         <v>2849</v>
       </c>
       <c r="G1421" s="1" t="s">
-        <v>4430</v>
+        <v>4429</v>
       </c>
     </row>
     <row r="1422" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1422" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1422" t="s">
         <v>3659</v>
-      </c>
-      <c r="B1422" t="s">
-        <v>3660</v>
       </c>
       <c r="C1422" s="1">
         <v>20</v>
@@ -39997,7 +39994,7 @@
     </row>
     <row r="1423" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1423" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="C1423" s="1">
         <v>18</v>
@@ -40014,7 +40011,7 @@
     </row>
     <row r="1424" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1424" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="C1424" s="1">
         <v>20</v>
@@ -40031,7 +40028,7 @@
     </row>
     <row r="1425" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1425" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="C1425" s="1">
         <v>18</v>
@@ -40048,24 +40045,24 @@
     </row>
     <row r="1426" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1426" t="s">
+        <v>3663</v>
+      </c>
+      <c r="C1426" s="1" t="s">
         <v>3664</v>
-      </c>
-      <c r="C1426" s="1" t="s">
-        <v>3665</v>
       </c>
       <c r="D1426" t="s">
         <v>72</v>
       </c>
       <c r="E1426" s="1" t="s">
+        <v>3665</v>
+      </c>
+      <c r="F1426" t="s">
         <v>3666</v>
-      </c>
-      <c r="F1426" t="s">
-        <v>3667</v>
       </c>
     </row>
     <row r="1427" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1427" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="C1427" s="1">
         <v>83</v>
@@ -40077,15 +40074,15 @@
         <v>632</v>
       </c>
       <c r="G1427" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
     </row>
     <row r="1428" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1428" t="s">
+        <v>3669</v>
+      </c>
+      <c r="B1428" t="s">
         <v>3670</v>
-      </c>
-      <c r="B1428" t="s">
-        <v>3671</v>
       </c>
       <c r="C1428" s="1" t="s">
         <v>1603</v>
@@ -40100,12 +40097,12 @@
         <v>1605</v>
       </c>
       <c r="G1428" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="1429" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1429" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="C1429" s="1">
         <v>97</v>
@@ -40122,7 +40119,7 @@
     </row>
     <row r="1430" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1430" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="C1430" s="1">
         <v>67</v>
@@ -40139,7 +40136,7 @@
     </row>
     <row r="1431" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1431" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="C1431" s="1" t="s">
         <v>1443</v>
@@ -40156,10 +40153,10 @@
     </row>
     <row r="1432" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1432" t="s">
+        <v>3675</v>
+      </c>
+      <c r="B1432" t="s">
         <v>3676</v>
-      </c>
-      <c r="B1432" t="s">
-        <v>3677</v>
       </c>
       <c r="C1432" s="1">
         <v>21</v>
@@ -40174,12 +40171,12 @@
         <v>452</v>
       </c>
       <c r="G1432" s="1" t="s">
-        <v>4468</v>
+        <v>4467</v>
       </c>
     </row>
     <row r="1433" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1433" t="s">
-        <v>3678</v>
+        <v>3677</v>
       </c>
       <c r="C1433" s="1" t="s">
         <v>152</v>
@@ -40194,12 +40191,12 @@
         <v>154</v>
       </c>
       <c r="G1433" s="1" t="s">
-        <v>4492</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="1434" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1434" t="s">
-        <v>3679</v>
+        <v>3678</v>
       </c>
       <c r="C1434" s="1">
         <v>21</v>
@@ -40214,32 +40211,32 @@
         <v>452</v>
       </c>
       <c r="G1434" s="1" t="s">
-        <v>4469</v>
+        <v>4468</v>
       </c>
     </row>
     <row r="1435" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1435" t="s">
+        <v>3679</v>
+      </c>
+      <c r="C1435" s="1" t="s">
         <v>3680</v>
-      </c>
-      <c r="C1435" s="1" t="s">
-        <v>3681</v>
       </c>
       <c r="D1435" t="s">
         <v>159</v>
       </c>
       <c r="E1435" s="1" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F1435" t="s">
         <v>3682</v>
       </c>
-      <c r="F1435" t="s">
-        <v>3683</v>
-      </c>
       <c r="G1435" s="1" t="s">
-        <v>4470</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="1436" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1436" t="s">
-        <v>3684</v>
+        <v>3683</v>
       </c>
       <c r="C1436" s="1" t="s">
         <v>2356</v>
@@ -40254,15 +40251,15 @@
         <v>2357</v>
       </c>
       <c r="G1436" s="1" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="1437" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1437" t="s">
+        <v>3684</v>
+      </c>
+      <c r="C1437" s="1" t="s">
         <v>3685</v>
-      </c>
-      <c r="C1437" s="1" t="s">
-        <v>3686</v>
       </c>
       <c r="D1437" t="s">
         <v>147</v>
@@ -40271,12 +40268,12 @@
         <v>1638</v>
       </c>
       <c r="F1437" t="s">
-        <v>3687</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="1438" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1438" t="s">
-        <v>3688</v>
+        <v>3687</v>
       </c>
       <c r="C1438" s="1">
         <v>83</v>
@@ -40290,10 +40287,10 @@
     </row>
     <row r="1439" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1439" t="s">
+        <v>3688</v>
+      </c>
+      <c r="B1439" t="s">
         <v>3689</v>
-      </c>
-      <c r="B1439" t="s">
-        <v>3690</v>
       </c>
       <c r="C1439" s="1" t="s">
         <v>1603</v>
@@ -40310,7 +40307,7 @@
     </row>
     <row r="1440" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1440" t="s">
-        <v>3691</v>
+        <v>3690</v>
       </c>
       <c r="C1440" s="1">
         <v>83</v>
@@ -40324,10 +40321,10 @@
     </row>
     <row r="1441" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1441" t="s">
+        <v>3691</v>
+      </c>
+      <c r="B1441" t="s">
         <v>3692</v>
-      </c>
-      <c r="B1441" t="s">
-        <v>3693</v>
       </c>
       <c r="C1441" s="1" t="s">
         <v>1495</v>
@@ -40342,12 +40339,12 @@
         <v>2162</v>
       </c>
       <c r="G1441" t="s">
-        <v>3697</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="1442" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1442" t="s">
-        <v>3694</v>
+        <v>3693</v>
       </c>
       <c r="C1442" s="1">
         <v>97</v>
@@ -40362,12 +40359,12 @@
         <v>506</v>
       </c>
       <c r="G1442" s="1" t="s">
-        <v>4408</v>
+        <v>4407</v>
       </c>
     </row>
     <row r="1443" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1443" t="s">
-        <v>3695</v>
+        <v>3694</v>
       </c>
       <c r="C1443" s="1">
         <v>67</v>
@@ -40384,7 +40381,7 @@
     </row>
     <row r="1444" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1444" t="s">
-        <v>3696</v>
+        <v>3695</v>
       </c>
       <c r="C1444" s="1" t="s">
         <v>137</v>
@@ -40401,7 +40398,7 @@
     </row>
     <row r="1445" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1445" t="s">
-        <v>3698</v>
+        <v>3697</v>
       </c>
       <c r="C1445" s="1" t="s">
         <v>999</v>
@@ -40418,7 +40415,7 @@
     </row>
     <row r="1446" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1446" t="s">
-        <v>3699</v>
+        <v>3698</v>
       </c>
       <c r="C1446" s="1">
         <v>67</v>
@@ -40435,7 +40432,7 @@
     </row>
     <row r="1447" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1447" t="s">
-        <v>3700</v>
+        <v>3699</v>
       </c>
       <c r="C1447" s="1" t="s">
         <v>935</v>
@@ -40452,24 +40449,24 @@
     </row>
     <row r="1448" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1448" t="s">
+        <v>3700</v>
+      </c>
+      <c r="C1448" s="1" t="s">
         <v>3701</v>
-      </c>
-      <c r="C1448" s="1" t="s">
-        <v>3702</v>
       </c>
       <c r="D1448" t="s">
         <v>72</v>
       </c>
       <c r="E1448" s="1" t="s">
+        <v>3702</v>
+      </c>
+      <c r="F1448" t="s">
         <v>3703</v>
-      </c>
-      <c r="F1448" t="s">
-        <v>3704</v>
       </c>
     </row>
     <row r="1449" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1449" t="s">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="C1449" s="1">
         <v>83</v>
@@ -40483,10 +40480,10 @@
     </row>
     <row r="1450" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1450" t="s">
+        <v>3705</v>
+      </c>
+      <c r="B1450" t="s">
         <v>3706</v>
-      </c>
-      <c r="B1450" t="s">
-        <v>3707</v>
       </c>
       <c r="C1450" s="1" t="s">
         <v>1199</v>
@@ -40501,12 +40498,12 @@
         <v>1201</v>
       </c>
       <c r="G1450" s="1" t="s">
-        <v>4445</v>
+        <v>4444</v>
       </c>
     </row>
     <row r="1451" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1451" t="s">
-        <v>3708</v>
+        <v>3707</v>
       </c>
       <c r="C1451" s="1" t="s">
         <v>1637</v>
@@ -40523,61 +40520,61 @@
     </row>
     <row r="1452" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1452" t="s">
+        <v>3708</v>
+      </c>
+      <c r="C1452" s="1" t="s">
         <v>3709</v>
-      </c>
-      <c r="C1452" s="1" t="s">
-        <v>3710</v>
       </c>
       <c r="D1452" t="s">
         <v>260</v>
       </c>
       <c r="E1452" s="1" t="s">
+        <v>3710</v>
+      </c>
+      <c r="F1452" t="s">
         <v>3711</v>
-      </c>
-      <c r="F1452" t="s">
-        <v>3712</v>
       </c>
     </row>
     <row r="1453" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1453" t="s">
+        <v>3712</v>
+      </c>
+      <c r="C1453" s="1" t="s">
         <v>3713</v>
-      </c>
-      <c r="C1453" s="1" t="s">
-        <v>3714</v>
       </c>
       <c r="D1453" t="s">
         <v>159</v>
       </c>
       <c r="E1453" s="1" t="s">
+        <v>3714</v>
+      </c>
+      <c r="F1453" t="s">
         <v>3715</v>
-      </c>
-      <c r="F1453" t="s">
-        <v>3716</v>
       </c>
     </row>
     <row r="1454" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1454" t="s">
+        <v>3716</v>
+      </c>
+      <c r="C1454" s="1" t="s">
         <v>3717</v>
       </c>
-      <c r="C1454" s="1" t="s">
+      <c r="D1454" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1454" s="1" t="s">
         <v>3718</v>
       </c>
-      <c r="D1454" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1454" s="1" t="s">
+      <c r="F1454" t="s">
         <v>3719</v>
-      </c>
-      <c r="F1454" t="s">
-        <v>3720</v>
       </c>
     </row>
     <row r="1455" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1455" t="s">
-        <v>3717</v>
+        <v>3716</v>
       </c>
       <c r="B1455" t="s">
-        <v>3721</v>
+        <v>3720</v>
       </c>
       <c r="C1455" s="1">
         <v>83</v>
@@ -40591,107 +40588,107 @@
     </row>
     <row r="1456" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1456" s="6" t="s">
+        <v>3721</v>
+      </c>
+      <c r="B1456" s="6" t="s">
         <v>3722</v>
       </c>
-      <c r="B1456" s="6" t="s">
+      <c r="C1456" s="7" t="s">
         <v>3723</v>
-      </c>
-      <c r="C1456" s="7" t="s">
-        <v>3724</v>
       </c>
       <c r="D1456" s="6" t="s">
         <v>211</v>
       </c>
       <c r="E1456" s="7" t="s">
+        <v>3724</v>
+      </c>
+      <c r="F1456" s="6" t="s">
         <v>3725</v>
       </c>
-      <c r="F1456" s="6" t="s">
+      <c r="G1456" s="6" t="s">
         <v>3726</v>
-      </c>
-      <c r="G1456" s="6" t="s">
-        <v>3727</v>
       </c>
     </row>
     <row r="1457" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1457" t="s">
+        <v>3727</v>
+      </c>
+      <c r="C1457" s="1" t="s">
         <v>3728</v>
-      </c>
-      <c r="C1457" s="1" t="s">
-        <v>3729</v>
       </c>
       <c r="D1457" t="s">
         <v>211</v>
       </c>
       <c r="E1457" s="1" t="s">
+        <v>3729</v>
+      </c>
+      <c r="F1457" t="s">
         <v>3730</v>
-      </c>
-      <c r="F1457" t="s">
-        <v>3731</v>
       </c>
     </row>
     <row r="1458" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1458" t="s">
+        <v>3731</v>
+      </c>
+      <c r="C1458" s="1" t="s">
         <v>3732</v>
-      </c>
-      <c r="C1458" s="1" t="s">
-        <v>3733</v>
       </c>
       <c r="D1458" t="s">
         <v>114</v>
       </c>
       <c r="E1458" s="1" t="s">
+        <v>3733</v>
+      </c>
+      <c r="F1458" t="s">
         <v>3734</v>
       </c>
-      <c r="F1458" t="s">
+      <c r="G1458" t="s">
         <v>3735</v>
-      </c>
-      <c r="G1458" t="s">
-        <v>3736</v>
       </c>
     </row>
     <row r="1459" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1459" t="s">
-        <v>3737</v>
+        <v>3736</v>
       </c>
       <c r="C1459" s="1" t="s">
-        <v>3724</v>
+        <v>3723</v>
       </c>
       <c r="D1459" t="s">
         <v>211</v>
       </c>
       <c r="E1459" s="1" t="s">
+        <v>3724</v>
+      </c>
+      <c r="F1459" t="s">
         <v>3725</v>
       </c>
-      <c r="F1459" t="s">
-        <v>3726</v>
-      </c>
       <c r="G1459" t="s">
-        <v>3738</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="1460" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1460" t="s">
+        <v>3738</v>
+      </c>
+      <c r="C1460" s="1" t="s">
         <v>3739</v>
-      </c>
-      <c r="C1460" s="1" t="s">
-        <v>3740</v>
       </c>
       <c r="D1460" t="s">
         <v>211</v>
       </c>
       <c r="E1460" s="1" t="s">
+        <v>3740</v>
+      </c>
+      <c r="F1460" t="s">
         <v>3741</v>
-      </c>
-      <c r="F1460" t="s">
-        <v>3742</v>
       </c>
     </row>
     <row r="1461" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1461" t="s">
+        <v>3742</v>
+      </c>
+      <c r="C1461" s="2" t="s">
         <v>3743</v>
-      </c>
-      <c r="C1461" s="2" t="s">
-        <v>3744</v>
       </c>
       <c r="D1461" t="s">
         <v>47</v>
@@ -40723,33 +40720,33 @@
   <sheetData>
     <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
+        <v>3744</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>3745</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="11" t="s">
         <v>3746</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="14" t="s">
+        <v>4356</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>3747</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>4357</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>3748</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="46" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
       <c r="B2" s="12">
         <v>0</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>4358</v>
+        <v>4357</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="E2" s="18">
         <v>38</v>
@@ -40764,38 +40761,38 @@
         <v>23</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>3752</v>
+        <v>3751</v>
       </c>
       <c r="B4" s="12">
         <v>2</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>4359</v>
+        <v>4358</v>
       </c>
       <c r="D4" s="15" t="s">
+        <v>3752</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>3753</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>3754</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>3755</v>
+        <v>3754</v>
       </c>
       <c r="B5" s="12">
         <v>3</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>3754</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>3755</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>3756</v>
       </c>
       <c r="E5" s="18">
         <v>0</v>
@@ -40807,21 +40804,21 @@
       </c>
       <c r="C6" s="9"/>
       <c r="E6" s="18" t="s">
-        <v>3757</v>
+        <v>3756</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>3758</v>
+        <v>3757</v>
       </c>
       <c r="B7" s="12">
         <v>5</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>4360</v>
+        <v>4359</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>3759</v>
+        <v>3758</v>
       </c>
       <c r="E7" s="18">
         <v>13</v>
@@ -40829,33 +40826,33 @@
     </row>
     <row r="8" spans="1:11" ht="46" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>3760</v>
+        <v>3759</v>
       </c>
       <c r="B8" s="12">
         <v>6</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>3759</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>3760</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="E8" s="18" t="s">
         <v>3761</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>3762</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="92" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>3763</v>
+        <v>3762</v>
       </c>
       <c r="B9" s="12">
         <v>7</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>4361</v>
+        <v>4360</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>1559</v>
@@ -40867,7 +40864,7 @@
       </c>
       <c r="C10" s="9"/>
       <c r="E10" s="18" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -40885,12 +40882,12 @@
       </c>
       <c r="C12" s="9"/>
       <c r="E12" s="18" t="s">
-        <v>3766</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="12" t="s">
-        <v>3767</v>
+        <v>3766</v>
       </c>
       <c r="C13" s="9"/>
       <c r="E13" s="18">
@@ -40903,12 +40900,12 @@
       </c>
       <c r="C14" s="9"/>
       <c r="E14" s="18" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="12" t="s">
-        <v>3769</v>
+        <v>3768</v>
       </c>
       <c r="C15" s="9"/>
       <c r="E15" s="18">
@@ -40917,16 +40914,16 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="12" t="s">
-        <v>3770</v>
+        <v>3769</v>
       </c>
       <c r="C16" s="9"/>
       <c r="E16" s="18" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="12" t="s">
-        <v>3771</v>
+        <v>3770</v>
       </c>
       <c r="C17" s="9"/>
       <c r="E17" s="18">
@@ -40939,10 +40936,10 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="15" t="s">
-        <v>3772</v>
+        <v>3771</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>3766</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
@@ -40969,7 +40966,7 @@
       </c>
       <c r="C21" s="9"/>
       <c r="E21" s="18" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
@@ -41028,7 +41025,7 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="12" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="C28" s="9"/>
       <c r="E28" s="18">
@@ -41037,7 +41034,7 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="12" t="s">
-        <v>3775</v>
+        <v>3774</v>
       </c>
       <c r="C29" s="9"/>
       <c r="E29" s="18">
@@ -41046,7 +41043,7 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="12" t="s">
-        <v>3776</v>
+        <v>3775</v>
       </c>
       <c r="C30" s="9"/>
       <c r="E30" s="18">
@@ -41055,7 +41052,7 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="12" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="C31" s="9"/>
       <c r="E31" s="18">
@@ -41064,7 +41061,7 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="12" t="s">
-        <v>3778</v>
+        <v>3777</v>
       </c>
       <c r="C32" s="9"/>
       <c r="E32" s="18">
@@ -41073,7 +41070,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="C33" s="9"/>
       <c r="E33" s="18">
@@ -41104,7 +41101,7 @@
       </c>
       <c r="C36" s="9"/>
       <c r="E36" s="18" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -41119,19 +41116,19 @@
     </row>
     <row r="38" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
       <c r="B38" s="12">
         <v>24</v>
       </c>
       <c r="C38" s="9" t="s">
+        <v>3779</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>3780</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="E38" s="18" t="s">
         <v>3781</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>3782</v>
       </c>
       <c r="K38" s="10"/>
     </row>
@@ -41187,33 +41184,33 @@
     </row>
     <row r="44" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="13" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="16" t="s">
+        <v>3783</v>
+      </c>
+      <c r="E44" s="18" t="s">
         <v>3784</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>3785</v>
       </c>
       <c r="L44" s="10"/>
     </row>
     <row r="45" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="13" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="16" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>3775</v>
+        <v>3774</v>
       </c>
       <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B46" s="12" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="C46" s="9"/>
       <c r="E46" s="18">
@@ -41223,7 +41220,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B47" s="12" t="s">
-        <v>3789</v>
+        <v>3788</v>
       </c>
       <c r="C47" s="9"/>
       <c r="E47" s="18">
@@ -41233,31 +41230,31 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
+        <v>3789</v>
+      </c>
+      <c r="B48" s="12" t="s">
         <v>3790</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="C48" s="9" t="s">
+        <v>4361</v>
+      </c>
+      <c r="E48" s="18" t="s">
         <v>3791</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>4362</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>3792</v>
       </c>
       <c r="K48" s="10"/>
     </row>
     <row r="49" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
+        <v>3792</v>
+      </c>
+      <c r="B49" s="12" t="s">
         <v>3793</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="C49" s="9" t="s">
+        <v>4362</v>
+      </c>
+      <c r="D49" s="15" t="s">
         <v>3794</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>4363</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>3795</v>
       </c>
       <c r="E49" s="18">
         <v>0</v>
@@ -41270,19 +41267,19 @@
       </c>
       <c r="C50" s="9"/>
       <c r="E50" s="18" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="K50" s="10"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="B51" s="12">
         <v>31</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="E51" s="18">
         <v>0</v>
@@ -41301,16 +41298,16 @@
     </row>
     <row r="53" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="B53" s="12">
         <v>33</v>
       </c>
       <c r="C53" s="9" t="s">
+        <v>3796</v>
+      </c>
+      <c r="D53" s="15" t="s">
         <v>3797</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>3798</v>
       </c>
       <c r="E53" s="18">
         <v>0</v>
@@ -41323,7 +41320,7 @@
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="15" t="s">
-        <v>4500</v>
+        <v>4499</v>
       </c>
       <c r="E54" s="18">
         <v>6</v>
@@ -41336,7 +41333,7 @@
       </c>
       <c r="C55" s="9"/>
       <c r="E55" s="18" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="K55" s="10"/>
     </row>
@@ -41346,7 +41343,7 @@
       </c>
       <c r="C56" s="9"/>
       <c r="E56" s="18" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="K56" s="10"/>
     </row>
@@ -41361,16 +41358,16 @@
     </row>
     <row r="58" spans="1:11" ht="46" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="B58" s="12">
         <v>38</v>
       </c>
       <c r="C58" s="9" t="s">
+        <v>3798</v>
+      </c>
+      <c r="D58" s="15" t="s">
         <v>3799</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>3800</v>
       </c>
       <c r="E58" s="18">
         <v>71</v>
@@ -41379,34 +41376,34 @@
     </row>
     <row r="59" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="B59" s="12">
         <v>39</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>4377</v>
+        <v>4376</v>
       </c>
       <c r="D59" s="15" t="s">
+        <v>3801</v>
+      </c>
+      <c r="E59" s="18" t="s">
         <v>3802</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>3803</v>
       </c>
       <c r="K59" s="10"/>
     </row>
     <row r="60" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
+        <v>3803</v>
+      </c>
+      <c r="B60" s="12" t="s">
         <v>3804</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="C60" s="9" t="s">
+        <v>4364</v>
+      </c>
+      <c r="D60" s="15" t="s">
         <v>3805</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>4365</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>3806</v>
       </c>
       <c r="E60" s="18">
         <v>0</v>
@@ -41415,13 +41412,13 @@
     </row>
     <row r="61" spans="1:11" ht="46" x14ac:dyDescent="0.3">
       <c r="B61" s="12" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
       <c r="C61" s="9" t="s">
+        <v>4378</v>
+      </c>
+      <c r="D61" s="15" t="s">
         <v>4379</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>4380</v>
       </c>
       <c r="E61" s="18">
         <v>77</v>
@@ -41429,16 +41426,16 @@
     </row>
     <row r="62" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
+        <v>3807</v>
+      </c>
+      <c r="B62" s="12" t="s">
         <v>3808</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="C62" s="9" t="s">
+        <v>4365</v>
+      </c>
+      <c r="D62" s="15" t="s">
         <v>3809</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>4366</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>3810</v>
       </c>
       <c r="E62" s="18">
         <v>77</v>
@@ -41447,7 +41444,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B63" s="12" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="C63" s="9"/>
       <c r="E63" s="18">
@@ -41456,13 +41453,13 @@
     </row>
     <row r="64" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="13" t="s">
+        <v>3811</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>4366</v>
+      </c>
+      <c r="D64" s="16" t="s">
         <v>3812</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>4367</v>
-      </c>
-      <c r="D64" s="16" t="s">
-        <v>3813</v>
       </c>
       <c r="E64" s="18">
         <v>77</v>
@@ -41470,7 +41467,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B65" s="12" t="s">
-        <v>3814</v>
+        <v>3813</v>
       </c>
       <c r="C65" s="9"/>
       <c r="E65" s="18">
@@ -41509,10 +41506,10 @@
         <v>43</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>4378</v>
+        <v>4377</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>4381</v>
+        <v>4380</v>
       </c>
       <c r="E69" s="18">
         <v>0</v>
@@ -41520,16 +41517,16 @@
     </row>
     <row r="70" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>3815</v>
+        <v>3814</v>
       </c>
       <c r="B70" s="12">
         <v>44</v>
       </c>
       <c r="C70" s="9" t="s">
+        <v>3814</v>
+      </c>
+      <c r="D70" s="15" t="s">
         <v>3815</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>3816</v>
       </c>
       <c r="E70" s="18">
         <v>0</v>
@@ -41537,16 +41534,16 @@
     </row>
     <row r="71" spans="1:11" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="B71" s="12">
         <v>45</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>4368</v>
+        <v>4367</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="E71" s="18">
         <v>0</v>
@@ -41554,16 +41551,16 @@
     </row>
     <row r="72" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="B72" s="12">
         <v>46</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>4369</v>
+        <v>4368</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="E72" s="18">
         <v>0</v>
@@ -41571,16 +41568,16 @@
     </row>
     <row r="73" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
-        <v>4385</v>
+        <v>4384</v>
       </c>
       <c r="B73" s="13">
         <v>47</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>4370</v>
+        <v>4369</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="E73" s="18">
         <v>0</v>
@@ -41589,16 +41586,16 @@
     </row>
     <row r="74" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
-        <v>4382</v>
+        <v>4381</v>
       </c>
       <c r="B74" s="13">
         <v>48</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>4371</v>
+        <v>4370</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="E74" s="18">
         <v>0</v>
@@ -41616,13 +41613,13 @@
     </row>
     <row r="76" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="13" t="s">
+        <v>3822</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>4371</v>
+      </c>
+      <c r="D76" s="16" t="s">
         <v>3823</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>4372</v>
-      </c>
-      <c r="D76" s="16" t="s">
-        <v>3824</v>
       </c>
       <c r="E76" s="18">
         <v>0</v>
@@ -41630,13 +41627,13 @@
     </row>
     <row r="77" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="13" t="s">
+        <v>3824</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>4372</v>
+      </c>
+      <c r="D77" s="16" t="s">
         <v>3825</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>4373</v>
-      </c>
-      <c r="D77" s="16" t="s">
-        <v>3826</v>
       </c>
       <c r="E77" s="18">
         <v>0</v>
@@ -41644,16 +41641,16 @@
     </row>
     <row r="78" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>4383</v>
+        <v>4382</v>
       </c>
       <c r="B78" s="13" t="s">
+        <v>3826</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>4373</v>
+      </c>
+      <c r="D78" s="16" t="s">
         <v>3827</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>4374</v>
-      </c>
-      <c r="D78" s="16" t="s">
-        <v>3828</v>
       </c>
       <c r="E78" s="18">
         <v>0</v>
@@ -41661,7 +41658,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B79" s="13" t="s">
-        <v>3829</v>
+        <v>3828</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="16"/>
@@ -41671,13 +41668,13 @@
     </row>
     <row r="80" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="13" t="s">
+        <v>3829</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>4374</v>
+      </c>
+      <c r="D80" s="16" t="s">
         <v>3830</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>4375</v>
-      </c>
-      <c r="D80" s="16" t="s">
-        <v>3831</v>
       </c>
       <c r="E80" s="18">
         <v>0</v>
@@ -41685,7 +41682,7 @@
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="13" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="16"/>
@@ -41698,10 +41695,10 @@
         <v>50</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>4376</v>
+        <v>4375</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
       <c r="E82" s="18">
         <v>0</v>
@@ -41799,7 +41796,7 @@
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92" s="13" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="16"/>
@@ -41809,7 +41806,7 @@
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" s="13" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="16"/>
@@ -41819,7 +41816,7 @@
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94" s="13" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="16"/>
@@ -41829,7 +41826,7 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" s="13" t="s">
-        <v>3837</v>
+        <v>3836</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="16"/>
@@ -41839,7 +41836,7 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" s="13" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="16"/>
@@ -41849,7 +41846,7 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97" s="13" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="16"/>
@@ -41953,7 +41950,7 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="16" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
       <c r="E107" s="18">
         <v>0</v>
@@ -41961,7 +41958,7 @@
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B108" s="13" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="C108" s="9"/>
       <c r="D108" s="16"/>
@@ -41971,11 +41968,11 @@
     </row>
     <row r="109" spans="2:5" ht="23" x14ac:dyDescent="0.3">
       <c r="B109" s="13" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="16" t="s">
-        <v>4393</v>
+        <v>4392</v>
       </c>
       <c r="E109" s="18">
         <v>0</v>
@@ -41983,7 +41980,7 @@
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B110" s="13" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
       <c r="C110" s="9"/>
       <c r="D110" s="16"/>
@@ -41993,7 +41990,7 @@
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B111" s="13" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="16"/>
@@ -42003,7 +42000,7 @@
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B112" s="13" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="C112" s="9"/>
       <c r="D112" s="16"/>
@@ -42013,7 +42010,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B113" s="13" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="16"/>
@@ -42067,7 +42064,7 @@
       </c>
       <c r="C118" s="9"/>
       <c r="D118" s="16" t="s">
-        <v>4435</v>
+        <v>4434</v>
       </c>
       <c r="E118" s="18">
         <v>0</v>
@@ -42079,7 +42076,7 @@
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="16" t="s">
-        <v>4435</v>
+        <v>4434</v>
       </c>
       <c r="E119" s="18">
         <v>0</v>
@@ -42091,7 +42088,7 @@
       </c>
       <c r="C120" s="9"/>
       <c r="D120" s="16" t="s">
-        <v>4435</v>
+        <v>4434</v>
       </c>
       <c r="E120" s="18">
         <v>0</v>
@@ -42103,7 +42100,7 @@
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="16" t="s">
-        <v>4435</v>
+        <v>4434</v>
       </c>
       <c r="E121" s="18">
         <v>0</v>
@@ -42115,7 +42112,7 @@
       </c>
       <c r="C122" s="9"/>
       <c r="D122" s="16" t="s">
-        <v>4435</v>
+        <v>4434</v>
       </c>
       <c r="E122" s="18">
         <v>0</v>
@@ -42127,7 +42124,7 @@
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="16" t="s">
-        <v>4435</v>
+        <v>4434</v>
       </c>
       <c r="E123" s="18">
         <v>0</v>
@@ -42135,16 +42132,16 @@
     </row>
     <row r="124" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="9" t="s">
-        <v>4384</v>
+        <v>4383</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>4436</v>
+        <v>4435</v>
       </c>
       <c r="E124" s="18">
         <v>0</v>
@@ -42152,11 +42149,11 @@
     </row>
     <row r="125" spans="1:5" ht="23" x14ac:dyDescent="0.3">
       <c r="B125" s="12" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="15" t="s">
-        <v>4467</v>
+        <v>4466</v>
       </c>
       <c r="E125" s="18">
         <v>0</v>
@@ -42164,7 +42161,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B126" s="12" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
       <c r="C126" s="9"/>
       <c r="E126" s="18">
@@ -42173,7 +42170,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B127" s="12" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="C127" s="9"/>
       <c r="E127" s="18">
@@ -42182,7 +42179,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B128" s="12" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="C128" s="9"/>
       <c r="E128" s="18">
@@ -42191,7 +42188,7 @@
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B129" s="12" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="E129" s="18" t="s">
         <v>1559</v>
@@ -42212,7 +42209,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="B1" t="s">
         <v>1769</v>
@@ -42220,7 +42217,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="B2" t="s">
         <v>1864</v>
@@ -42228,7 +42225,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="B3" t="s">
         <v>1864</v>
@@ -42236,7 +42233,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="B4" t="s">
         <v>1864</v>
@@ -42244,7 +42241,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="B5" t="s">
         <v>1832</v>
@@ -42252,7 +42249,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="B6" t="s">
         <v>1893</v>
@@ -42260,7 +42257,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="B7" t="s">
         <v>2008</v>
@@ -42268,7 +42265,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
       <c r="B8" t="s">
         <v>2031</v>
@@ -42290,2050 +42287,2050 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>3859</v>
+      </c>
+      <c r="B1" t="s">
         <v>3860</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3861</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>3861</v>
+      </c>
+      <c r="B2" t="s">
         <v>3862</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3863</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>3863</v>
+      </c>
+      <c r="B3" t="s">
         <v>3864</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3865</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>3865</v>
+      </c>
+      <c r="B4" t="s">
         <v>3866</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3867</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>3867</v>
+      </c>
+      <c r="B5" t="s">
         <v>3868</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3869</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>3869</v>
+      </c>
+      <c r="B6" t="s">
         <v>3870</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3871</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>3871</v>
+      </c>
+      <c r="B7" t="s">
         <v>3872</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3873</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>3873</v>
+      </c>
+      <c r="B8" t="s">
         <v>3874</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3875</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>3875</v>
+      </c>
+      <c r="B9" t="s">
         <v>3876</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3877</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>3877</v>
+      </c>
+      <c r="B10" t="s">
         <v>3878</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3879</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>3879</v>
+      </c>
+      <c r="B11" t="s">
         <v>3880</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3881</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="B12" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>3882</v>
+      </c>
+      <c r="B13" t="s">
         <v>3883</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3884</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>3884</v>
+      </c>
+      <c r="B14" t="s">
         <v>3885</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3886</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>3886</v>
+      </c>
+      <c r="B15" t="s">
         <v>3887</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3888</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>3888</v>
+      </c>
+      <c r="B16" t="s">
         <v>3889</v>
-      </c>
-      <c r="B16" t="s">
-        <v>3890</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>3890</v>
+      </c>
+      <c r="B17" t="s">
         <v>3891</v>
-      </c>
-      <c r="B17" t="s">
-        <v>3892</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>3892</v>
+      </c>
+      <c r="B18" t="s">
         <v>3893</v>
-      </c>
-      <c r="B18" t="s">
-        <v>3894</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>3894</v>
+      </c>
+      <c r="B19" t="s">
         <v>3895</v>
-      </c>
-      <c r="B19" t="s">
-        <v>3896</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>3896</v>
+      </c>
+      <c r="B20" t="s">
         <v>3897</v>
-      </c>
-      <c r="B20" t="s">
-        <v>3898</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>3898</v>
+      </c>
+      <c r="B21" t="s">
         <v>3899</v>
-      </c>
-      <c r="B21" t="s">
-        <v>3900</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>3900</v>
+      </c>
+      <c r="B22" t="s">
         <v>3901</v>
-      </c>
-      <c r="B22" t="s">
-        <v>3902</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>3902</v>
+      </c>
+      <c r="B23" t="s">
         <v>3903</v>
-      </c>
-      <c r="B23" t="s">
-        <v>3904</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>3904</v>
+      </c>
+      <c r="B24" t="s">
         <v>3905</v>
-      </c>
-      <c r="B24" t="s">
-        <v>3906</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>3906</v>
+      </c>
+      <c r="B25" t="s">
         <v>3907</v>
-      </c>
-      <c r="B25" t="s">
-        <v>3908</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>3908</v>
+      </c>
+      <c r="B26" t="s">
         <v>3909</v>
-      </c>
-      <c r="B26" t="s">
-        <v>3910</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>3910</v>
+      </c>
+      <c r="B27" t="s">
         <v>3911</v>
-      </c>
-      <c r="B27" t="s">
-        <v>3912</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>3912</v>
+      </c>
+      <c r="B28" t="s">
         <v>3913</v>
-      </c>
-      <c r="B28" t="s">
-        <v>3914</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>3914</v>
+      </c>
+      <c r="B29" t="s">
         <v>3915</v>
-      </c>
-      <c r="B29" t="s">
-        <v>3916</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>3916</v>
+      </c>
+      <c r="B30" t="s">
         <v>3917</v>
-      </c>
-      <c r="B30" t="s">
-        <v>3918</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>3918</v>
+      </c>
+      <c r="B31" t="s">
         <v>3919</v>
-      </c>
-      <c r="B31" t="s">
-        <v>3920</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>3920</v>
+      </c>
+      <c r="B32" t="s">
         <v>3921</v>
-      </c>
-      <c r="B32" t="s">
-        <v>3922</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>3922</v>
+      </c>
+      <c r="B33" t="s">
         <v>3923</v>
-      </c>
-      <c r="B33" t="s">
-        <v>3924</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>3924</v>
+      </c>
+      <c r="B34" t="s">
         <v>3925</v>
-      </c>
-      <c r="B34" t="s">
-        <v>3926</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>3927</v>
+        <v>3926</v>
       </c>
       <c r="B35" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>3927</v>
+      </c>
+      <c r="B36" t="s">
         <v>3928</v>
-      </c>
-      <c r="B36" t="s">
-        <v>3929</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>3929</v>
+      </c>
+      <c r="B37" t="s">
         <v>3930</v>
-      </c>
-      <c r="B37" t="s">
-        <v>3931</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>3931</v>
+      </c>
+      <c r="B38" t="s">
         <v>3932</v>
-      </c>
-      <c r="B38" t="s">
-        <v>3933</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>3933</v>
+      </c>
+      <c r="B39" t="s">
         <v>3934</v>
-      </c>
-      <c r="B39" t="s">
-        <v>3935</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>3935</v>
+      </c>
+      <c r="B40" t="s">
         <v>3936</v>
-      </c>
-      <c r="B40" t="s">
-        <v>3937</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>3937</v>
+      </c>
+      <c r="B41" t="s">
         <v>3938</v>
-      </c>
-      <c r="B41" t="s">
-        <v>3939</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>3939</v>
+      </c>
+      <c r="B42" t="s">
         <v>3940</v>
-      </c>
-      <c r="B42" t="s">
-        <v>3941</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>3941</v>
+      </c>
+      <c r="B43" t="s">
         <v>3942</v>
-      </c>
-      <c r="B43" t="s">
-        <v>3943</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>3943</v>
+      </c>
+      <c r="B44" t="s">
         <v>3944</v>
-      </c>
-      <c r="B44" t="s">
-        <v>3945</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>3945</v>
+      </c>
+      <c r="B45" t="s">
         <v>3946</v>
-      </c>
-      <c r="B45" t="s">
-        <v>3947</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>3947</v>
+      </c>
+      <c r="B46" t="s">
         <v>3948</v>
-      </c>
-      <c r="B46" t="s">
-        <v>3949</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>3949</v>
+      </c>
+      <c r="B47" t="s">
         <v>3950</v>
-      </c>
-      <c r="B47" t="s">
-        <v>3951</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>3951</v>
+      </c>
+      <c r="B48" t="s">
         <v>3952</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3953</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>3953</v>
+      </c>
+      <c r="B49" t="s">
         <v>3954</v>
-      </c>
-      <c r="B49" t="s">
-        <v>3955</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>3955</v>
+      </c>
+      <c r="B50" t="s">
         <v>3956</v>
-      </c>
-      <c r="B50" t="s">
-        <v>3957</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>3957</v>
+      </c>
+      <c r="B51" t="s">
         <v>3958</v>
-      </c>
-      <c r="B51" t="s">
-        <v>3959</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="B52" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>3960</v>
+      </c>
+      <c r="B53" t="s">
         <v>3961</v>
-      </c>
-      <c r="B53" t="s">
-        <v>3962</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="B54" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>3963</v>
+      </c>
+      <c r="B55" t="s">
         <v>3964</v>
-      </c>
-      <c r="B55" t="s">
-        <v>3965</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>3965</v>
+      </c>
+      <c r="B56" t="s">
         <v>3966</v>
-      </c>
-      <c r="B56" t="s">
-        <v>3967</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="B57" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="B58" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>3969</v>
+      </c>
+      <c r="B59" t="s">
         <v>3970</v>
-      </c>
-      <c r="B59" t="s">
-        <v>3971</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>3971</v>
+      </c>
+      <c r="B60" t="s">
         <v>3972</v>
-      </c>
-      <c r="B60" t="s">
-        <v>3973</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>3973</v>
+      </c>
+      <c r="B61" t="s">
         <v>3974</v>
-      </c>
-      <c r="B61" t="s">
-        <v>3975</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>3975</v>
+      </c>
+      <c r="B62" t="s">
         <v>3976</v>
-      </c>
-      <c r="B62" t="s">
-        <v>3977</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>3977</v>
+      </c>
+      <c r="B63" t="s">
         <v>3978</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3979</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>3979</v>
+      </c>
+      <c r="B64" t="s">
         <v>3980</v>
-      </c>
-      <c r="B64" t="s">
-        <v>3981</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>3981</v>
+      </c>
+      <c r="B65" t="s">
         <v>3982</v>
-      </c>
-      <c r="B65" t="s">
-        <v>3983</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>3983</v>
+      </c>
+      <c r="B66" t="s">
         <v>3984</v>
-      </c>
-      <c r="B66" t="s">
-        <v>3985</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
+        <v>3985</v>
+      </c>
+      <c r="B67" t="s">
         <v>3986</v>
-      </c>
-      <c r="B67" t="s">
-        <v>3987</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>3987</v>
+      </c>
+      <c r="B68" t="s">
         <v>3988</v>
-      </c>
-      <c r="B68" t="s">
-        <v>3989</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>3989</v>
+      </c>
+      <c r="B69" t="s">
         <v>3990</v>
-      </c>
-      <c r="B69" t="s">
-        <v>3991</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>3991</v>
+      </c>
+      <c r="B70" t="s">
         <v>3992</v>
-      </c>
-      <c r="B70" t="s">
-        <v>3993</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>3993</v>
+      </c>
+      <c r="B71" t="s">
         <v>3994</v>
-      </c>
-      <c r="B71" t="s">
-        <v>3995</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>3995</v>
+      </c>
+      <c r="B72" t="s">
         <v>3996</v>
-      </c>
-      <c r="B72" t="s">
-        <v>3997</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>3997</v>
+      </c>
+      <c r="B73" t="s">
         <v>3998</v>
-      </c>
-      <c r="B73" t="s">
-        <v>3999</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>3999</v>
+      </c>
+      <c r="B74" t="s">
         <v>4000</v>
-      </c>
-      <c r="B74" t="s">
-        <v>4001</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>4001</v>
+      </c>
+      <c r="B75" t="s">
         <v>4002</v>
-      </c>
-      <c r="B75" t="s">
-        <v>4003</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
+        <v>4003</v>
+      </c>
+      <c r="B76" t="s">
         <v>4004</v>
-      </c>
-      <c r="B76" t="s">
-        <v>4005</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
+        <v>4005</v>
+      </c>
+      <c r="B77" t="s">
         <v>4006</v>
-      </c>
-      <c r="B77" t="s">
-        <v>4007</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>4007</v>
+      </c>
+      <c r="B78" t="s">
         <v>4008</v>
-      </c>
-      <c r="B78" t="s">
-        <v>4009</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
+        <v>4009</v>
+      </c>
+      <c r="B79" t="s">
         <v>4010</v>
-      </c>
-      <c r="B79" t="s">
-        <v>4011</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>4011</v>
+      </c>
+      <c r="B80" t="s">
         <v>4012</v>
-      </c>
-      <c r="B80" t="s">
-        <v>4013</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
+        <v>4013</v>
+      </c>
+      <c r="B81" t="s">
         <v>4014</v>
-      </c>
-      <c r="B81" t="s">
-        <v>4015</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>4015</v>
+      </c>
+      <c r="B82" t="s">
         <v>4016</v>
-      </c>
-      <c r="B82" t="s">
-        <v>4017</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>4017</v>
+      </c>
+      <c r="B83" t="s">
         <v>4018</v>
-      </c>
-      <c r="B83" t="s">
-        <v>4019</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
+        <v>4019</v>
+      </c>
+      <c r="B84" t="s">
         <v>4020</v>
-      </c>
-      <c r="B84" t="s">
-        <v>4021</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
+        <v>4021</v>
+      </c>
+      <c r="B85" t="s">
         <v>4022</v>
-      </c>
-      <c r="B85" t="s">
-        <v>4023</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
+        <v>4023</v>
+      </c>
+      <c r="B86" t="s">
         <v>4024</v>
-      </c>
-      <c r="B86" t="s">
-        <v>4025</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>4025</v>
+      </c>
+      <c r="B87" t="s">
         <v>4026</v>
-      </c>
-      <c r="B87" t="s">
-        <v>4027</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
+        <v>4027</v>
+      </c>
+      <c r="B88" t="s">
         <v>4028</v>
-      </c>
-      <c r="B88" t="s">
-        <v>4029</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>4029</v>
+      </c>
+      <c r="B89" t="s">
         <v>4030</v>
-      </c>
-      <c r="B89" t="s">
-        <v>4031</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
+        <v>4031</v>
+      </c>
+      <c r="B90" t="s">
         <v>4032</v>
-      </c>
-      <c r="B90" t="s">
-        <v>4033</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>4033</v>
+      </c>
+      <c r="B91" t="s">
         <v>4034</v>
-      </c>
-      <c r="B91" t="s">
-        <v>4035</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>4035</v>
+      </c>
+      <c r="B92" t="s">
         <v>4036</v>
-      </c>
-      <c r="B92" t="s">
-        <v>4037</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
+        <v>4037</v>
+      </c>
+      <c r="B93" t="s">
         <v>4038</v>
-      </c>
-      <c r="B93" t="s">
-        <v>4039</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>4039</v>
+      </c>
+      <c r="B94" t="s">
         <v>4040</v>
-      </c>
-      <c r="B94" t="s">
-        <v>4041</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
+        <v>4041</v>
+      </c>
+      <c r="B95" t="s">
         <v>4042</v>
-      </c>
-      <c r="B95" t="s">
-        <v>4043</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>4043</v>
+      </c>
+      <c r="B96" t="s">
         <v>4044</v>
-      </c>
-      <c r="B96" t="s">
-        <v>4045</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B97" t="s">
         <v>4046</v>
-      </c>
-      <c r="B97" t="s">
-        <v>4047</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>4047</v>
+      </c>
+      <c r="B98" t="s">
         <v>4048</v>
-      </c>
-      <c r="B98" t="s">
-        <v>4049</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B99" t="s">
         <v>4050</v>
-      </c>
-      <c r="B99" t="s">
-        <v>4051</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>4052</v>
+        <v>4051</v>
       </c>
       <c r="B100" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>4052</v>
+      </c>
+      <c r="B101" t="s">
         <v>4053</v>
-      </c>
-      <c r="B101" t="s">
-        <v>4054</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>4054</v>
+      </c>
+      <c r="B102" t="s">
         <v>4055</v>
-      </c>
-      <c r="B102" t="s">
-        <v>4056</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>4057</v>
+        <v>4056</v>
       </c>
       <c r="B103" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
+        <v>4057</v>
+      </c>
+      <c r="B104" t="s">
         <v>4058</v>
-      </c>
-      <c r="B104" t="s">
-        <v>4059</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
+        <v>4059</v>
+      </c>
+      <c r="B105" t="s">
         <v>4060</v>
-      </c>
-      <c r="B105" t="s">
-        <v>4061</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
+        <v>4061</v>
+      </c>
+      <c r="B106" t="s">
         <v>4062</v>
-      </c>
-      <c r="B106" t="s">
-        <v>4063</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
+        <v>4063</v>
+      </c>
+      <c r="B107" t="s">
         <v>4064</v>
-      </c>
-      <c r="B107" t="s">
-        <v>4065</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
+        <v>4065</v>
+      </c>
+      <c r="B108" t="s">
         <v>4066</v>
-      </c>
-      <c r="B108" t="s">
-        <v>4067</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
+        <v>4067</v>
+      </c>
+      <c r="B109" t="s">
         <v>4068</v>
-      </c>
-      <c r="B109" t="s">
-        <v>4069</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
+        <v>4069</v>
+      </c>
+      <c r="B110" t="s">
         <v>4070</v>
-      </c>
-      <c r="B110" t="s">
-        <v>4071</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
+        <v>4071</v>
+      </c>
+      <c r="B111" t="s">
         <v>4072</v>
-      </c>
-      <c r="B111" t="s">
-        <v>4073</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
+        <v>4073</v>
+      </c>
+      <c r="B112" t="s">
         <v>4074</v>
-      </c>
-      <c r="B112" t="s">
-        <v>4075</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>4075</v>
+      </c>
+      <c r="B113" t="s">
         <v>4076</v>
-      </c>
-      <c r="B113" t="s">
-        <v>4077</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
+        <v>4077</v>
+      </c>
+      <c r="B114" t="s">
         <v>4078</v>
-      </c>
-      <c r="B114" t="s">
-        <v>4079</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
+        <v>4079</v>
+      </c>
+      <c r="B115" t="s">
         <v>4080</v>
-      </c>
-      <c r="B115" t="s">
-        <v>4081</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>4081</v>
+      </c>
+      <c r="B116" t="s">
         <v>4082</v>
-      </c>
-      <c r="B116" t="s">
-        <v>4083</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
+        <v>4083</v>
+      </c>
+      <c r="B117" t="s">
         <v>4084</v>
-      </c>
-      <c r="B117" t="s">
-        <v>4085</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
+        <v>4085</v>
+      </c>
+      <c r="B118" t="s">
         <v>4086</v>
-      </c>
-      <c r="B118" t="s">
-        <v>4087</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
+        <v>4087</v>
+      </c>
+      <c r="B119" t="s">
         <v>4088</v>
-      </c>
-      <c r="B119" t="s">
-        <v>4089</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
+        <v>4089</v>
+      </c>
+      <c r="B120" t="s">
         <v>4090</v>
-      </c>
-      <c r="B120" t="s">
-        <v>4091</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
+        <v>4091</v>
+      </c>
+      <c r="B121" t="s">
         <v>4092</v>
-      </c>
-      <c r="B121" t="s">
-        <v>4093</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
+        <v>4093</v>
+      </c>
+      <c r="B122" t="s">
         <v>4094</v>
-      </c>
-      <c r="B122" t="s">
-        <v>4095</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
+        <v>4095</v>
+      </c>
+      <c r="B123" t="s">
         <v>4096</v>
-      </c>
-      <c r="B123" t="s">
-        <v>4097</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
+        <v>4097</v>
+      </c>
+      <c r="B124" t="s">
         <v>4098</v>
-      </c>
-      <c r="B124" t="s">
-        <v>4099</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
+        <v>4099</v>
+      </c>
+      <c r="B125" t="s">
         <v>4100</v>
-      </c>
-      <c r="B125" t="s">
-        <v>4101</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
+        <v>4101</v>
+      </c>
+      <c r="B126" t="s">
         <v>4102</v>
-      </c>
-      <c r="B126" t="s">
-        <v>4103</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
+        <v>4103</v>
+      </c>
+      <c r="B127" t="s">
         <v>4104</v>
-      </c>
-      <c r="B127" t="s">
-        <v>4105</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>4105</v>
+      </c>
+      <c r="B128" t="s">
         <v>4106</v>
-      </c>
-      <c r="B128" t="s">
-        <v>4107</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
+        <v>4107</v>
+      </c>
+      <c r="B129" t="s">
         <v>4108</v>
-      </c>
-      <c r="B129" t="s">
-        <v>4109</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
+        <v>4109</v>
+      </c>
+      <c r="B130" t="s">
         <v>4110</v>
-      </c>
-      <c r="B130" t="s">
-        <v>4111</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="B131" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
+        <v>4112</v>
+      </c>
+      <c r="B132" t="s">
         <v>4113</v>
-      </c>
-      <c r="B132" t="s">
-        <v>4114</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
+        <v>4114</v>
+      </c>
+      <c r="B133" t="s">
         <v>4115</v>
-      </c>
-      <c r="B133" t="s">
-        <v>4116</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
+        <v>4116</v>
+      </c>
+      <c r="B134" t="s">
         <v>4117</v>
-      </c>
-      <c r="B134" t="s">
-        <v>4118</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
+        <v>4118</v>
+      </c>
+      <c r="B135" t="s">
         <v>4119</v>
-      </c>
-      <c r="B135" t="s">
-        <v>4120</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>4121</v>
+        <v>4120</v>
       </c>
       <c r="B136" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
+        <v>4121</v>
+      </c>
+      <c r="B137" t="s">
         <v>4122</v>
-      </c>
-      <c r="B137" t="s">
-        <v>4123</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
+        <v>4123</v>
+      </c>
+      <c r="B138" t="s">
         <v>4124</v>
-      </c>
-      <c r="B138" t="s">
-        <v>4125</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
+        <v>4125</v>
+      </c>
+      <c r="B139" t="s">
         <v>4126</v>
-      </c>
-      <c r="B139" t="s">
-        <v>4127</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>4128</v>
+        <v>4127</v>
       </c>
       <c r="B140" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
+        <v>4128</v>
+      </c>
+      <c r="B141" t="s">
         <v>4129</v>
-      </c>
-      <c r="B141" t="s">
-        <v>4130</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
+        <v>4130</v>
+      </c>
+      <c r="B142" t="s">
         <v>4131</v>
-      </c>
-      <c r="B142" t="s">
-        <v>4132</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
+        <v>4132</v>
+      </c>
+      <c r="B143" t="s">
         <v>4133</v>
-      </c>
-      <c r="B143" t="s">
-        <v>4134</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
+        <v>4134</v>
+      </c>
+      <c r="B144" t="s">
         <v>4135</v>
-      </c>
-      <c r="B144" t="s">
-        <v>4136</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
+        <v>4136</v>
+      </c>
+      <c r="B145" t="s">
         <v>4137</v>
-      </c>
-      <c r="B145" t="s">
-        <v>4138</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
+        <v>4138</v>
+      </c>
+      <c r="B146" t="s">
         <v>4139</v>
-      </c>
-      <c r="B146" t="s">
-        <v>4140</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
+        <v>4140</v>
+      </c>
+      <c r="B147" t="s">
         <v>4141</v>
-      </c>
-      <c r="B147" t="s">
-        <v>4142</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
+        <v>4142</v>
+      </c>
+      <c r="B148" t="s">
         <v>4143</v>
-      </c>
-      <c r="B148" t="s">
-        <v>4144</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
+        <v>4144</v>
+      </c>
+      <c r="B149" t="s">
         <v>4145</v>
-      </c>
-      <c r="B149" t="s">
-        <v>4146</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
+        <v>4146</v>
+      </c>
+      <c r="B150" t="s">
         <v>4147</v>
-      </c>
-      <c r="B150" t="s">
-        <v>4148</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
+        <v>4148</v>
+      </c>
+      <c r="B151" t="s">
         <v>4149</v>
-      </c>
-      <c r="B151" t="s">
-        <v>4150</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
+        <v>4150</v>
+      </c>
+      <c r="B152" t="s">
         <v>4151</v>
-      </c>
-      <c r="B152" t="s">
-        <v>4152</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
+        <v>4152</v>
+      </c>
+      <c r="B153" t="s">
         <v>4153</v>
-      </c>
-      <c r="B153" t="s">
-        <v>4154</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
+        <v>4154</v>
+      </c>
+      <c r="B154" t="s">
         <v>4155</v>
-      </c>
-      <c r="B154" t="s">
-        <v>4156</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
+        <v>4156</v>
+      </c>
+      <c r="B155" t="s">
         <v>4157</v>
-      </c>
-      <c r="B155" t="s">
-        <v>4158</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="B156" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
+        <v>4159</v>
+      </c>
+      <c r="B157" t="s">
         <v>4160</v>
-      </c>
-      <c r="B157" t="s">
-        <v>4161</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
+        <v>4161</v>
+      </c>
+      <c r="B158" t="s">
         <v>4162</v>
-      </c>
-      <c r="B158" t="s">
-        <v>4163</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
+        <v>4163</v>
+      </c>
+      <c r="B159" t="s">
         <v>4164</v>
-      </c>
-      <c r="B159" t="s">
-        <v>4165</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>4166</v>
+        <v>4165</v>
       </c>
       <c r="B160" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
+        <v>4166</v>
+      </c>
+      <c r="B161" t="s">
         <v>4167</v>
-      </c>
-      <c r="B161" t="s">
-        <v>4168</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
+        <v>4168</v>
+      </c>
+      <c r="B162" t="s">
         <v>4169</v>
-      </c>
-      <c r="B162" t="s">
-        <v>4170</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>4171</v>
+        <v>4170</v>
       </c>
       <c r="B163" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
+        <v>4171</v>
+      </c>
+      <c r="B164" t="s">
         <v>4172</v>
-      </c>
-      <c r="B164" t="s">
-        <v>4173</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
+        <v>4173</v>
+      </c>
+      <c r="B165" t="s">
         <v>4174</v>
-      </c>
-      <c r="B165" t="s">
-        <v>4175</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
+        <v>4175</v>
+      </c>
+      <c r="B166" t="s">
         <v>4176</v>
-      </c>
-      <c r="B166" t="s">
-        <v>4177</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>4178</v>
+        <v>4177</v>
       </c>
       <c r="B167" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
+        <v>4178</v>
+      </c>
+      <c r="B168" t="s">
         <v>4179</v>
-      </c>
-      <c r="B168" t="s">
-        <v>4180</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
+        <v>4180</v>
+      </c>
+      <c r="B169" t="s">
         <v>4181</v>
-      </c>
-      <c r="B169" t="s">
-        <v>4182</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
+        <v>4182</v>
+      </c>
+      <c r="B170" t="s">
         <v>4183</v>
-      </c>
-      <c r="B170" t="s">
-        <v>4184</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
+        <v>4184</v>
+      </c>
+      <c r="B171" t="s">
         <v>4185</v>
-      </c>
-      <c r="B171" t="s">
-        <v>4186</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
+        <v>4186</v>
+      </c>
+      <c r="B172" t="s">
         <v>4187</v>
-      </c>
-      <c r="B172" t="s">
-        <v>4188</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
+        <v>4188</v>
+      </c>
+      <c r="B173" t="s">
         <v>4189</v>
-      </c>
-      <c r="B173" t="s">
-        <v>4190</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
+        <v>4190</v>
+      </c>
+      <c r="B174" t="s">
         <v>4191</v>
-      </c>
-      <c r="B174" t="s">
-        <v>4192</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
+        <v>4192</v>
+      </c>
+      <c r="B175" t="s">
         <v>4193</v>
-      </c>
-      <c r="B175" t="s">
-        <v>4194</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
+        <v>4194</v>
+      </c>
+      <c r="B176" t="s">
         <v>4195</v>
-      </c>
-      <c r="B176" t="s">
-        <v>4196</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
+        <v>4196</v>
+      </c>
+      <c r="B177" t="s">
         <v>4197</v>
-      </c>
-      <c r="B177" t="s">
-        <v>4198</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
+        <v>4198</v>
+      </c>
+      <c r="B178" t="s">
         <v>4199</v>
-      </c>
-      <c r="B178" t="s">
-        <v>4200</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
+        <v>4200</v>
+      </c>
+      <c r="B179" t="s">
         <v>4201</v>
-      </c>
-      <c r="B179" t="s">
-        <v>4202</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
+        <v>4202</v>
+      </c>
+      <c r="B180" t="s">
         <v>4203</v>
-      </c>
-      <c r="B180" t="s">
-        <v>4204</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
+        <v>4204</v>
+      </c>
+      <c r="B181" t="s">
         <v>4205</v>
-      </c>
-      <c r="B181" t="s">
-        <v>4206</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
+        <v>4206</v>
+      </c>
+      <c r="B182" t="s">
         <v>4207</v>
-      </c>
-      <c r="B182" t="s">
-        <v>4208</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
+        <v>4208</v>
+      </c>
+      <c r="B183" t="s">
         <v>4209</v>
-      </c>
-      <c r="B183" t="s">
-        <v>4210</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>4211</v>
+        <v>4210</v>
       </c>
       <c r="B184" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
+        <v>4211</v>
+      </c>
+      <c r="B185" t="s">
         <v>4212</v>
-      </c>
-      <c r="B185" t="s">
-        <v>4213</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
+        <v>4213</v>
+      </c>
+      <c r="B186" t="s">
         <v>4214</v>
-      </c>
-      <c r="B186" t="s">
-        <v>4215</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
+        <v>4215</v>
+      </c>
+      <c r="B187" t="s">
         <v>4216</v>
-      </c>
-      <c r="B187" t="s">
-        <v>4217</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
+        <v>4217</v>
+      </c>
+      <c r="B188" t="s">
         <v>4218</v>
-      </c>
-      <c r="B188" t="s">
-        <v>4219</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
+        <v>4219</v>
+      </c>
+      <c r="B189" t="s">
         <v>4220</v>
-      </c>
-      <c r="B189" t="s">
-        <v>4221</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
+        <v>4221</v>
+      </c>
+      <c r="B190" t="s">
         <v>4222</v>
-      </c>
-      <c r="B190" t="s">
-        <v>4223</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
+        <v>4223</v>
+      </c>
+      <c r="B191" t="s">
         <v>4224</v>
-      </c>
-      <c r="B191" t="s">
-        <v>4225</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
+        <v>4225</v>
+      </c>
+      <c r="B192" t="s">
         <v>4226</v>
-      </c>
-      <c r="B192" t="s">
-        <v>4227</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>4228</v>
+        <v>4227</v>
       </c>
       <c r="B193" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
       <c r="B194" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
       <c r="B195" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
       <c r="B196" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
+        <v>4231</v>
+      </c>
+      <c r="B197" t="s">
         <v>4232</v>
-      </c>
-      <c r="B197" t="s">
-        <v>4233</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
+        <v>4233</v>
+      </c>
+      <c r="B198" t="s">
         <v>4234</v>
-      </c>
-      <c r="B198" t="s">
-        <v>4235</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
+        <v>4235</v>
+      </c>
+      <c r="B199" t="s">
         <v>4236</v>
-      </c>
-      <c r="B199" t="s">
-        <v>4237</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
+        <v>4237</v>
+      </c>
+      <c r="B200" t="s">
         <v>4238</v>
-      </c>
-      <c r="B200" t="s">
-        <v>4239</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
+        <v>4239</v>
+      </c>
+      <c r="B201" t="s">
         <v>4240</v>
-      </c>
-      <c r="B201" t="s">
-        <v>4241</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
+        <v>4241</v>
+      </c>
+      <c r="B202" t="s">
         <v>4242</v>
-      </c>
-      <c r="B202" t="s">
-        <v>4243</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
+        <v>4243</v>
+      </c>
+      <c r="B203" t="s">
         <v>4244</v>
-      </c>
-      <c r="B203" t="s">
-        <v>4245</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
+        <v>4245</v>
+      </c>
+      <c r="B204" t="s">
         <v>4246</v>
-      </c>
-      <c r="B204" t="s">
-        <v>4247</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
+        <v>4247</v>
+      </c>
+      <c r="B205" t="s">
         <v>4248</v>
-      </c>
-      <c r="B205" t="s">
-        <v>4249</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
+        <v>4249</v>
+      </c>
+      <c r="B206" t="s">
         <v>4250</v>
-      </c>
-      <c r="B206" t="s">
-        <v>4251</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
+        <v>4251</v>
+      </c>
+      <c r="B207" t="s">
         <v>4252</v>
-      </c>
-      <c r="B207" t="s">
-        <v>4253</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
+        <v>4253</v>
+      </c>
+      <c r="B208" t="s">
         <v>4254</v>
-      </c>
-      <c r="B208" t="s">
-        <v>4255</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
+        <v>4255</v>
+      </c>
+      <c r="B209" t="s">
         <v>4256</v>
-      </c>
-      <c r="B209" t="s">
-        <v>4257</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
+        <v>4257</v>
+      </c>
+      <c r="B210" t="s">
         <v>4258</v>
-      </c>
-      <c r="B210" t="s">
-        <v>4259</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
+        <v>4259</v>
+      </c>
+      <c r="B211" t="s">
         <v>4260</v>
-      </c>
-      <c r="B211" t="s">
-        <v>4261</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
+        <v>4261</v>
+      </c>
+      <c r="B212" t="s">
         <v>4262</v>
-      </c>
-      <c r="B212" t="s">
-        <v>4263</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
+        <v>4263</v>
+      </c>
+      <c r="B213" t="s">
         <v>4264</v>
-      </c>
-      <c r="B213" t="s">
-        <v>4265</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
+        <v>4265</v>
+      </c>
+      <c r="B214" t="s">
         <v>4266</v>
-      </c>
-      <c r="B214" t="s">
-        <v>4267</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>4268</v>
+        <v>4267</v>
       </c>
       <c r="B215" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
+        <v>4268</v>
+      </c>
+      <c r="B216" t="s">
         <v>4269</v>
-      </c>
-      <c r="B216" t="s">
-        <v>4270</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
+        <v>4270</v>
+      </c>
+      <c r="B217" t="s">
         <v>4271</v>
-      </c>
-      <c r="B217" t="s">
-        <v>4272</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
+        <v>4272</v>
+      </c>
+      <c r="B218" t="s">
         <v>4273</v>
-      </c>
-      <c r="B218" t="s">
-        <v>4274</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
+        <v>4274</v>
+      </c>
+      <c r="B219" t="s">
         <v>4275</v>
-      </c>
-      <c r="B219" t="s">
-        <v>4276</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
+        <v>4276</v>
+      </c>
+      <c r="B220" t="s">
         <v>4277</v>
-      </c>
-      <c r="B220" t="s">
-        <v>4278</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
+        <v>4278</v>
+      </c>
+      <c r="B221" t="s">
         <v>4279</v>
-      </c>
-      <c r="B221" t="s">
-        <v>4280</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
+        <v>4280</v>
+      </c>
+      <c r="B222" t="s">
         <v>4281</v>
-      </c>
-      <c r="B222" t="s">
-        <v>4282</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
+        <v>4282</v>
+      </c>
+      <c r="B223" t="s">
         <v>4283</v>
-      </c>
-      <c r="B223" t="s">
-        <v>4284</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
+        <v>4284</v>
+      </c>
+      <c r="B224" t="s">
         <v>4285</v>
-      </c>
-      <c r="B224" t="s">
-        <v>4286</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>4287</v>
+        <v>4286</v>
       </c>
       <c r="B225" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>4288</v>
+        <v>4287</v>
       </c>
       <c r="B226" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>4289</v>
+        <v>4288</v>
       </c>
       <c r="B227" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
+        <v>4289</v>
+      </c>
+      <c r="B228" t="s">
         <v>4290</v>
-      </c>
-      <c r="B228" t="s">
-        <v>4291</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
+        <v>4291</v>
+      </c>
+      <c r="B229" t="s">
         <v>4292</v>
-      </c>
-      <c r="B229" t="s">
-        <v>4293</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
+        <v>4293</v>
+      </c>
+      <c r="B230" t="s">
         <v>4294</v>
-      </c>
-      <c r="B230" t="s">
-        <v>4295</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
+        <v>4295</v>
+      </c>
+      <c r="B231" t="s">
         <v>4296</v>
-      </c>
-      <c r="B231" t="s">
-        <v>4297</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
+        <v>4297</v>
+      </c>
+      <c r="B232" t="s">
         <v>4298</v>
-      </c>
-      <c r="B232" t="s">
-        <v>4299</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
+        <v>4299</v>
+      </c>
+      <c r="B233" t="s">
         <v>4300</v>
-      </c>
-      <c r="B233" t="s">
-        <v>4301</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
+        <v>4301</v>
+      </c>
+      <c r="B234" t="s">
         <v>4302</v>
-      </c>
-      <c r="B234" t="s">
-        <v>4303</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
+        <v>4303</v>
+      </c>
+      <c r="B235" t="s">
         <v>4304</v>
-      </c>
-      <c r="B235" t="s">
-        <v>4305</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
+        <v>4305</v>
+      </c>
+      <c r="B236" t="s">
         <v>4306</v>
-      </c>
-      <c r="B236" t="s">
-        <v>4307</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
+        <v>4307</v>
+      </c>
+      <c r="B237" t="s">
         <v>4308</v>
-      </c>
-      <c r="B237" t="s">
-        <v>4309</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B238" t="s">
         <v>4310</v>
-      </c>
-      <c r="B238" t="s">
-        <v>4311</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
+        <v>4311</v>
+      </c>
+      <c r="B239" t="s">
         <v>4312</v>
-      </c>
-      <c r="B239" t="s">
-        <v>4313</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
+        <v>4313</v>
+      </c>
+      <c r="B240" t="s">
         <v>4314</v>
-      </c>
-      <c r="B240" t="s">
-        <v>4315</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
+        <v>4315</v>
+      </c>
+      <c r="B241" t="s">
         <v>4316</v>
-      </c>
-      <c r="B241" t="s">
-        <v>4317</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
+        <v>4317</v>
+      </c>
+      <c r="B242" t="s">
         <v>4318</v>
-      </c>
-      <c r="B242" t="s">
-        <v>4319</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
+        <v>4319</v>
+      </c>
+      <c r="B243" t="s">
         <v>4320</v>
-      </c>
-      <c r="B243" t="s">
-        <v>4321</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>4322</v>
+        <v>4321</v>
       </c>
       <c r="B244" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
+        <v>4322</v>
+      </c>
+      <c r="B245" t="s">
         <v>4323</v>
-      </c>
-      <c r="B245" t="s">
-        <v>4324</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
+        <v>4324</v>
+      </c>
+      <c r="B246" t="s">
         <v>4325</v>
-      </c>
-      <c r="B246" t="s">
-        <v>4326</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
+        <v>4326</v>
+      </c>
+      <c r="B247" t="s">
         <v>4327</v>
-      </c>
-      <c r="B247" t="s">
-        <v>4328</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
+        <v>4328</v>
+      </c>
+      <c r="B248" t="s">
         <v>4329</v>
-      </c>
-      <c r="B248" t="s">
-        <v>4330</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
+        <v>4330</v>
+      </c>
+      <c r="B249" t="s">
         <v>4331</v>
-      </c>
-      <c r="B249" t="s">
-        <v>4332</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
+        <v>4332</v>
+      </c>
+      <c r="B250" t="s">
         <v>4333</v>
-      </c>
-      <c r="B250" t="s">
-        <v>4334</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
+        <v>4334</v>
+      </c>
+      <c r="B251" t="s">
         <v>4335</v>
-      </c>
-      <c r="B251" t="s">
-        <v>4336</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
+        <v>4336</v>
+      </c>
+      <c r="B252" t="s">
         <v>4337</v>
-      </c>
-      <c r="B252" t="s">
-        <v>4338</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
+        <v>4338</v>
+      </c>
+      <c r="B253" t="s">
         <v>4339</v>
-      </c>
-      <c r="B253" t="s">
-        <v>4340</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
+        <v>4340</v>
+      </c>
+      <c r="B254" t="s">
         <v>4341</v>
-      </c>
-      <c r="B254" t="s">
-        <v>4342</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
+        <v>4342</v>
+      </c>
+      <c r="B255" t="s">
         <v>4343</v>
-      </c>
-      <c r="B255" t="s">
-        <v>4344</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
+        <v>4344</v>
+      </c>
+      <c r="B256" t="s">
         <v>4345</v>
-      </c>
-      <c r="B256" t="s">
-        <v>4346</v>
       </c>
     </row>
   </sheetData>

--- a/gemini8048/bin/87KLR951.xlsx
+++ b/gemini8048/bin/87KLR951.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mike/coding_projects/944/DME_sim/gemini8048/bin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC48498-4E86-3044-BF70-F15395387878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFB4227-23BE-7C4A-BA59-E60C47553AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7400" yWindow="15820" windowWidth="54880" windowHeight="24240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9540" yWindow="36300" windowWidth="54880" windowHeight="24240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASM" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8248" uniqueCount="4502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8250" uniqueCount="4504">
   <si>
     <t>https://junctionbyte.com/8051-microcontroller-special-function-registers/</t>
   </si>
@@ -13553,6 +13553,12 @@
   </si>
   <si>
     <t>// BCD code for TPS signal - increments to 4-2. Experimentally, this tends to occur for TPS value &gt; D8h</t>
+  </si>
+  <si>
+    <t>MAP sensor value raw + 10</t>
+  </si>
+  <si>
+    <t>MAP compare?</t>
   </si>
 </sst>
 </file>
@@ -41708,7 +41714,9 @@
       <c r="B83" s="13">
         <v>51</v>
       </c>
-      <c r="C83" s="9"/>
+      <c r="C83" s="9" t="s">
+        <v>4503</v>
+      </c>
       <c r="D83" s="16"/>
       <c r="E83" s="18">
         <v>0</v>
@@ -41718,7 +41726,9 @@
       <c r="B84" s="13">
         <v>52</v>
       </c>
-      <c r="C84" s="9"/>
+      <c r="C84" s="9" t="s">
+        <v>4502</v>
+      </c>
       <c r="D84" s="16"/>
       <c r="E84" s="18">
         <v>0</v>

--- a/gemini8048/bin/87KLR951.xlsx
+++ b/gemini8048/bin/87KLR951.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mike/coding_projects/944/DME_sim/gemini8048/bin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFB4227-23BE-7C4A-BA59-E60C47553AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A793498D-88E8-DC4E-98D5-05FE86057465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9540" yWindow="36300" windowWidth="54880" windowHeight="24240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12760" yWindow="1340" windowWidth="76800" windowHeight="40780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASM" sheetId="1" r:id="rId1"/>
     <sheet name="byte_mem" sheetId="2" r:id="rId2"/>
-    <sheet name="jump table 040d" sheetId="3" r:id="rId3"/>
-    <sheet name="8048opcodes" sheetId="4" r:id="rId4"/>
-    <sheet name="references" sheetId="5" r:id="rId5"/>
+    <sheet name="consrtants" sheetId="6" r:id="rId3"/>
+    <sheet name="jump table 040d" sheetId="3" r:id="rId4"/>
+    <sheet name="8048opcodes" sheetId="4" r:id="rId5"/>
+    <sheet name="references" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_87_g48asm2" localSheetId="0">ASM!$A$2:$G$1463</definedName>
     <definedName name="_87_g48asm2_3" localSheetId="0">ASM!$A$2:$G$1461</definedName>
     <definedName name="_87KLR_951_3" localSheetId="0">ASM!$C$2:$C$1462</definedName>
     <definedName name="_87KLR_951_3_3" localSheetId="0">ASM!$C$2:$C$1460</definedName>
-    <definedName name="codes" localSheetId="3">'8048opcodes'!$A$1:$A$256</definedName>
-    <definedName name="instr" localSheetId="3">'8048opcodes'!$B$1:$B$256</definedName>
+    <definedName name="codes" localSheetId="4">'8048opcodes'!$A$1:$A$256</definedName>
+    <definedName name="instr" localSheetId="4">'8048opcodes'!$B$1:$B$256</definedName>
     <definedName name="temp" localSheetId="0">ASM!$D$2:$E$1463</definedName>
     <definedName name="temp_1" localSheetId="0">ASM!$D$2:$E$1461</definedName>
   </definedNames>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8250" uniqueCount="4504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8327" uniqueCount="4587">
   <si>
     <t>https://junctionbyte.com/8051-microcontroller-special-function-registers/</t>
   </si>
@@ -11287,9 +11288,6 @@
     <t>hex addr</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>Value After Short Simulation</t>
   </si>
   <si>
@@ -11389,9 +11387,6 @@
     <t>eng_speed</t>
   </si>
   <si>
-    <t>// 24h - engine_speed???</t>
-  </si>
-  <si>
     <t>7f</t>
   </si>
   <si>
@@ -11431,18 +11426,12 @@
     <t>2f</t>
   </si>
   <si>
-    <t>// 2fh - raw knock sensor reading?</t>
-  </si>
-  <si>
     <t>knk_test</t>
   </si>
   <si>
     <t>blink</t>
   </si>
   <si>
-    <t>// 33h - blink code</t>
-  </si>
-  <si>
     <t>scratch</t>
   </si>
   <si>
@@ -11452,9 +11441,6 @@
     <t>TPS</t>
   </si>
   <si>
-    <t>// 39h - +V value read by the ADC</t>
-  </si>
-  <si>
     <t>c8</t>
   </si>
   <si>
@@ -11464,9 +11450,6 @@
     <t>3a</t>
   </si>
   <si>
-    <t>// 3ah - throttle position in degrees</t>
-  </si>
-  <si>
     <t>3b</t>
   </si>
   <si>
@@ -11476,9 +11459,6 @@
     <t>3c</t>
   </si>
   <si>
-    <t>// 3ch - raw throttle position sensor</t>
-  </si>
-  <si>
     <t>3d</t>
   </si>
   <si>
@@ -11494,9 +11474,6 @@
     <t>rpm_range</t>
   </si>
   <si>
-    <t>// 44h - RPM range. 64 means 0-1863 RPM, 0 means over 6386 RPM.</t>
-  </si>
-  <si>
     <t>max_knk</t>
   </si>
   <si>
@@ -13132,21 +13109,9 @@
     <t>timer_period</t>
   </si>
   <si>
-    <t>battery_volts</t>
-  </si>
-  <si>
-    <t>knock_raw</t>
-  </si>
-  <si>
     <t>knock_test_out</t>
   </si>
   <si>
-    <t>throttle_degrees</t>
-  </si>
-  <si>
-    <t>throttle_raw_sensor</t>
-  </si>
-  <si>
     <t>WOT_angle</t>
   </si>
   <si>
@@ -13177,21 +13142,12 @@
     <t>cycle_count_before_restore_boost</t>
   </si>
   <si>
-    <t>TPS Voltage</t>
-  </si>
-  <si>
-    <t>TPS_Cycling</t>
-  </si>
-  <si>
     <t>TPS_Scaling</t>
   </si>
   <si>
     <t>//3bh - The scaling numerator 3B is initialized to 119 in the trigger/reset routine. So the nominal scaling factor is 119/256, or about 0.46</t>
   </si>
   <si>
-    <t>//value ranging from 0-27, used for cycling value control map lookups</t>
-  </si>
-  <si>
     <t>throt_pos_thresh</t>
   </si>
   <si>
@@ -13555,10 +13511,304 @@
     <t>// BCD code for TPS signal - increments to 4-2. Experimentally, this tends to occur for TPS value &gt; D8h</t>
   </si>
   <si>
-    <t>MAP sensor value raw + 10</t>
-  </si>
-  <si>
     <t>MAP compare?</t>
+  </si>
+  <si>
+    <t>battery voltage</t>
+  </si>
+  <si>
+    <t>knock sensor (diagnostics)</t>
+  </si>
+  <si>
+    <t>throttle position (power supply)</t>
+  </si>
+  <si>
+    <t>throttle position (degrees)</t>
+  </si>
+  <si>
+    <t>throttle position (raw)</t>
+  </si>
+  <si>
+    <t>engine speed (in timer ticks)</t>
+  </si>
+  <si>
+    <t>MAP pressure</t>
+  </si>
+  <si>
+    <t>current blink code</t>
+  </si>
+  <si>
+    <t>angle to begin ADC initialization routine (in timer ticks)</t>
+  </si>
+  <si>
+    <t>angle to read ADC (after 22h, in timer ticks)</t>
+  </si>
+  <si>
+    <t>rpm range (map axis)</t>
+  </si>
+  <si>
+    <t>throttle position (map axis)</t>
+  </si>
+  <si>
+    <t>boost control PID error (target boost - actual boost)</t>
+  </si>
+  <si>
+    <t>boost control PID I term (integral)</t>
+  </si>
+  <si>
+    <t>boost control PID D term (derivative)</t>
+  </si>
+  <si>
+    <t>boost control feedforward value (CV duty cycle)</t>
+  </si>
+  <si>
+    <t>final CV duty cycle</t>
+  </si>
+  <si>
+    <t>total boost reduction for knock control</t>
+  </si>
+  <si>
+    <t>BATTERY_VOLTAGE</t>
+  </si>
+  <si>
+    <t>KNOCK_SENSOR_DIAG</t>
+  </si>
+  <si>
+    <t>TPS_POWER_SUPPLY</t>
+  </si>
+  <si>
+    <t>TPS_DEGREES</t>
+  </si>
+  <si>
+    <t>TPS_RAW</t>
+  </si>
+  <si>
+    <t>UNKNOWN_38</t>
+  </si>
+  <si>
+    <t>ENGINE_SPEED_TICKS</t>
+  </si>
+  <si>
+    <t>MAP_PRESSURE</t>
+  </si>
+  <si>
+    <t>BLINK_CODE_CURRENT</t>
+  </si>
+  <si>
+    <t>ADC_INIT_ANGLE</t>
+  </si>
+  <si>
+    <t>ADC_READ_ANGLE</t>
+  </si>
+  <si>
+    <t>RPM_MAP_AXIS</t>
+  </si>
+  <si>
+    <t>TPS_MAP_AXIS</t>
+  </si>
+  <si>
+    <t>BOOST_PID_ERROR</t>
+  </si>
+  <si>
+    <t>BOOST_PID_ITERM</t>
+  </si>
+  <si>
+    <t>BOOST_PID_DTERM</t>
+  </si>
+  <si>
+    <t>BOOST_FEEDFORWARD_CV</t>
+  </si>
+  <si>
+    <t>CV_DUTY_FINAL</t>
+  </si>
+  <si>
+    <t>BOOST_REDUCTION_KNOCK</t>
+  </si>
+  <si>
+    <t>CYL_TIMING_DELAY_C1</t>
+  </si>
+  <si>
+    <t>per-cylinder timing delay cylinder 1</t>
+  </si>
+  <si>
+    <t>CYL_TIMING_DELAY_C2</t>
+  </si>
+  <si>
+    <t>CYL_TIMING_DELAY_C3</t>
+  </si>
+  <si>
+    <t>CYL_TIMING_DELAY_C4</t>
+  </si>
+  <si>
+    <t>per-cylinder timing delay cylinder 2</t>
+  </si>
+  <si>
+    <t>per-cylinder timing delay cylinder 3</t>
+  </si>
+  <si>
+    <t>per-cylinder timing delay cylinder 4</t>
+  </si>
+  <si>
+    <t>CYL_KNOCK_THRESH_C1</t>
+  </si>
+  <si>
+    <t>per-cylinder knock threshold cyinder 1</t>
+  </si>
+  <si>
+    <t>CYL_KNOCK_THRESH_C2</t>
+  </si>
+  <si>
+    <t>CYL_KNOCK_THRESH_C3</t>
+  </si>
+  <si>
+    <t>CYL_KNOCK_THRESH_C4</t>
+  </si>
+  <si>
+    <t>per-cylinder knock threshold cyinder 2</t>
+  </si>
+  <si>
+    <t>per-cylinder knock threshold cyinder 3</t>
+  </si>
+  <si>
+    <t>per-cylinder knock threshold cyinder 4</t>
+  </si>
+  <si>
+    <t>BLINK_ERR_KNOCK_MAP</t>
+  </si>
+  <si>
+    <t>knock/MAP</t>
+  </si>
+  <si>
+    <t>BLINK_ERR_BOOST_HILO</t>
+  </si>
+  <si>
+    <t>boost high/low</t>
+  </si>
+  <si>
+    <t>BLINK_ERR_TPS</t>
+  </si>
+  <si>
+    <t>TPS/TPS power supply</t>
+  </si>
+  <si>
+    <t>KLR Memory Map — RPM Dependent Constants</t>
+  </si>
+  <si>
+    <t>These are loaded from a series of 2D maps (rpm only) located at 0x925.</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Variable Name</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>0x2A</t>
+  </si>
+  <si>
+    <t>RPM_K_ADC_START_ANGLE</t>
+  </si>
+  <si>
+    <t>for calculating the angle to start ADC stuff (22h)</t>
+  </si>
+  <si>
+    <t>0x2B</t>
+  </si>
+  <si>
+    <t>RPM_K_ADC_READ_ANGLE</t>
+  </si>
+  <si>
+    <t>for calculating the angle for ADC read (23h)</t>
+  </si>
+  <si>
+    <t>0x47</t>
+  </si>
+  <si>
+    <t>RPM_K_KNOCK_THRESH_COEF</t>
+  </si>
+  <si>
+    <t>coefficient for knock threshold (comparison with 46h)</t>
+  </si>
+  <si>
+    <t>0x4A</t>
+  </si>
+  <si>
+    <t>RPM_K_TIMING_RESTORE_CNT</t>
+  </si>
+  <si>
+    <t>cycle count before restoring 0.3 deg. timing (49h)</t>
+  </si>
+  <si>
+    <t>0x50</t>
+  </si>
+  <si>
+    <t>RPM_K_BOOST_RESTORE_CNT</t>
+  </si>
+  <si>
+    <t>cycle count before restoring boost (15 to 37)</t>
+  </si>
+  <si>
+    <t>0x4E</t>
+  </si>
+  <si>
+    <t>RPM_K_BOOST_PULL_CNT</t>
+  </si>
+  <si>
+    <t>cycle count before pulling boost (31 to 125)</t>
+  </si>
+  <si>
+    <t>0x4B</t>
+  </si>
+  <si>
+    <t>RPM_K_MAX_TIMING_RETARD</t>
+  </si>
+  <si>
+    <t>max timing retard (18 dec. for all rpm)</t>
+  </si>
+  <si>
+    <t>0x48</t>
+  </si>
+  <si>
+    <t>RPM_K_KNOCK_TPS_THRESH</t>
+  </si>
+  <si>
+    <t>throttle position threshhold for knock control</t>
+  </si>
+  <si>
+    <t>0x4C</t>
+  </si>
+  <si>
+    <t>RPM_K_BOOST_PULL_THRESH</t>
+  </si>
+  <si>
+    <t>0x3E</t>
+  </si>
+  <si>
+    <t>RPM_K_WOT_ANGLE</t>
+  </si>
+  <si>
+    <t>0x45</t>
+  </si>
+  <si>
+    <t>RPM_K_MIN_KNOCK_THRESH</t>
+  </si>
+  <si>
+    <t>minimum knock threshold value (10 for all rpm)</t>
+  </si>
+  <si>
+    <t>0x69</t>
+  </si>
+  <si>
+    <t>RPM_K_CNT_FOR_6A</t>
+  </si>
+  <si>
+    <t>counter for 6A (set to 4 for all rpm)</t>
+  </si>
+  <si>
+    <t>old var name</t>
   </si>
 </sst>
 </file>
@@ -13568,7 +13818,7 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -13640,8 +13890,28 @@
       <name val="Consolas"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -13654,8 +13924,14 @@
         <bgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7A1F1F"/>
+        <bgColor rgb="FF7A1F1F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -13663,12 +13939,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -13727,11 +14018,21 @@
     <xf numFmtId="6" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -15450,7 +15751,7 @@
         <v>310</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>4399</v>
+        <v>4384</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -18565,7 +18866,7 @@
         <v>809</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>4346</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.2">
@@ -18639,7 +18940,7 @@
         <v>820</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>4347</v>
+        <v>4339</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.2">
@@ -18699,7 +19000,7 @@
         <v>592</v>
       </c>
       <c r="G253" t="s">
-        <v>4348</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.2">
@@ -21554,14 +21855,14 @@
         <v>59</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>4396</v>
+        <v>4381</v>
       </c>
       <c r="F408" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">mov r2,#41 </v>
       </c>
       <c r="G408" t="s">
-        <v>4500</v>
+        <v>4485</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
@@ -21639,7 +21940,7 @@
         <v>inc r2</v>
       </c>
       <c r="G412" t="s">
-        <v>4501</v>
+        <v>4486</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
@@ -24326,7 +24627,7 @@
         <v>1730</v>
       </c>
       <c r="G558" t="s">
-        <v>4352</v>
+        <v>4344</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.2">
@@ -24346,7 +24647,7 @@
         <v>1734</v>
       </c>
       <c r="G559" s="1" t="s">
-        <v>4353</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.2">
@@ -24366,7 +24667,7 @@
         <v>1734</v>
       </c>
       <c r="G560" s="1" t="s">
-        <v>4353</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.2">
@@ -24386,7 +24687,7 @@
         <v>1734</v>
       </c>
       <c r="G561" s="1" t="s">
-        <v>4353</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.2">
@@ -24406,7 +24707,7 @@
         <v>1739</v>
       </c>
       <c r="G562" s="1" t="s">
-        <v>4354</v>
+        <v>4346</v>
       </c>
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.2">
@@ -24426,7 +24727,7 @@
         <v>1743</v>
       </c>
       <c r="G563" s="1" t="s">
-        <v>4350</v>
+        <v>4342</v>
       </c>
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.2">
@@ -24446,7 +24747,7 @@
         <v>1747</v>
       </c>
       <c r="G564" s="1" t="s">
-        <v>4351</v>
+        <v>4343</v>
       </c>
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.2">
@@ -24466,7 +24767,7 @@
         <v>1750</v>
       </c>
       <c r="G565" t="s">
-        <v>4355</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.2">
@@ -26220,7 +26521,7 @@
         <v>287</v>
       </c>
       <c r="G659" s="1" t="s">
-        <v>4497</v>
+        <v>4482</v>
       </c>
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.2">
@@ -26978,7 +27279,7 @@
       <c r="A701" t="s">
         <v>2139</v>
       </c>
-      <c r="B701" s="27" t="s">
+      <c r="B701" s="26" t="s">
         <v>93</v>
       </c>
       <c r="C701" s="1" t="s">
@@ -27207,10 +27508,10 @@
         <v>630</v>
       </c>
       <c r="G713" s="1" t="s">
-        <v>4389</v>
+        <v>4374</v>
       </c>
       <c r="H713" t="s">
-        <v>4390</v>
+        <v>4375</v>
       </c>
     </row>
     <row r="714" spans="1:8" x14ac:dyDescent="0.2">
@@ -27299,7 +27600,7 @@
         <v>149</v>
       </c>
       <c r="G718" s="1" t="s">
-        <v>4385</v>
+        <v>4370</v>
       </c>
     </row>
     <row r="719" spans="1:8" x14ac:dyDescent="0.2">
@@ -27319,7 +27620,7 @@
         <v>2178</v>
       </c>
       <c r="G719" s="1" t="s">
-        <v>4386</v>
+        <v>4371</v>
       </c>
     </row>
     <row r="720" spans="1:8" x14ac:dyDescent="0.2">
@@ -27339,7 +27640,7 @@
         <v>630</v>
       </c>
       <c r="G720" s="1" t="s">
-        <v>4387</v>
+        <v>4372</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.2">
@@ -27359,7 +27660,7 @@
         <v>387</v>
       </c>
       <c r="G721" s="1" t="s">
-        <v>4388</v>
+        <v>4373</v>
       </c>
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.2">
@@ -27487,7 +27788,7 @@
         <v>630</v>
       </c>
       <c r="G728" s="1" t="s">
-        <v>4391</v>
+        <v>4376</v>
       </c>
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.2">
@@ -29345,7 +29646,7 @@
         <v>2431</v>
       </c>
       <c r="G829" s="1" t="s">
-        <v>4393</v>
+        <v>4378</v>
       </c>
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.2">
@@ -29521,7 +29822,7 @@
         <v>323</v>
       </c>
       <c r="E839" s="1" t="s">
-        <v>4395</v>
+        <v>4380</v>
       </c>
       <c r="F839" t="s">
         <v>2457</v>
@@ -29694,7 +29995,7 @@
         <v>2478</v>
       </c>
       <c r="B849" t="s">
-        <v>4394</v>
+        <v>4379</v>
       </c>
       <c r="C849" s="1" t="s">
         <v>130</v>
@@ -31264,7 +31565,7 @@
         <v>2661</v>
       </c>
       <c r="G935" s="1" t="s">
-        <v>4487</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="936" spans="1:8" x14ac:dyDescent="0.2">
@@ -31301,7 +31602,7 @@
         <v>287</v>
       </c>
       <c r="G937" s="1" t="s">
-        <v>4488</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.2">
@@ -31324,7 +31625,7 @@
         <v>2668</v>
       </c>
       <c r="G938" t="s">
-        <v>4489</v>
+        <v>4474</v>
       </c>
     </row>
     <row r="939" spans="1:8" x14ac:dyDescent="0.2">
@@ -31395,7 +31696,7 @@
         <v>1462</v>
       </c>
       <c r="G942" s="1" t="s">
-        <v>4493</v>
+        <v>4478</v>
       </c>
     </row>
     <row r="943" spans="1:8" x14ac:dyDescent="0.2">
@@ -31415,7 +31716,7 @@
         <v>154</v>
       </c>
       <c r="G943" s="1" t="s">
-        <v>4490</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="944" spans="1:8" x14ac:dyDescent="0.2">
@@ -31435,7 +31736,7 @@
         <v>2680</v>
       </c>
       <c r="G944" s="1" t="s">
-        <v>4470</v>
+        <v>4455</v>
       </c>
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.2">
@@ -31455,7 +31756,7 @@
         <v>2680</v>
       </c>
       <c r="G945" s="1" t="s">
-        <v>4470</v>
+        <v>4455</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.2">
@@ -31475,7 +31776,7 @@
         <v>2685</v>
       </c>
       <c r="G946" s="1" t="s">
-        <v>4471</v>
+        <v>4456</v>
       </c>
     </row>
     <row r="947" spans="1:8" x14ac:dyDescent="0.2">
@@ -31495,7 +31796,7 @@
         <v>2685</v>
       </c>
       <c r="G947" s="1" t="s">
-        <v>4471</v>
+        <v>4456</v>
       </c>
     </row>
     <row r="948" spans="1:8" x14ac:dyDescent="0.2">
@@ -31555,7 +31856,7 @@
         <v>427</v>
       </c>
       <c r="G950" s="1" t="s">
-        <v>4401</v>
+        <v>4386</v>
       </c>
     </row>
     <row r="951" spans="1:8" x14ac:dyDescent="0.2">
@@ -31592,7 +31893,7 @@
         <v>366</v>
       </c>
       <c r="G952" s="1" t="s">
-        <v>4494</v>
+        <v>4479</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.2">
@@ -31629,7 +31930,7 @@
         <v>2357</v>
       </c>
       <c r="G954" s="1" t="s">
-        <v>4495</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="955" spans="1:8" x14ac:dyDescent="0.2">
@@ -31649,7 +31950,7 @@
         <v>2697</v>
       </c>
       <c r="G955" s="1" t="s">
-        <v>4496</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.2">
@@ -31669,7 +31970,7 @@
         <v>2701</v>
       </c>
       <c r="G956" t="s">
-        <v>4472</v>
+        <v>4457</v>
       </c>
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.2">
@@ -31828,7 +32129,7 @@
         <v>323</v>
       </c>
       <c r="E965" s="1" t="s">
-        <v>4464</v>
+        <v>4449</v>
       </c>
       <c r="F965" t="s">
         <v>2722</v>
@@ -32011,7 +32312,7 @@
         <v>2743</v>
       </c>
       <c r="G975" s="1" t="s">
-        <v>4402</v>
+        <v>4387</v>
       </c>
     </row>
     <row r="976" spans="1:8" x14ac:dyDescent="0.2">
@@ -32031,7 +32332,7 @@
         <v>659</v>
       </c>
       <c r="G976" t="s">
-        <v>4403</v>
+        <v>4388</v>
       </c>
     </row>
     <row r="977" spans="1:8" x14ac:dyDescent="0.2">
@@ -32088,7 +32389,7 @@
         <v>2752</v>
       </c>
       <c r="G979" s="1" t="s">
-        <v>4404</v>
+        <v>4389</v>
       </c>
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.2">
@@ -32108,7 +32409,7 @@
         <v>387</v>
       </c>
       <c r="G980" s="1" t="s">
-        <v>4405</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.2">
@@ -32131,7 +32432,7 @@
         <v>2758</v>
       </c>
       <c r="G981" t="s">
-        <v>4406</v>
+        <v>4391</v>
       </c>
       <c r="H981" t="s">
         <v>2759</v>
@@ -32188,7 +32489,7 @@
         <v>2178</v>
       </c>
       <c r="G984" s="1" t="s">
-        <v>4483</v>
+        <v>4468</v>
       </c>
     </row>
     <row r="985" spans="1:8" x14ac:dyDescent="0.2">
@@ -32225,7 +32526,7 @@
         <v>366</v>
       </c>
       <c r="G986" s="1" t="s">
-        <v>4400</v>
+        <v>4385</v>
       </c>
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.2">
@@ -32262,7 +32563,7 @@
         <v>2769</v>
       </c>
       <c r="G988" s="1" t="s">
-        <v>4408</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.2">
@@ -32367,7 +32668,7 @@
         <v>2784</v>
       </c>
       <c r="G994" s="1" t="s">
-        <v>4486</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="995" spans="1:8" x14ac:dyDescent="0.2">
@@ -32640,7 +32941,7 @@
         <v>2825</v>
       </c>
       <c r="G1009" s="1" t="s">
-        <v>4482</v>
+        <v>4467</v>
       </c>
     </row>
     <row r="1010" spans="1:7" x14ac:dyDescent="0.2">
@@ -32660,7 +32961,7 @@
         <v>2162</v>
       </c>
       <c r="G1010" s="1" t="s">
-        <v>4484</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="1011" spans="1:7" x14ac:dyDescent="0.2">
@@ -32680,7 +32981,7 @@
         <v>2830</v>
       </c>
       <c r="G1011" s="1" t="s">
-        <v>4485</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="1012" spans="1:7" x14ac:dyDescent="0.2">
@@ -32700,7 +33001,7 @@
         <v>2834</v>
       </c>
       <c r="G1012" s="1" t="s">
-        <v>4481</v>
+        <v>4466</v>
       </c>
     </row>
     <row r="1013" spans="1:7" x14ac:dyDescent="0.2">
@@ -32845,7 +33146,7 @@
         <v>2853</v>
       </c>
       <c r="G1020" s="1" t="s">
-        <v>4498</v>
+        <v>4483</v>
       </c>
     </row>
     <row r="1021" spans="1:7" x14ac:dyDescent="0.2">
@@ -32933,7 +33234,7 @@
         <v>2853</v>
       </c>
       <c r="G1025" s="1" t="s">
-        <v>4498</v>
+        <v>4483</v>
       </c>
     </row>
     <row r="1026" spans="1:7" x14ac:dyDescent="0.2">
@@ -34067,7 +34368,7 @@
         <v>323</v>
       </c>
       <c r="E1091" s="1" t="s">
-        <v>4438</v>
+        <v>4423</v>
       </c>
       <c r="F1091" t="s">
         <v>3007</v>
@@ -34281,7 +34582,7 @@
         <v>3023</v>
       </c>
       <c r="B1105" t="s">
-        <v>4349</v>
+        <v>4341</v>
       </c>
       <c r="C1105" s="1" t="s">
         <v>3024</v>
@@ -34366,7 +34667,7 @@
         <v>3038</v>
       </c>
       <c r="B1110" t="s">
-        <v>4437</v>
+        <v>4422</v>
       </c>
       <c r="C1110" s="1" t="s">
         <v>64</v>
@@ -34380,8 +34681,8 @@
       <c r="F1110" t="s">
         <v>66</v>
       </c>
-      <c r="G1110" s="28" t="s">
-        <v>4436</v>
+      <c r="G1110" s="27" t="s">
+        <v>4421</v>
       </c>
     </row>
     <row r="1111" spans="1:7" x14ac:dyDescent="0.2">
@@ -34418,7 +34719,7 @@
         <v>132</v>
       </c>
       <c r="G1112" s="1" t="s">
-        <v>4417</v>
+        <v>4402</v>
       </c>
     </row>
     <row r="1113" spans="1:7" x14ac:dyDescent="0.2">
@@ -34489,7 +34790,7 @@
         <v>937</v>
       </c>
       <c r="G1116" s="1" t="s">
-        <v>4418</v>
+        <v>4403</v>
       </c>
     </row>
     <row r="1117" spans="1:7" x14ac:dyDescent="0.2">
@@ -34509,7 +34810,7 @@
         <v>3048</v>
       </c>
       <c r="G1117" s="1" t="s">
-        <v>4409</v>
+        <v>4394</v>
       </c>
     </row>
     <row r="1118" spans="1:7" x14ac:dyDescent="0.2">
@@ -34529,7 +34830,7 @@
         <v>1639</v>
       </c>
       <c r="G1118" s="1" t="s">
-        <v>4410</v>
+        <v>4395</v>
       </c>
     </row>
     <row r="1119" spans="1:7" x14ac:dyDescent="0.2">
@@ -34549,7 +34850,7 @@
         <v>511</v>
       </c>
       <c r="G1119" s="1" t="s">
-        <v>4410</v>
+        <v>4395</v>
       </c>
     </row>
     <row r="1120" spans="1:7" x14ac:dyDescent="0.2">
@@ -34586,7 +34887,7 @@
         <v>257</v>
       </c>
       <c r="G1121" s="1" t="s">
-        <v>4411</v>
+        <v>4396</v>
       </c>
     </row>
     <row r="1122" spans="1:7" x14ac:dyDescent="0.2">
@@ -34623,7 +34924,7 @@
         <v>271</v>
       </c>
       <c r="G1123" s="1" t="s">
-        <v>4413</v>
+        <v>4398</v>
       </c>
     </row>
     <row r="1124" spans="1:7" x14ac:dyDescent="0.2">
@@ -34677,7 +34978,7 @@
         <v>3061</v>
       </c>
       <c r="G1126" s="1" t="s">
-        <v>4412</v>
+        <v>4397</v>
       </c>
     </row>
     <row r="1127" spans="1:7" x14ac:dyDescent="0.2">
@@ -34697,7 +34998,7 @@
         <v>1462</v>
       </c>
       <c r="G1127" s="1" t="s">
-        <v>4414</v>
+        <v>4399</v>
       </c>
     </row>
     <row r="1128" spans="1:7" x14ac:dyDescent="0.2">
@@ -34717,7 +35018,7 @@
         <v>366</v>
       </c>
       <c r="G1128" s="1" t="s">
-        <v>4415</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="1129" spans="1:7" x14ac:dyDescent="0.2">
@@ -34737,7 +35038,7 @@
         <v>139</v>
       </c>
       <c r="G1129" s="1" t="s">
-        <v>4416</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="1130" spans="1:7" x14ac:dyDescent="0.2">
@@ -34774,7 +35075,7 @@
         <v>3048</v>
       </c>
       <c r="G1131" s="1" t="s">
-        <v>4419</v>
+        <v>4404</v>
       </c>
     </row>
     <row r="1132" spans="1:7" x14ac:dyDescent="0.2">
@@ -34794,7 +35095,7 @@
         <v>132</v>
       </c>
       <c r="G1132" s="1" t="s">
-        <v>4421</v>
+        <v>4406</v>
       </c>
     </row>
     <row r="1133" spans="1:7" x14ac:dyDescent="0.2">
@@ -34814,7 +35115,7 @@
         <v>2178</v>
       </c>
       <c r="G1133" s="1" t="s">
-        <v>4422</v>
+        <v>4407</v>
       </c>
     </row>
     <row r="1134" spans="1:7" x14ac:dyDescent="0.2">
@@ -34834,7 +35135,7 @@
         <v>271</v>
       </c>
       <c r="G1134" s="1" t="s">
-        <v>4413</v>
+        <v>4398</v>
       </c>
     </row>
     <row r="1135" spans="1:7" x14ac:dyDescent="0.2">
@@ -34871,7 +35172,7 @@
         <v>132</v>
       </c>
       <c r="G1136" s="1" t="s">
-        <v>4420</v>
+        <v>4405</v>
       </c>
     </row>
     <row r="1137" spans="1:7" x14ac:dyDescent="0.2">
@@ -34890,8 +35191,8 @@
       <c r="F1137" t="s">
         <v>3077</v>
       </c>
-      <c r="G1137" s="27" t="s">
-        <v>4423</v>
+      <c r="G1137" s="26" t="s">
+        <v>4408</v>
       </c>
     </row>
     <row r="1138" spans="1:7" x14ac:dyDescent="0.2">
@@ -34911,7 +35212,7 @@
         <v>1462</v>
       </c>
       <c r="G1138" s="1" t="s">
-        <v>4414</v>
+        <v>4399</v>
       </c>
     </row>
     <row r="1139" spans="1:7" x14ac:dyDescent="0.2">
@@ -34931,7 +35232,7 @@
         <v>3081</v>
       </c>
       <c r="G1139" s="1" t="s">
-        <v>4424</v>
+        <v>4409</v>
       </c>
     </row>
     <row r="1140" spans="1:7" x14ac:dyDescent="0.2">
@@ -34951,7 +35252,7 @@
         <v>1596</v>
       </c>
       <c r="G1140" s="1" t="s">
-        <v>4426</v>
+        <v>4411</v>
       </c>
     </row>
     <row r="1141" spans="1:7" x14ac:dyDescent="0.2">
@@ -34971,7 +35272,7 @@
         <v>937</v>
       </c>
       <c r="G1141" s="1" t="s">
-        <v>4425</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="1142" spans="1:7" x14ac:dyDescent="0.2">
@@ -34991,7 +35292,7 @@
         <v>1639</v>
       </c>
       <c r="G1142" s="1" t="s">
-        <v>4427</v>
+        <v>4412</v>
       </c>
     </row>
     <row r="1143" spans="1:7" x14ac:dyDescent="0.2">
@@ -35011,7 +35312,7 @@
         <v>3088</v>
       </c>
       <c r="G1143" s="1" t="s">
-        <v>4431</v>
+        <v>4416</v>
       </c>
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.2">
@@ -38498,7 +38799,7 @@
         <v>3503</v>
       </c>
       <c r="G1343" s="1" t="s">
-        <v>4445</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="1344" spans="1:7" x14ac:dyDescent="0.2">
@@ -38538,7 +38839,7 @@
         <v>366</v>
       </c>
       <c r="G1345" s="1" t="s">
-        <v>4455</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.2">
@@ -38558,7 +38859,7 @@
         <v>3510</v>
       </c>
       <c r="G1346" s="1" t="s">
-        <v>4458</v>
+        <v>4443</v>
       </c>
     </row>
     <row r="1347" spans="1:7" x14ac:dyDescent="0.2">
@@ -38578,7 +38879,7 @@
         <v>3513</v>
       </c>
       <c r="G1347" s="1" t="s">
-        <v>4456</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="1348" spans="1:7" x14ac:dyDescent="0.2">
@@ -38598,7 +38899,7 @@
         <v>3517</v>
       </c>
       <c r="G1348" s="1" t="s">
-        <v>4457</v>
+        <v>4442</v>
       </c>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.2">
@@ -38794,7 +39095,7 @@
         <v>3542</v>
       </c>
       <c r="G1359" s="1" t="s">
-        <v>4449</v>
+        <v>4434</v>
       </c>
     </row>
     <row r="1360" spans="1:7" x14ac:dyDescent="0.2">
@@ -38814,7 +39115,7 @@
         <v>366</v>
       </c>
       <c r="G1360" s="1" t="s">
-        <v>4439</v>
+        <v>4424</v>
       </c>
     </row>
     <row r="1361" spans="1:7" x14ac:dyDescent="0.2">
@@ -38834,7 +39135,7 @@
         <v>139</v>
       </c>
       <c r="G1361" s="1" t="s">
-        <v>4450</v>
+        <v>4435</v>
       </c>
     </row>
     <row r="1362" spans="1:7" x14ac:dyDescent="0.2">
@@ -38871,7 +39172,7 @@
         <v>366</v>
       </c>
       <c r="G1363" s="1" t="s">
-        <v>4451</v>
+        <v>4436</v>
       </c>
     </row>
     <row r="1364" spans="1:7" x14ac:dyDescent="0.2">
@@ -38891,7 +39192,7 @@
         <v>3551</v>
       </c>
       <c r="G1364" s="1" t="s">
-        <v>4452</v>
+        <v>4437</v>
       </c>
     </row>
     <row r="1365" spans="1:7" x14ac:dyDescent="0.2">
@@ -38911,7 +39212,7 @@
         <v>3554</v>
       </c>
       <c r="G1365" s="1" t="s">
-        <v>4453</v>
+        <v>4438</v>
       </c>
     </row>
     <row r="1366" spans="1:7" x14ac:dyDescent="0.2">
@@ -38931,7 +39232,7 @@
         <v>3557</v>
       </c>
       <c r="G1366" s="1" t="s">
-        <v>4454</v>
+        <v>4439</v>
       </c>
     </row>
     <row r="1367" spans="1:7" x14ac:dyDescent="0.2">
@@ -38959,7 +39260,7 @@
         <v>3560</v>
       </c>
       <c r="B1368" t="s">
-        <v>4397</v>
+        <v>4382</v>
       </c>
       <c r="C1368" s="1" t="s">
         <v>58</v>
@@ -39028,7 +39329,7 @@
         <v>220</v>
       </c>
       <c r="G1371" s="1" t="s">
-        <v>4446</v>
+        <v>4431</v>
       </c>
     </row>
     <row r="1372" spans="1:7" x14ac:dyDescent="0.2">
@@ -39082,7 +39383,7 @@
         <v>1634</v>
       </c>
       <c r="G1374" s="1" t="s">
-        <v>4447</v>
+        <v>4432</v>
       </c>
     </row>
     <row r="1375" spans="1:7" x14ac:dyDescent="0.2">
@@ -39102,7 +39403,7 @@
         <v>3571</v>
       </c>
       <c r="G1375" s="1" t="s">
-        <v>4448</v>
+        <v>4433</v>
       </c>
     </row>
     <row r="1376" spans="1:7" x14ac:dyDescent="0.2">
@@ -39122,7 +39423,7 @@
         <v>2162</v>
       </c>
       <c r="G1376" s="1" t="s">
-        <v>4439</v>
+        <v>4424</v>
       </c>
     </row>
     <row r="1377" spans="1:7" x14ac:dyDescent="0.2">
@@ -39142,7 +39443,7 @@
         <v>287</v>
       </c>
       <c r="G1377" s="1" t="s">
-        <v>4440</v>
+        <v>4425</v>
       </c>
     </row>
     <row r="1378" spans="1:7" x14ac:dyDescent="0.2">
@@ -39179,7 +39480,7 @@
         <v>366</v>
       </c>
       <c r="G1379" s="1" t="s">
-        <v>4441</v>
+        <v>4426</v>
       </c>
     </row>
     <row r="1380" spans="1:7" x14ac:dyDescent="0.2">
@@ -39199,7 +39500,7 @@
         <v>3578</v>
       </c>
       <c r="G1380" s="1" t="s">
-        <v>4442</v>
+        <v>4427</v>
       </c>
     </row>
     <row r="1381" spans="1:7" x14ac:dyDescent="0.2">
@@ -39219,7 +39520,7 @@
         <v>3582</v>
       </c>
       <c r="G1381" s="1" t="s">
-        <v>4443</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="1382" spans="1:7" x14ac:dyDescent="0.2">
@@ -39276,7 +39577,7 @@
         <v>486</v>
       </c>
       <c r="G1384" s="1" t="s">
-        <v>4459</v>
+        <v>4444</v>
       </c>
     </row>
     <row r="1385" spans="1:7" x14ac:dyDescent="0.2">
@@ -39384,7 +39685,7 @@
         <v>3606</v>
       </c>
       <c r="G1390" s="1" t="s">
-        <v>4460</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="1391" spans="1:7" x14ac:dyDescent="0.2">
@@ -39421,7 +39722,7 @@
         <v>3606</v>
       </c>
       <c r="G1392" s="1" t="s">
-        <v>4461</v>
+        <v>4446</v>
       </c>
     </row>
     <row r="1393" spans="1:7" x14ac:dyDescent="0.2">
@@ -39458,7 +39759,7 @@
         <v>366</v>
       </c>
       <c r="G1394" s="1" t="s">
-        <v>4462</v>
+        <v>4447</v>
       </c>
     </row>
     <row r="1395" spans="1:7" x14ac:dyDescent="0.2">
@@ -39496,7 +39797,7 @@
         <v>387</v>
       </c>
       <c r="G1396" s="1" t="s">
-        <v>4463</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="1397" spans="1:7" x14ac:dyDescent="0.2">
@@ -39527,7 +39828,7 @@
         <v>35</v>
       </c>
       <c r="E1398" s="1" t="s">
-        <v>4398</v>
+        <v>4383</v>
       </c>
       <c r="F1398" t="s">
         <v>3619</v>
@@ -39538,7 +39839,7 @@
         <v>3620</v>
       </c>
       <c r="B1399" t="s">
-        <v>4465</v>
+        <v>4450</v>
       </c>
       <c r="C1399" s="1">
         <v>11</v>
@@ -39553,7 +39854,7 @@
         <v>610</v>
       </c>
       <c r="G1399" s="1" t="s">
-        <v>4473</v>
+        <v>4458</v>
       </c>
     </row>
     <row r="1400" spans="1:7" x14ac:dyDescent="0.2">
@@ -39573,7 +39874,7 @@
         <v>366</v>
       </c>
       <c r="G1400" s="1" t="s">
-        <v>4474</v>
+        <v>4459</v>
       </c>
     </row>
     <row r="1401" spans="1:7" x14ac:dyDescent="0.2">
@@ -39593,7 +39894,7 @@
         <v>3625</v>
       </c>
       <c r="G1401" s="1" t="s">
-        <v>4475</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="1402" spans="1:7" x14ac:dyDescent="0.2">
@@ -39613,7 +39914,7 @@
         <v>455</v>
       </c>
       <c r="G1402" s="1" t="s">
-        <v>4476</v>
+        <v>4461</v>
       </c>
     </row>
     <row r="1403" spans="1:7" x14ac:dyDescent="0.2">
@@ -39633,7 +39934,7 @@
         <v>366</v>
       </c>
       <c r="G1403" s="1" t="s">
-        <v>4477</v>
+        <v>4462</v>
       </c>
     </row>
     <row r="1404" spans="1:7" x14ac:dyDescent="0.2">
@@ -39653,7 +39954,7 @@
         <v>257</v>
       </c>
       <c r="G1404" s="1" t="s">
-        <v>4478</v>
+        <v>4463</v>
       </c>
     </row>
     <row r="1405" spans="1:7" x14ac:dyDescent="0.2">
@@ -39673,7 +39974,7 @@
         <v>592</v>
       </c>
       <c r="G1405" s="1" t="s">
-        <v>4479</v>
+        <v>4464</v>
       </c>
     </row>
     <row r="1406" spans="1:7" x14ac:dyDescent="0.2">
@@ -39693,7 +39994,7 @@
         <v>387</v>
       </c>
       <c r="G1406" s="1" t="s">
-        <v>4480</v>
+        <v>4465</v>
       </c>
     </row>
     <row r="1407" spans="1:7" x14ac:dyDescent="0.2">
@@ -39818,13 +40119,13 @@
         <v>323</v>
       </c>
       <c r="E1413" t="s">
-        <v>4438</v>
+        <v>4423</v>
       </c>
       <c r="F1413" t="s">
         <v>3007</v>
       </c>
-      <c r="G1413" s="27" t="s">
-        <v>4431</v>
+      <c r="G1413" s="26" t="s">
+        <v>4416</v>
       </c>
     </row>
     <row r="1414" spans="1:7" x14ac:dyDescent="0.2">
@@ -39844,7 +40145,7 @@
         <v>3649</v>
       </c>
       <c r="G1414" t="s">
-        <v>4432</v>
+        <v>4417</v>
       </c>
     </row>
     <row r="1415" spans="1:7" x14ac:dyDescent="0.2">
@@ -39864,7 +40165,7 @@
         <v>3649</v>
       </c>
       <c r="G1415" t="s">
-        <v>4433</v>
+        <v>4418</v>
       </c>
     </row>
     <row r="1416" spans="1:7" x14ac:dyDescent="0.2">
@@ -39901,7 +40202,7 @@
         <v>2399</v>
       </c>
       <c r="G1417" s="1" t="s">
-        <v>4430</v>
+        <v>4415</v>
       </c>
     </row>
     <row r="1418" spans="1:7" x14ac:dyDescent="0.2">
@@ -39955,7 +40256,7 @@
         <v>1401</v>
       </c>
       <c r="G1420" s="1" t="s">
-        <v>4428</v>
+        <v>4413</v>
       </c>
     </row>
     <row r="1421" spans="1:7" x14ac:dyDescent="0.2">
@@ -39975,7 +40276,7 @@
         <v>2849</v>
       </c>
       <c r="G1421" s="1" t="s">
-        <v>4429</v>
+        <v>4414</v>
       </c>
     </row>
     <row r="1422" spans="1:7" x14ac:dyDescent="0.2">
@@ -40177,7 +40478,7 @@
         <v>452</v>
       </c>
       <c r="G1432" s="1" t="s">
-        <v>4467</v>
+        <v>4452</v>
       </c>
     </row>
     <row r="1433" spans="1:7" x14ac:dyDescent="0.2">
@@ -40197,7 +40498,7 @@
         <v>154</v>
       </c>
       <c r="G1433" s="1" t="s">
-        <v>4491</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="1434" spans="1:7" x14ac:dyDescent="0.2">
@@ -40217,7 +40518,7 @@
         <v>452</v>
       </c>
       <c r="G1434" s="1" t="s">
-        <v>4468</v>
+        <v>4453</v>
       </c>
     </row>
     <row r="1435" spans="1:7" x14ac:dyDescent="0.2">
@@ -40237,7 +40538,7 @@
         <v>3682</v>
       </c>
       <c r="G1435" s="1" t="s">
-        <v>4469</v>
+        <v>4454</v>
       </c>
     </row>
     <row r="1436" spans="1:7" x14ac:dyDescent="0.2">
@@ -40257,7 +40558,7 @@
         <v>2357</v>
       </c>
       <c r="G1436" s="1" t="s">
-        <v>4492</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="1437" spans="1:7" x14ac:dyDescent="0.2">
@@ -40365,7 +40666,7 @@
         <v>506</v>
       </c>
       <c r="G1442" s="1" t="s">
-        <v>4407</v>
+        <v>4392</v>
       </c>
     </row>
     <row r="1443" spans="1:7" x14ac:dyDescent="0.2">
@@ -40504,7 +40805,7 @@
         <v>1201</v>
       </c>
       <c r="G1450" s="1" t="s">
-        <v>4444</v>
+        <v>4429</v>
       </c>
     </row>
     <row r="1451" spans="1:7" x14ac:dyDescent="0.2">
@@ -40720,39 +41021,41 @@
     <col min="2" max="3" width="37.83203125" style="12" customWidth="1"/>
     <col min="4" max="4" width="98.6640625" style="15" customWidth="1"/>
     <col min="5" max="5" width="39.33203125" style="17" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="9" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="9"/>
+    <col min="6" max="6" width="7.33203125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="33.6640625" style="9" customWidth="1"/>
+    <col min="8" max="8" width="87.83203125" style="9" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>3744</v>
+        <v>4586</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>3745</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="8" t="s">
+        <v>3744</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>4348</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>3746</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>4356</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>3747</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="46" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>3748</v>
+        <v>3747</v>
       </c>
       <c r="B2" s="12">
         <v>0</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>4357</v>
+        <v>4349</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
       <c r="E2" s="18">
         <v>38</v>
@@ -40767,38 +41070,38 @@
         <v>23</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
       <c r="B4" s="12">
         <v>2</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>4358</v>
+        <v>4350</v>
       </c>
       <c r="D4" s="15" t="s">
+        <v>3751</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>3752</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>3753</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>3754</v>
+        <v>3753</v>
       </c>
       <c r="B5" s="12">
         <v>3</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>3753</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>3754</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>3755</v>
       </c>
       <c r="E5" s="18">
         <v>0</v>
@@ -40810,21 +41113,21 @@
       </c>
       <c r="C6" s="9"/>
       <c r="E6" s="18" t="s">
-        <v>3756</v>
+        <v>3755</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>3757</v>
+        <v>3756</v>
       </c>
       <c r="B7" s="12">
         <v>5</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>4359</v>
+        <v>4351</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>3758</v>
+        <v>3757</v>
       </c>
       <c r="E7" s="18">
         <v>13</v>
@@ -40832,33 +41135,33 @@
     </row>
     <row r="8" spans="1:11" ht="46" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>3759</v>
+        <v>3758</v>
       </c>
       <c r="B8" s="12">
         <v>6</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>3758</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>3759</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="E8" s="18" t="s">
         <v>3760</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>3761</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="92" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
       <c r="B9" s="12">
         <v>7</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>4360</v>
+        <v>4352</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>3763</v>
+        <v>3762</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>1559</v>
@@ -40870,7 +41173,7 @@
       </c>
       <c r="C10" s="9"/>
       <c r="E10" s="18" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -40888,12 +41191,12 @@
       </c>
       <c r="C12" s="9"/>
       <c r="E12" s="18" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="12" t="s">
-        <v>3766</v>
+        <v>3765</v>
       </c>
       <c r="C13" s="9"/>
       <c r="E13" s="18">
@@ -40906,12 +41209,12 @@
       </c>
       <c r="C14" s="9"/>
       <c r="E14" s="18" t="s">
-        <v>3767</v>
+        <v>3766</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="12" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
       <c r="C15" s="9"/>
       <c r="E15" s="18">
@@ -40920,16 +41223,16 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="12" t="s">
-        <v>3769</v>
+        <v>3768</v>
       </c>
       <c r="C16" s="9"/>
       <c r="E16" s="18" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="12" t="s">
-        <v>3770</v>
+        <v>3769</v>
       </c>
       <c r="C17" s="9"/>
       <c r="E17" s="18">
@@ -40942,10 +41245,10 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="15" t="s">
-        <v>3771</v>
+        <v>3770</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
@@ -40972,7 +41275,7 @@
       </c>
       <c r="C21" s="9"/>
       <c r="E21" s="18" t="s">
-        <v>3772</v>
+        <v>3771</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
@@ -41031,7 +41334,7 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="12" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
       <c r="C28" s="9"/>
       <c r="E28" s="18">
@@ -41040,7 +41343,7 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="12" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="C29" s="9"/>
       <c r="E29" s="18">
@@ -41049,7 +41352,7 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="12" t="s">
-        <v>3775</v>
+        <v>3774</v>
       </c>
       <c r="C30" s="9"/>
       <c r="E30" s="18">
@@ -41058,7 +41361,7 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="12" t="s">
-        <v>3776</v>
+        <v>3775</v>
       </c>
       <c r="C31" s="9"/>
       <c r="E31" s="18">
@@ -41067,7 +41370,7 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="12" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="C32" s="9"/>
       <c r="E32" s="18">
@@ -41076,7 +41379,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
-        <v>3778</v>
+        <v>3777</v>
       </c>
       <c r="C33" s="9"/>
       <c r="E33" s="18">
@@ -41105,16 +41408,26 @@
       <c r="B36" s="12">
         <v>22</v>
       </c>
-      <c r="C36" s="9"/>
+      <c r="C36" s="28" t="s">
+        <v>4515</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>4496</v>
+      </c>
       <c r="E36" s="18" t="s">
-        <v>3761</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B37" s="12">
         <v>23</v>
       </c>
-      <c r="C37" s="9"/>
+      <c r="C37" s="28" t="s">
+        <v>4516</v>
+      </c>
+      <c r="D37" s="29" t="s">
+        <v>4497</v>
+      </c>
       <c r="E37" s="18">
         <v>2</v>
       </c>
@@ -41122,20 +41435,23 @@
     </row>
     <row r="38" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="B38" s="12">
         <v>24</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="28" t="s">
+        <v>4512</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>4493</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>3779</v>
       </c>
-      <c r="D38" s="15" t="s">
-        <v>3780</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>3781</v>
-      </c>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="29"/>
       <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -41146,6 +41462,9 @@
       <c r="E39" s="18">
         <v>0</v>
       </c>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="29"/>
       <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -41156,6 +41475,9 @@
       <c r="E40" s="18">
         <v>0</v>
       </c>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="29"/>
       <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -41166,6 +41488,9 @@
       <c r="E41" s="18">
         <v>27</v>
       </c>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="29"/>
       <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -41176,6 +41501,9 @@
       <c r="E42" s="18">
         <v>0</v>
       </c>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="29"/>
       <c r="K42" s="10"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -41186,110 +41514,145 @@
       <c r="E43" s="18">
         <v>0</v>
       </c>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="29"/>
       <c r="L43" s="10"/>
     </row>
     <row r="44" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="13" t="s">
-        <v>3782</v>
+        <v>3780</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="16" t="s">
-        <v>3783</v>
+        <v>3781</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>3784</v>
-      </c>
+        <v>3782</v>
+      </c>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="29"/>
       <c r="L44" s="10"/>
     </row>
     <row r="45" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="13" t="s">
-        <v>3785</v>
+        <v>3783</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="16" t="s">
-        <v>3786</v>
+        <v>3784</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>3774</v>
-      </c>
+        <v>3773</v>
+      </c>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="29"/>
       <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B46" s="12" t="s">
-        <v>3787</v>
+        <v>3785</v>
       </c>
       <c r="C46" s="9"/>
       <c r="E46" s="18">
         <v>0</v>
       </c>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="29"/>
       <c r="K46" s="10"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B47" s="12" t="s">
-        <v>3788</v>
+        <v>3786</v>
       </c>
       <c r="C47" s="9"/>
       <c r="E47" s="18">
         <v>0</v>
       </c>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="29"/>
       <c r="K47" s="10"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
+        <v>3787</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>3788</v>
+      </c>
+      <c r="C48" s="28" t="s">
+        <v>4506</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>4488</v>
+      </c>
+      <c r="E48" s="18" t="s">
         <v>3789</v>
       </c>
-      <c r="B48" s="12" t="s">
-        <v>3790</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>4361</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>3791</v>
-      </c>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="29"/>
       <c r="K48" s="10"/>
     </row>
     <row r="49" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>3792</v>
+        <v>3790</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>3793</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>4362</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>3794</v>
+        <v>3791</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>4507</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>4489</v>
       </c>
       <c r="E49" s="18">
         <v>0</v>
       </c>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="29"/>
       <c r="K49" s="10"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B50" s="12">
         <v>30</v>
       </c>
-      <c r="C50" s="9"/>
+      <c r="C50" s="28" t="s">
+        <v>4541</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>4542</v>
+      </c>
       <c r="E50" s="18" t="s">
-        <v>3791</v>
-      </c>
+        <v>3789</v>
+      </c>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="29"/>
       <c r="K50" s="10"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
-        <v>3795</v>
+        <v>3792</v>
       </c>
       <c r="B51" s="12">
         <v>31</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>4363</v>
+        <v>4353</v>
       </c>
       <c r="E51" s="18">
         <v>0</v>
       </c>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="29"/>
       <c r="K51" s="10"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
@@ -41300,24 +41663,30 @@
       <c r="E52" s="18">
         <v>0</v>
       </c>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="29"/>
       <c r="K52" s="10"/>
     </row>
     <row r="53" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
-        <v>3796</v>
+        <v>3793</v>
       </c>
       <c r="B53" s="12">
         <v>33</v>
       </c>
-      <c r="C53" s="9" t="s">
-        <v>3796</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>3797</v>
+      <c r="C53" s="28" t="s">
+        <v>4514</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>4495</v>
       </c>
       <c r="E53" s="18">
         <v>0</v>
       </c>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="29"/>
       <c r="K53" s="10"/>
     </row>
     <row r="54" spans="1:11" ht="46" x14ac:dyDescent="0.3">
@@ -41326,31 +41695,50 @@
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="15" t="s">
-        <v>4499</v>
+        <v>4484</v>
       </c>
       <c r="E54" s="18">
         <v>6</v>
       </c>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="29"/>
       <c r="K54" s="10"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B55" s="12">
         <v>35</v>
       </c>
-      <c r="C55" s="9"/>
+      <c r="C55" s="28" t="s">
+        <v>4543</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>4544</v>
+      </c>
       <c r="E55" s="18" t="s">
-        <v>3791</v>
-      </c>
+        <v>3789</v>
+      </c>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="29"/>
       <c r="K55" s="10"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B56" s="12">
         <v>36</v>
       </c>
-      <c r="C56" s="9"/>
+      <c r="C56" s="28" t="s">
+        <v>4545</v>
+      </c>
+      <c r="D56" s="29" t="s">
+        <v>4546</v>
+      </c>
       <c r="E56" s="18" t="s">
-        <v>3791</v>
-      </c>
+        <v>3789</v>
+      </c>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="29"/>
       <c r="K56" s="10"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
@@ -41361,87 +41749,102 @@
       <c r="E57" s="18">
         <v>0</v>
       </c>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="29"/>
     </row>
     <row r="58" spans="1:11" ht="46" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>3798</v>
+        <v>3794</v>
       </c>
       <c r="B58" s="12">
         <v>38</v>
       </c>
-      <c r="C58" s="9" t="s">
-        <v>3798</v>
+      <c r="C58" s="28" t="s">
+        <v>4511</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>3799</v>
+        <v>3795</v>
       </c>
       <c r="E58" s="18">
         <v>71</v>
       </c>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="29"/>
       <c r="K58" s="10"/>
     </row>
     <row r="59" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>3800</v>
+        <v>3796</v>
       </c>
       <c r="B59" s="12">
         <v>39</v>
       </c>
-      <c r="C59" s="9" t="s">
-        <v>4376</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>3801</v>
+      <c r="C59" s="28" t="s">
+        <v>4508</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>4490</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>3802</v>
-      </c>
+        <v>3797</v>
+      </c>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="29"/>
       <c r="K59" s="10"/>
     </row>
     <row r="60" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>3803</v>
+        <v>3798</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>3804</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>4364</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>3805</v>
+        <v>3799</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>4509</v>
+      </c>
+      <c r="D60" s="29" t="s">
+        <v>4491</v>
       </c>
       <c r="E60" s="18">
         <v>0</v>
       </c>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="29"/>
       <c r="K60" s="10"/>
     </row>
     <row r="61" spans="1:11" ht="46" x14ac:dyDescent="0.3">
       <c r="B61" s="12" t="s">
-        <v>3806</v>
+        <v>3800</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>4378</v>
+        <v>4364</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>4379</v>
+        <v>4365</v>
       </c>
       <c r="E61" s="18">
         <v>77</v>
       </c>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="29"/>
     </row>
     <row r="62" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>3807</v>
+        <v>3801</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>3808</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>4365</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>3809</v>
+        <v>3802</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>4510</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>4492</v>
       </c>
       <c r="E62" s="18">
         <v>77</v>
@@ -41450,7 +41853,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B63" s="12" t="s">
-        <v>3810</v>
+        <v>3803</v>
       </c>
       <c r="C63" s="9"/>
       <c r="E63" s="18">
@@ -41459,13 +41862,13 @@
     </row>
     <row r="64" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="13" t="s">
-        <v>3811</v>
+        <v>3804</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>4366</v>
+        <v>4354</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>3812</v>
+        <v>3805</v>
       </c>
       <c r="E64" s="18">
         <v>77</v>
@@ -41473,7 +41876,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B65" s="12" t="s">
-        <v>3813</v>
+        <v>3806</v>
       </c>
       <c r="C65" s="9"/>
       <c r="E65" s="18">
@@ -41493,7 +41896,12 @@
       <c r="B67" s="12">
         <v>41</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="28" t="s">
+        <v>4523</v>
+      </c>
+      <c r="D67" s="29" t="s">
+        <v>4504</v>
+      </c>
       <c r="E67" s="18">
         <v>0</v>
       </c>
@@ -41511,11 +41919,11 @@
       <c r="B69" s="12">
         <v>43</v>
       </c>
-      <c r="C69" s="9" t="s">
-        <v>4377</v>
-      </c>
-      <c r="D69" s="26" t="s">
-        <v>4380</v>
+      <c r="C69" s="28" t="s">
+        <v>4518</v>
+      </c>
+      <c r="D69" s="29" t="s">
+        <v>4499</v>
       </c>
       <c r="E69" s="18">
         <v>0</v>
@@ -41523,16 +41931,16 @@
     </row>
     <row r="70" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>3814</v>
+        <v>3807</v>
       </c>
       <c r="B70" s="12">
         <v>44</v>
       </c>
-      <c r="C70" s="9" t="s">
-        <v>3814</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>3815</v>
+      <c r="C70" s="28" t="s">
+        <v>4517</v>
+      </c>
+      <c r="D70" s="29" t="s">
+        <v>4498</v>
       </c>
       <c r="E70" s="18">
         <v>0</v>
@@ -41540,16 +41948,16 @@
     </row>
     <row r="71" spans="1:11" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
-        <v>3816</v>
+        <v>3808</v>
       </c>
       <c r="B71" s="12">
         <v>45</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>4367</v>
+        <v>4355</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>3817</v>
+        <v>3809</v>
       </c>
       <c r="E71" s="18">
         <v>0</v>
@@ -41557,16 +41965,16 @@
     </row>
     <row r="72" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>3818</v>
+        <v>3810</v>
       </c>
       <c r="B72" s="12">
         <v>46</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>4368</v>
+        <v>4356</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>3819</v>
+        <v>3811</v>
       </c>
       <c r="E72" s="18">
         <v>0</v>
@@ -41574,16 +41982,16 @@
     </row>
     <row r="73" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
-        <v>4384</v>
+        <v>4369</v>
       </c>
       <c r="B73" s="13">
         <v>47</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>4369</v>
+        <v>4357</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>3820</v>
+        <v>3812</v>
       </c>
       <c r="E73" s="18">
         <v>0</v>
@@ -41592,16 +42000,16 @@
     </row>
     <row r="74" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
-        <v>4381</v>
+        <v>4366</v>
       </c>
       <c r="B74" s="13">
         <v>48</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>4370</v>
+        <v>4358</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>3821</v>
+        <v>3813</v>
       </c>
       <c r="E74" s="18">
         <v>0</v>
@@ -41619,13 +42027,13 @@
     </row>
     <row r="76" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="13" t="s">
-        <v>3822</v>
+        <v>3814</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>4371</v>
+        <v>4359</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>3823</v>
+        <v>3815</v>
       </c>
       <c r="E76" s="18">
         <v>0</v>
@@ -41633,13 +42041,13 @@
     </row>
     <row r="77" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="13" t="s">
-        <v>3824</v>
+        <v>3816</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>4372</v>
+        <v>4360</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>3825</v>
+        <v>3817</v>
       </c>
       <c r="E77" s="18">
         <v>0</v>
@@ -41647,16 +42055,16 @@
     </row>
     <row r="78" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>4382</v>
+        <v>4367</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>3826</v>
+        <v>3818</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>4373</v>
+        <v>4361</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>3827</v>
+        <v>3819</v>
       </c>
       <c r="E78" s="18">
         <v>0</v>
@@ -41664,7 +42072,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B79" s="13" t="s">
-        <v>3828</v>
+        <v>3820</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="16"/>
@@ -41674,13 +42082,13 @@
     </row>
     <row r="80" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="13" t="s">
-        <v>3829</v>
+        <v>3821</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>4374</v>
+        <v>4362</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>3830</v>
+        <v>3822</v>
       </c>
       <c r="E80" s="18">
         <v>0</v>
@@ -41688,7 +42096,7 @@
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="13" t="s">
-        <v>3831</v>
+        <v>3823</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="16"/>
@@ -41701,10 +42109,10 @@
         <v>50</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>4375</v>
+        <v>4363</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>3832</v>
+        <v>3824</v>
       </c>
       <c r="E82" s="18">
         <v>0</v>
@@ -41715,7 +42123,7 @@
         <v>51</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>4503</v>
+        <v>4487</v>
       </c>
       <c r="D83" s="16"/>
       <c r="E83" s="18">
@@ -41726,10 +42134,12 @@
       <c r="B84" s="13">
         <v>52</v>
       </c>
-      <c r="C84" s="9" t="s">
-        <v>4502</v>
-      </c>
-      <c r="D84" s="16"/>
+      <c r="C84" s="28" t="s">
+        <v>4513</v>
+      </c>
+      <c r="D84" s="29" t="s">
+        <v>4494</v>
+      </c>
       <c r="E84" s="18">
         <v>0</v>
       </c>
@@ -41778,8 +42188,12 @@
       <c r="B89" s="13">
         <v>57</v>
       </c>
-      <c r="C89" s="9"/>
-      <c r="D89" s="16"/>
+      <c r="C89" s="28" t="s">
+        <v>4524</v>
+      </c>
+      <c r="D89" s="29" t="s">
+        <v>4505</v>
+      </c>
       <c r="E89" s="18">
         <v>0</v>
       </c>
@@ -41806,7 +42220,7 @@
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92" s="13" t="s">
-        <v>3833</v>
+        <v>3825</v>
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="16"/>
@@ -41816,7 +42230,7 @@
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" s="13" t="s">
-        <v>3834</v>
+        <v>3826</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="16"/>
@@ -41826,7 +42240,7 @@
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94" s="13" t="s">
-        <v>3835</v>
+        <v>3827</v>
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="16"/>
@@ -41836,7 +42250,7 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" s="13" t="s">
-        <v>3836</v>
+        <v>3828</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="16"/>
@@ -41846,7 +42260,7 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" s="13" t="s">
-        <v>3837</v>
+        <v>3829</v>
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="16"/>
@@ -41856,7 +42270,7 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97" s="13" t="s">
-        <v>3838</v>
+        <v>3830</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="16"/>
@@ -41868,8 +42282,12 @@
       <c r="B98" s="13">
         <v>60</v>
       </c>
-      <c r="C98" s="9"/>
-      <c r="D98" s="16"/>
+      <c r="C98" s="28" t="s">
+        <v>4519</v>
+      </c>
+      <c r="D98" s="29" t="s">
+        <v>4500</v>
+      </c>
       <c r="E98" s="18">
         <v>0</v>
       </c>
@@ -41878,8 +42296,12 @@
       <c r="B99" s="13">
         <v>61</v>
       </c>
-      <c r="C99" s="9"/>
-      <c r="D99" s="16"/>
+      <c r="C99" s="28" t="s">
+        <v>4520</v>
+      </c>
+      <c r="D99" s="29" t="s">
+        <v>4501</v>
+      </c>
       <c r="E99" s="18">
         <v>0</v>
       </c>
@@ -41888,8 +42310,12 @@
       <c r="B100" s="13">
         <v>62</v>
       </c>
-      <c r="C100" s="9"/>
-      <c r="D100" s="16"/>
+      <c r="C100" s="28" t="s">
+        <v>4521</v>
+      </c>
+      <c r="D100" s="29" t="s">
+        <v>4502</v>
+      </c>
       <c r="E100" s="18">
         <v>0</v>
       </c>
@@ -41948,8 +42374,12 @@
       <c r="B106" s="13">
         <v>68</v>
       </c>
-      <c r="C106" s="9"/>
-      <c r="D106" s="16"/>
+      <c r="C106" s="28" t="s">
+        <v>4522</v>
+      </c>
+      <c r="D106" s="29" t="s">
+        <v>4503</v>
+      </c>
       <c r="E106" s="18">
         <v>0</v>
       </c>
@@ -41960,7 +42390,7 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="16" t="s">
-        <v>3839</v>
+        <v>3831</v>
       </c>
       <c r="E107" s="18">
         <v>0</v>
@@ -41968,7 +42398,7 @@
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B108" s="13" t="s">
-        <v>3840</v>
+        <v>3832</v>
       </c>
       <c r="C108" s="9"/>
       <c r="D108" s="16"/>
@@ -41978,11 +42408,11 @@
     </row>
     <row r="109" spans="2:5" ht="23" x14ac:dyDescent="0.3">
       <c r="B109" s="13" t="s">
-        <v>3841</v>
+        <v>3833</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="16" t="s">
-        <v>4392</v>
+        <v>4377</v>
       </c>
       <c r="E109" s="18">
         <v>0</v>
@@ -41990,7 +42420,7 @@
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B110" s="13" t="s">
-        <v>3842</v>
+        <v>3834</v>
       </c>
       <c r="C110" s="9"/>
       <c r="D110" s="16"/>
@@ -42000,7 +42430,7 @@
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B111" s="13" t="s">
-        <v>3843</v>
+        <v>3835</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="16"/>
@@ -42010,7 +42440,7 @@
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B112" s="13" t="s">
-        <v>3844</v>
+        <v>3836</v>
       </c>
       <c r="C112" s="9"/>
       <c r="D112" s="16"/>
@@ -42020,7 +42450,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B113" s="13" t="s">
-        <v>3767</v>
+        <v>3766</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="16"/>
@@ -42032,8 +42462,12 @@
       <c r="B114" s="13">
         <v>70</v>
       </c>
-      <c r="C114" s="9"/>
-      <c r="D114" s="16"/>
+      <c r="C114" s="28" t="s">
+        <v>4525</v>
+      </c>
+      <c r="D114" s="29" t="s">
+        <v>4526</v>
+      </c>
       <c r="E114" s="18">
         <v>0</v>
       </c>
@@ -42042,8 +42476,12 @@
       <c r="B115" s="13">
         <v>71</v>
       </c>
-      <c r="C115" s="9"/>
-      <c r="D115" s="16"/>
+      <c r="C115" s="28" t="s">
+        <v>4527</v>
+      </c>
+      <c r="D115" s="29" t="s">
+        <v>4530</v>
+      </c>
       <c r="E115" s="18">
         <v>0</v>
       </c>
@@ -42052,8 +42490,12 @@
       <c r="B116" s="13">
         <v>72</v>
       </c>
-      <c r="C116" s="9"/>
-      <c r="D116" s="16"/>
+      <c r="C116" s="28" t="s">
+        <v>4528</v>
+      </c>
+      <c r="D116" s="29" t="s">
+        <v>4531</v>
+      </c>
       <c r="E116" s="18">
         <v>0</v>
       </c>
@@ -42062,55 +42504,67 @@
       <c r="B117" s="13">
         <v>73</v>
       </c>
-      <c r="C117" s="9"/>
-      <c r="D117" s="16"/>
+      <c r="C117" s="28" t="s">
+        <v>4529</v>
+      </c>
+      <c r="D117" s="29" t="s">
+        <v>4532</v>
+      </c>
       <c r="E117" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="23" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B118" s="13">
         <v>74</v>
       </c>
-      <c r="C118" s="9"/>
-      <c r="D118" s="16" t="s">
-        <v>4434</v>
+      <c r="C118" s="28" t="s">
+        <v>4533</v>
+      </c>
+      <c r="D118" s="29" t="s">
+        <v>4534</v>
       </c>
       <c r="E118" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="23" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B119" s="13">
         <v>75</v>
       </c>
-      <c r="C119" s="9"/>
-      <c r="D119" s="16" t="s">
-        <v>4434</v>
+      <c r="C119" s="28" t="s">
+        <v>4535</v>
+      </c>
+      <c r="D119" s="29" t="s">
+        <v>4538</v>
       </c>
       <c r="E119" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="23" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B120" s="13">
         <v>76</v>
       </c>
-      <c r="C120" s="9"/>
-      <c r="D120" s="16" t="s">
-        <v>4434</v>
+      <c r="C120" s="28" t="s">
+        <v>4536</v>
+      </c>
+      <c r="D120" s="29" t="s">
+        <v>4539</v>
       </c>
       <c r="E120" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="23" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B121" s="13">
         <v>77</v>
       </c>
-      <c r="C121" s="9"/>
-      <c r="D121" s="16" t="s">
-        <v>4434</v>
+      <c r="C121" s="28" t="s">
+        <v>4537</v>
+      </c>
+      <c r="D121" s="29" t="s">
+        <v>4540</v>
       </c>
       <c r="E121" s="18">
         <v>0</v>
@@ -42122,7 +42576,7 @@
       </c>
       <c r="C122" s="9"/>
       <c r="D122" s="16" t="s">
-        <v>4434</v>
+        <v>4419</v>
       </c>
       <c r="E122" s="18">
         <v>0</v>
@@ -42134,7 +42588,7 @@
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="16" t="s">
-        <v>4434</v>
+        <v>4419</v>
       </c>
       <c r="E123" s="18">
         <v>0</v>
@@ -42142,16 +42596,16 @@
     </row>
     <row r="124" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="9" t="s">
-        <v>4383</v>
+        <v>4368</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>3846</v>
+        <v>3838</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>3845</v>
+        <v>3837</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>4435</v>
+        <v>4420</v>
       </c>
       <c r="E124" s="18">
         <v>0</v>
@@ -42159,11 +42613,11 @@
     </row>
     <row r="125" spans="1:5" ht="23" x14ac:dyDescent="0.3">
       <c r="B125" s="12" t="s">
-        <v>3847</v>
+        <v>3839</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="15" t="s">
-        <v>4466</v>
+        <v>4451</v>
       </c>
       <c r="E125" s="18">
         <v>0</v>
@@ -42171,7 +42625,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B126" s="12" t="s">
-        <v>3848</v>
+        <v>3840</v>
       </c>
       <c r="C126" s="9"/>
       <c r="E126" s="18">
@@ -42180,7 +42634,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B127" s="12" t="s">
-        <v>3849</v>
+        <v>3841</v>
       </c>
       <c r="C127" s="9"/>
       <c r="E127" s="18">
@@ -42189,7 +42643,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B128" s="12" t="s">
-        <v>3850</v>
+        <v>3842</v>
       </c>
       <c r="C128" s="9"/>
       <c r="E128" s="18">
@@ -42198,7 +42652,7 @@
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B129" s="12" t="s">
-        <v>3781</v>
+        <v>3779</v>
       </c>
       <c r="E129" s="18" t="s">
         <v>1559</v>
@@ -42210,6 +42664,173 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04826869-3C8D-F24D-8F29-3783DBE1C726}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="3" max="3" width="58.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="30" t="s">
+        <v>4547</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>4548</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A4" s="32" t="s">
+        <v>4549</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>4550</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>4551</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A5" s="28" t="s">
+        <v>4552</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>4553</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>4554</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A6" s="28" t="s">
+        <v>4555</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>4556</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>4557</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A7" s="28" t="s">
+        <v>4558</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>4559</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>4560</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A8" s="28" t="s">
+        <v>4561</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>4562</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>4563</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A9" s="28" t="s">
+        <v>4564</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>4565</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A10" s="28" t="s">
+        <v>4567</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>4568</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>4569</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A11" s="28" t="s">
+        <v>4570</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>4571</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>4572</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A12" s="28" t="s">
+        <v>4573</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>4574</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>4575</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A13" s="28" t="s">
+        <v>4576</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>4577</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>3819</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A14" s="28" t="s">
+        <v>4578</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>4579</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>3805</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A15" s="28" t="s">
+        <v>4580</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>4581</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>4582</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A16" s="28" t="s">
+        <v>4583</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>4584</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>4585</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -42219,7 +42840,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>3851</v>
+        <v>3843</v>
       </c>
       <c r="B1" t="s">
         <v>1769</v>
@@ -42227,7 +42848,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3852</v>
+        <v>3844</v>
       </c>
       <c r="B2" t="s">
         <v>1864</v>
@@ -42235,7 +42856,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3853</v>
+        <v>3845</v>
       </c>
       <c r="B3" t="s">
         <v>1864</v>
@@ -42243,7 +42864,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3854</v>
+        <v>3846</v>
       </c>
       <c r="B4" t="s">
         <v>1864</v>
@@ -42251,7 +42872,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3855</v>
+        <v>3847</v>
       </c>
       <c r="B5" t="s">
         <v>1832</v>
@@ -42259,7 +42880,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>3856</v>
+        <v>3848</v>
       </c>
       <c r="B6" t="s">
         <v>1893</v>
@@ -42267,7 +42888,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>3857</v>
+        <v>3849</v>
       </c>
       <c r="B7" t="s">
         <v>2008</v>
@@ -42275,7 +42896,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>3858</v>
+        <v>3850</v>
       </c>
       <c r="B8" t="s">
         <v>2031</v>
@@ -42286,7 +42907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B256"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -42297,2050 +42918,2050 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>3859</v>
+        <v>3851</v>
       </c>
       <c r="B1" t="s">
-        <v>3860</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3861</v>
+        <v>3853</v>
       </c>
       <c r="B2" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3863</v>
+        <v>3855</v>
       </c>
       <c r="B3" t="s">
-        <v>3864</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3865</v>
+        <v>3857</v>
       </c>
       <c r="B4" t="s">
-        <v>3866</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3867</v>
+        <v>3859</v>
       </c>
       <c r="B5" t="s">
-        <v>3868</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>3869</v>
+        <v>3861</v>
       </c>
       <c r="B6" t="s">
-        <v>3870</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>3871</v>
+        <v>3863</v>
       </c>
       <c r="B7" t="s">
-        <v>3872</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>3873</v>
+        <v>3865</v>
       </c>
       <c r="B8" t="s">
-        <v>3874</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>3875</v>
+        <v>3867</v>
       </c>
       <c r="B9" t="s">
-        <v>3876</v>
+        <v>3868</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>3877</v>
+        <v>3869</v>
       </c>
       <c r="B10" t="s">
-        <v>3878</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>3879</v>
+        <v>3871</v>
       </c>
       <c r="B11" t="s">
-        <v>3880</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>3881</v>
+        <v>3873</v>
       </c>
       <c r="B12" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>3882</v>
+        <v>3874</v>
       </c>
       <c r="B13" t="s">
-        <v>3883</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>3884</v>
+        <v>3876</v>
       </c>
       <c r="B14" t="s">
-        <v>3885</v>
+        <v>3877</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>3886</v>
+        <v>3878</v>
       </c>
       <c r="B15" t="s">
-        <v>3887</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>3888</v>
+        <v>3880</v>
       </c>
       <c r="B16" t="s">
-        <v>3889</v>
+        <v>3881</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>3890</v>
+        <v>3882</v>
       </c>
       <c r="B17" t="s">
-        <v>3891</v>
+        <v>3883</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>3892</v>
+        <v>3884</v>
       </c>
       <c r="B18" t="s">
-        <v>3893</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>3894</v>
+        <v>3886</v>
       </c>
       <c r="B19" t="s">
-        <v>3895</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>3896</v>
+        <v>3888</v>
       </c>
       <c r="B20" t="s">
-        <v>3897</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>3898</v>
+        <v>3890</v>
       </c>
       <c r="B21" t="s">
-        <v>3899</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>3900</v>
+        <v>3892</v>
       </c>
       <c r="B22" t="s">
-        <v>3901</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>3902</v>
+        <v>3894</v>
       </c>
       <c r="B23" t="s">
-        <v>3903</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>3904</v>
+        <v>3896</v>
       </c>
       <c r="B24" t="s">
-        <v>3905</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>3906</v>
+        <v>3898</v>
       </c>
       <c r="B25" t="s">
-        <v>3907</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>3908</v>
+        <v>3900</v>
       </c>
       <c r="B26" t="s">
-        <v>3909</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>3910</v>
+        <v>3902</v>
       </c>
       <c r="B27" t="s">
-        <v>3911</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>3912</v>
+        <v>3904</v>
       </c>
       <c r="B28" t="s">
-        <v>3913</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>3914</v>
+        <v>3906</v>
       </c>
       <c r="B29" t="s">
-        <v>3915</v>
+        <v>3907</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>3916</v>
+        <v>3908</v>
       </c>
       <c r="B30" t="s">
-        <v>3917</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>3918</v>
+        <v>3910</v>
       </c>
       <c r="B31" t="s">
-        <v>3919</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>3920</v>
+        <v>3912</v>
       </c>
       <c r="B32" t="s">
-        <v>3921</v>
+        <v>3913</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>3922</v>
+        <v>3914</v>
       </c>
       <c r="B33" t="s">
-        <v>3923</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>3924</v>
+        <v>3916</v>
       </c>
       <c r="B34" t="s">
-        <v>3925</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>3926</v>
+        <v>3918</v>
       </c>
       <c r="B35" t="s">
-        <v>3872</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>3927</v>
+        <v>3919</v>
       </c>
       <c r="B36" t="s">
-        <v>3928</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>3929</v>
+        <v>3921</v>
       </c>
       <c r="B37" t="s">
-        <v>3930</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>3931</v>
+        <v>3923</v>
       </c>
       <c r="B38" t="s">
-        <v>3932</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>3933</v>
+        <v>3925</v>
       </c>
       <c r="B39" t="s">
-        <v>3934</v>
+        <v>3926</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>3935</v>
+        <v>3927</v>
       </c>
       <c r="B40" t="s">
-        <v>3936</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>3937</v>
+        <v>3929</v>
       </c>
       <c r="B41" t="s">
-        <v>3938</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>3939</v>
+        <v>3931</v>
       </c>
       <c r="B42" t="s">
-        <v>3940</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>3941</v>
+        <v>3933</v>
       </c>
       <c r="B43" t="s">
-        <v>3942</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>3943</v>
+        <v>3935</v>
       </c>
       <c r="B44" t="s">
-        <v>3944</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>3945</v>
+        <v>3937</v>
       </c>
       <c r="B45" t="s">
-        <v>3946</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>3947</v>
+        <v>3939</v>
       </c>
       <c r="B46" t="s">
-        <v>3948</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>3949</v>
+        <v>3941</v>
       </c>
       <c r="B47" t="s">
-        <v>3950</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>3951</v>
+        <v>3943</v>
       </c>
       <c r="B48" t="s">
-        <v>3952</v>
+        <v>3944</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>3953</v>
+        <v>3945</v>
       </c>
       <c r="B49" t="s">
-        <v>3954</v>
+        <v>3946</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>3955</v>
+        <v>3947</v>
       </c>
       <c r="B50" t="s">
-        <v>3956</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>3957</v>
+        <v>3949</v>
       </c>
       <c r="B51" t="s">
-        <v>3958</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>3959</v>
+        <v>3951</v>
       </c>
       <c r="B52" t="s">
-        <v>3872</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>3960</v>
+        <v>3952</v>
       </c>
       <c r="B53" t="s">
-        <v>3961</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>3962</v>
+        <v>3954</v>
       </c>
       <c r="B54" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>3963</v>
+        <v>3955</v>
       </c>
       <c r="B55" t="s">
-        <v>3964</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>3965</v>
+        <v>3957</v>
       </c>
       <c r="B56" t="s">
-        <v>3966</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>3967</v>
+        <v>3959</v>
       </c>
       <c r="B57" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>3968</v>
+        <v>3960</v>
       </c>
       <c r="B58" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>3969</v>
+        <v>3961</v>
       </c>
       <c r="B59" t="s">
-        <v>3970</v>
+        <v>3962</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>3971</v>
+        <v>3963</v>
       </c>
       <c r="B60" t="s">
-        <v>3972</v>
+        <v>3964</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>3973</v>
+        <v>3965</v>
       </c>
       <c r="B61" t="s">
-        <v>3974</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>3975</v>
+        <v>3967</v>
       </c>
       <c r="B62" t="s">
-        <v>3976</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>3977</v>
+        <v>3969</v>
       </c>
       <c r="B63" t="s">
-        <v>3978</v>
+        <v>3970</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>3979</v>
+        <v>3971</v>
       </c>
       <c r="B64" t="s">
-        <v>3980</v>
+        <v>3972</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>3981</v>
+        <v>3973</v>
       </c>
       <c r="B65" t="s">
-        <v>3982</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>3983</v>
+        <v>3975</v>
       </c>
       <c r="B66" t="s">
-        <v>3984</v>
+        <v>3976</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>3985</v>
+        <v>3977</v>
       </c>
       <c r="B67" t="s">
-        <v>3986</v>
+        <v>3978</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>3987</v>
+        <v>3979</v>
       </c>
       <c r="B68" t="s">
-        <v>3988</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>3989</v>
+        <v>3981</v>
       </c>
       <c r="B69" t="s">
-        <v>3990</v>
+        <v>3982</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>3991</v>
+        <v>3983</v>
       </c>
       <c r="B70" t="s">
-        <v>3992</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>3993</v>
+        <v>3985</v>
       </c>
       <c r="B71" t="s">
-        <v>3994</v>
+        <v>3986</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>3995</v>
+        <v>3987</v>
       </c>
       <c r="B72" t="s">
-        <v>3996</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>3997</v>
+        <v>3989</v>
       </c>
       <c r="B73" t="s">
-        <v>3998</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>3999</v>
+        <v>3991</v>
       </c>
       <c r="B74" t="s">
-        <v>4000</v>
+        <v>3992</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>4001</v>
+        <v>3993</v>
       </c>
       <c r="B75" t="s">
-        <v>4002</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>4003</v>
+        <v>3995</v>
       </c>
       <c r="B76" t="s">
-        <v>4004</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>4005</v>
+        <v>3997</v>
       </c>
       <c r="B77" t="s">
-        <v>4006</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>4007</v>
+        <v>3999</v>
       </c>
       <c r="B78" t="s">
-        <v>4008</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>4009</v>
+        <v>4001</v>
       </c>
       <c r="B79" t="s">
-        <v>4010</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>4011</v>
+        <v>4003</v>
       </c>
       <c r="B80" t="s">
-        <v>4012</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>4013</v>
+        <v>4005</v>
       </c>
       <c r="B81" t="s">
-        <v>4014</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>4015</v>
+        <v>4007</v>
       </c>
       <c r="B82" t="s">
-        <v>4016</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>4017</v>
+        <v>4009</v>
       </c>
       <c r="B83" t="s">
-        <v>4018</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>4019</v>
+        <v>4011</v>
       </c>
       <c r="B84" t="s">
-        <v>4020</v>
+        <v>4012</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>4021</v>
+        <v>4013</v>
       </c>
       <c r="B85" t="s">
-        <v>4022</v>
+        <v>4014</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>4023</v>
+        <v>4015</v>
       </c>
       <c r="B86" t="s">
-        <v>4024</v>
+        <v>4016</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>4025</v>
+        <v>4017</v>
       </c>
       <c r="B87" t="s">
-        <v>4026</v>
+        <v>4018</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>4027</v>
+        <v>4019</v>
       </c>
       <c r="B88" t="s">
-        <v>4028</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>4029</v>
+        <v>4021</v>
       </c>
       <c r="B89" t="s">
-        <v>4030</v>
+        <v>4022</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>4031</v>
+        <v>4023</v>
       </c>
       <c r="B90" t="s">
-        <v>4032</v>
+        <v>4024</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>4033</v>
+        <v>4025</v>
       </c>
       <c r="B91" t="s">
-        <v>4034</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>4035</v>
+        <v>4027</v>
       </c>
       <c r="B92" t="s">
-        <v>4036</v>
+        <v>4028</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>4037</v>
+        <v>4029</v>
       </c>
       <c r="B93" t="s">
-        <v>4038</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>4039</v>
+        <v>4031</v>
       </c>
       <c r="B94" t="s">
-        <v>4040</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>4041</v>
+        <v>4033</v>
       </c>
       <c r="B95" t="s">
-        <v>4042</v>
+        <v>4034</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>4043</v>
+        <v>4035</v>
       </c>
       <c r="B96" t="s">
-        <v>4044</v>
+        <v>4036</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>4045</v>
+        <v>4037</v>
       </c>
       <c r="B97" t="s">
-        <v>4046</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>4047</v>
+        <v>4039</v>
       </c>
       <c r="B98" t="s">
-        <v>4048</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>4049</v>
+        <v>4041</v>
       </c>
       <c r="B99" t="s">
-        <v>4050</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>4051</v>
+        <v>4043</v>
       </c>
       <c r="B100" t="s">
-        <v>3872</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>4052</v>
+        <v>4044</v>
       </c>
       <c r="B101" t="s">
-        <v>4053</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>4054</v>
+        <v>4046</v>
       </c>
       <c r="B102" t="s">
-        <v>4055</v>
+        <v>4047</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>4056</v>
+        <v>4048</v>
       </c>
       <c r="B103" t="s">
-        <v>3872</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>4057</v>
+        <v>4049</v>
       </c>
       <c r="B104" t="s">
-        <v>4058</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>4059</v>
+        <v>4051</v>
       </c>
       <c r="B105" t="s">
-        <v>4060</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>4061</v>
+        <v>4053</v>
       </c>
       <c r="B106" t="s">
-        <v>4062</v>
+        <v>4054</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>4063</v>
+        <v>4055</v>
       </c>
       <c r="B107" t="s">
-        <v>4064</v>
+        <v>4056</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>4065</v>
+        <v>4057</v>
       </c>
       <c r="B108" t="s">
-        <v>4066</v>
+        <v>4058</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>4067</v>
+        <v>4059</v>
       </c>
       <c r="B109" t="s">
-        <v>4068</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>4069</v>
+        <v>4061</v>
       </c>
       <c r="B110" t="s">
-        <v>4070</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>4071</v>
+        <v>4063</v>
       </c>
       <c r="B111" t="s">
-        <v>4072</v>
+        <v>4064</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>4073</v>
+        <v>4065</v>
       </c>
       <c r="B112" t="s">
-        <v>4074</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>4075</v>
+        <v>4067</v>
       </c>
       <c r="B113" t="s">
-        <v>4076</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>4077</v>
+        <v>4069</v>
       </c>
       <c r="B114" t="s">
-        <v>4078</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>4079</v>
+        <v>4071</v>
       </c>
       <c r="B115" t="s">
-        <v>4080</v>
+        <v>4072</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>4081</v>
+        <v>4073</v>
       </c>
       <c r="B116" t="s">
-        <v>4082</v>
+        <v>4074</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>4083</v>
+        <v>4075</v>
       </c>
       <c r="B117" t="s">
-        <v>4084</v>
+        <v>4076</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>4085</v>
+        <v>4077</v>
       </c>
       <c r="B118" t="s">
-        <v>4086</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>4087</v>
+        <v>4079</v>
       </c>
       <c r="B119" t="s">
-        <v>4088</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>4089</v>
+        <v>4081</v>
       </c>
       <c r="B120" t="s">
-        <v>4090</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>4091</v>
+        <v>4083</v>
       </c>
       <c r="B121" t="s">
-        <v>4092</v>
+        <v>4084</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>4093</v>
+        <v>4085</v>
       </c>
       <c r="B122" t="s">
-        <v>4094</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>4095</v>
+        <v>4087</v>
       </c>
       <c r="B123" t="s">
-        <v>4096</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>4097</v>
+        <v>4089</v>
       </c>
       <c r="B124" t="s">
-        <v>4098</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>4099</v>
+        <v>4091</v>
       </c>
       <c r="B125" t="s">
-        <v>4100</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>4101</v>
+        <v>4093</v>
       </c>
       <c r="B126" t="s">
-        <v>4102</v>
+        <v>4094</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>4103</v>
+        <v>4095</v>
       </c>
       <c r="B127" t="s">
-        <v>4104</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>4105</v>
+        <v>4097</v>
       </c>
       <c r="B128" t="s">
-        <v>4106</v>
+        <v>4098</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>4107</v>
+        <v>4099</v>
       </c>
       <c r="B129" t="s">
-        <v>4108</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>4109</v>
+        <v>4101</v>
       </c>
       <c r="B130" t="s">
-        <v>4110</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>4111</v>
+        <v>4103</v>
       </c>
       <c r="B131" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>4112</v>
+        <v>4104</v>
       </c>
       <c r="B132" t="s">
-        <v>4113</v>
+        <v>4105</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>4114</v>
+        <v>4106</v>
       </c>
       <c r="B133" t="s">
-        <v>4115</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>4116</v>
+        <v>4108</v>
       </c>
       <c r="B134" t="s">
-        <v>4117</v>
+        <v>4109</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>4118</v>
+        <v>4110</v>
       </c>
       <c r="B135" t="s">
-        <v>4119</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>4120</v>
+        <v>4112</v>
       </c>
       <c r="B136" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>4121</v>
+        <v>4113</v>
       </c>
       <c r="B137" t="s">
-        <v>4122</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>4123</v>
+        <v>4115</v>
       </c>
       <c r="B138" t="s">
-        <v>4124</v>
+        <v>4116</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>4125</v>
+        <v>4117</v>
       </c>
       <c r="B139" t="s">
-        <v>4126</v>
+        <v>4118</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>4127</v>
+        <v>4119</v>
       </c>
       <c r="B140" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>4128</v>
+        <v>4120</v>
       </c>
       <c r="B141" t="s">
-        <v>4129</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>4130</v>
+        <v>4122</v>
       </c>
       <c r="B142" t="s">
-        <v>4131</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>4132</v>
+        <v>4124</v>
       </c>
       <c r="B143" t="s">
-        <v>4133</v>
+        <v>4125</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>4134</v>
+        <v>4126</v>
       </c>
       <c r="B144" t="s">
-        <v>4135</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>4136</v>
+        <v>4128</v>
       </c>
       <c r="B145" t="s">
-        <v>4137</v>
+        <v>4129</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>4138</v>
+        <v>4130</v>
       </c>
       <c r="B146" t="s">
-        <v>4139</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>4140</v>
+        <v>4132</v>
       </c>
       <c r="B147" t="s">
-        <v>4141</v>
+        <v>4133</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>4142</v>
+        <v>4134</v>
       </c>
       <c r="B148" t="s">
-        <v>4143</v>
+        <v>4135</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>4144</v>
+        <v>4136</v>
       </c>
       <c r="B149" t="s">
-        <v>4145</v>
+        <v>4137</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>4146</v>
+        <v>4138</v>
       </c>
       <c r="B150" t="s">
-        <v>4147</v>
+        <v>4139</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>4148</v>
+        <v>4140</v>
       </c>
       <c r="B151" t="s">
-        <v>4149</v>
+        <v>4141</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>4150</v>
+        <v>4142</v>
       </c>
       <c r="B152" t="s">
-        <v>4151</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>4152</v>
+        <v>4144</v>
       </c>
       <c r="B153" t="s">
-        <v>4153</v>
+        <v>4145</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>4154</v>
+        <v>4146</v>
       </c>
       <c r="B154" t="s">
-        <v>4155</v>
+        <v>4147</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>4156</v>
+        <v>4148</v>
       </c>
       <c r="B155" t="s">
-        <v>4157</v>
+        <v>4149</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>4158</v>
+        <v>4150</v>
       </c>
       <c r="B156" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>4159</v>
+        <v>4151</v>
       </c>
       <c r="B157" t="s">
-        <v>4160</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>4161</v>
+        <v>4153</v>
       </c>
       <c r="B158" t="s">
-        <v>4162</v>
+        <v>4154</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>4163</v>
+        <v>4155</v>
       </c>
       <c r="B159" t="s">
-        <v>4164</v>
+        <v>4156</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>4165</v>
+        <v>4157</v>
       </c>
       <c r="B160" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>4166</v>
+        <v>4158</v>
       </c>
       <c r="B161" t="s">
-        <v>4167</v>
+        <v>4159</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>4168</v>
+        <v>4160</v>
       </c>
       <c r="B162" t="s">
-        <v>4169</v>
+        <v>4161</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>4170</v>
+        <v>4162</v>
       </c>
       <c r="B163" t="s">
-        <v>3872</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>4171</v>
+        <v>4163</v>
       </c>
       <c r="B164" t="s">
-        <v>4172</v>
+        <v>4164</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>4173</v>
+        <v>4165</v>
       </c>
       <c r="B165" t="s">
-        <v>4174</v>
+        <v>4166</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>4175</v>
+        <v>4167</v>
       </c>
       <c r="B166" t="s">
-        <v>4176</v>
+        <v>4168</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>4177</v>
+        <v>4169</v>
       </c>
       <c r="B167" t="s">
-        <v>3872</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="B168" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="B169" t="s">
-        <v>4181</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>4182</v>
+        <v>4174</v>
       </c>
       <c r="B170" t="s">
-        <v>4183</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>4184</v>
+        <v>4176</v>
       </c>
       <c r="B171" t="s">
-        <v>4185</v>
+        <v>4177</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>4186</v>
+        <v>4178</v>
       </c>
       <c r="B172" t="s">
-        <v>4187</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="B173" t="s">
-        <v>4189</v>
+        <v>4181</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>4190</v>
+        <v>4182</v>
       </c>
       <c r="B174" t="s">
-        <v>4191</v>
+        <v>4183</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>4192</v>
+        <v>4184</v>
       </c>
       <c r="B175" t="s">
-        <v>4193</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>4194</v>
+        <v>4186</v>
       </c>
       <c r="B176" t="s">
-        <v>4195</v>
+        <v>4187</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>4196</v>
+        <v>4188</v>
       </c>
       <c r="B177" t="s">
-        <v>4197</v>
+        <v>4189</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="B178" t="s">
-        <v>4199</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>4200</v>
+        <v>4192</v>
       </c>
       <c r="B179" t="s">
-        <v>4201</v>
+        <v>4193</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>4202</v>
+        <v>4194</v>
       </c>
       <c r="B180" t="s">
-        <v>4203</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>4204</v>
+        <v>4196</v>
       </c>
       <c r="B181" t="s">
-        <v>4205</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>4206</v>
+        <v>4198</v>
       </c>
       <c r="B182" t="s">
-        <v>4207</v>
+        <v>4199</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>4208</v>
+        <v>4200</v>
       </c>
       <c r="B183" t="s">
-        <v>4209</v>
+        <v>4201</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>4210</v>
+        <v>4202</v>
       </c>
       <c r="B184" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>4211</v>
+        <v>4203</v>
       </c>
       <c r="B185" t="s">
-        <v>4212</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>4213</v>
+        <v>4205</v>
       </c>
       <c r="B186" t="s">
-        <v>4214</v>
+        <v>4206</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>4215</v>
+        <v>4207</v>
       </c>
       <c r="B187" t="s">
-        <v>4216</v>
+        <v>4208</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>4217</v>
+        <v>4209</v>
       </c>
       <c r="B188" t="s">
-        <v>4218</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>4219</v>
+        <v>4211</v>
       </c>
       <c r="B189" t="s">
-        <v>4220</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>4221</v>
+        <v>4213</v>
       </c>
       <c r="B190" t="s">
-        <v>4222</v>
+        <v>4214</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>4223</v>
+        <v>4215</v>
       </c>
       <c r="B191" t="s">
-        <v>4224</v>
+        <v>4216</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>4225</v>
+        <v>4217</v>
       </c>
       <c r="B192" t="s">
-        <v>4226</v>
+        <v>4218</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>4227</v>
+        <v>4219</v>
       </c>
       <c r="B193" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>4228</v>
+        <v>4220</v>
       </c>
       <c r="B194" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>4229</v>
+        <v>4221</v>
       </c>
       <c r="B195" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>4230</v>
+        <v>4222</v>
       </c>
       <c r="B196" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>4231</v>
+        <v>4223</v>
       </c>
       <c r="B197" t="s">
-        <v>4232</v>
+        <v>4224</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>4233</v>
+        <v>4225</v>
       </c>
       <c r="B198" t="s">
-        <v>4234</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>4235</v>
+        <v>4227</v>
       </c>
       <c r="B199" t="s">
-        <v>4236</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>4237</v>
+        <v>4229</v>
       </c>
       <c r="B200" t="s">
-        <v>4238</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>4239</v>
+        <v>4231</v>
       </c>
       <c r="B201" t="s">
-        <v>4240</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>4241</v>
+        <v>4233</v>
       </c>
       <c r="B202" t="s">
-        <v>4242</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>4243</v>
+        <v>4235</v>
       </c>
       <c r="B203" t="s">
-        <v>4244</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>4245</v>
+        <v>4237</v>
       </c>
       <c r="B204" t="s">
-        <v>4246</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>4247</v>
+        <v>4239</v>
       </c>
       <c r="B205" t="s">
-        <v>4248</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>4249</v>
+        <v>4241</v>
       </c>
       <c r="B206" t="s">
-        <v>4250</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>4251</v>
+        <v>4243</v>
       </c>
       <c r="B207" t="s">
-        <v>4252</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>4253</v>
+        <v>4245</v>
       </c>
       <c r="B208" t="s">
-        <v>4254</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>4255</v>
+        <v>4247</v>
       </c>
       <c r="B209" t="s">
-        <v>4256</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>4257</v>
+        <v>4249</v>
       </c>
       <c r="B210" t="s">
-        <v>4258</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>4259</v>
+        <v>4251</v>
       </c>
       <c r="B211" t="s">
-        <v>4260</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>4261</v>
+        <v>4253</v>
       </c>
       <c r="B212" t="s">
-        <v>4262</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>4263</v>
+        <v>4255</v>
       </c>
       <c r="B213" t="s">
-        <v>4264</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>4265</v>
+        <v>4257</v>
       </c>
       <c r="B214" t="s">
-        <v>4266</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>4267</v>
+        <v>4259</v>
       </c>
       <c r="B215" t="s">
-        <v>3872</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>4268</v>
+        <v>4260</v>
       </c>
       <c r="B216" t="s">
-        <v>4269</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>4270</v>
+        <v>4262</v>
       </c>
       <c r="B217" t="s">
-        <v>4271</v>
+        <v>4263</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>4272</v>
+        <v>4264</v>
       </c>
       <c r="B218" t="s">
-        <v>4273</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>4274</v>
+        <v>4266</v>
       </c>
       <c r="B219" t="s">
-        <v>4275</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>4276</v>
+        <v>4268</v>
       </c>
       <c r="B220" t="s">
-        <v>4277</v>
+        <v>4269</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>4278</v>
+        <v>4270</v>
       </c>
       <c r="B221" t="s">
-        <v>4279</v>
+        <v>4271</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>4280</v>
+        <v>4272</v>
       </c>
       <c r="B222" t="s">
-        <v>4281</v>
+        <v>4273</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>4282</v>
+        <v>4274</v>
       </c>
       <c r="B223" t="s">
-        <v>4283</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>4284</v>
+        <v>4276</v>
       </c>
       <c r="B224" t="s">
-        <v>4285</v>
+        <v>4277</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>4286</v>
+        <v>4278</v>
       </c>
       <c r="B225" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>4287</v>
+        <v>4279</v>
       </c>
       <c r="B226" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>4288</v>
+        <v>4280</v>
       </c>
       <c r="B227" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>4289</v>
+        <v>4281</v>
       </c>
       <c r="B228" t="s">
-        <v>4290</v>
+        <v>4282</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>4291</v>
+        <v>4283</v>
       </c>
       <c r="B229" t="s">
-        <v>4292</v>
+        <v>4284</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>4293</v>
+        <v>4285</v>
       </c>
       <c r="B230" t="s">
-        <v>4294</v>
+        <v>4286</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>4295</v>
+        <v>4287</v>
       </c>
       <c r="B231" t="s">
-        <v>4296</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>4297</v>
+        <v>4289</v>
       </c>
       <c r="B232" t="s">
-        <v>4298</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>4299</v>
+        <v>4291</v>
       </c>
       <c r="B233" t="s">
-        <v>4300</v>
+        <v>4292</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>4301</v>
+        <v>4293</v>
       </c>
       <c r="B234" t="s">
-        <v>4302</v>
+        <v>4294</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>4303</v>
+        <v>4295</v>
       </c>
       <c r="B235" t="s">
-        <v>4304</v>
+        <v>4296</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>4305</v>
+        <v>4297</v>
       </c>
       <c r="B236" t="s">
-        <v>4306</v>
+        <v>4298</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>4307</v>
+        <v>4299</v>
       </c>
       <c r="B237" t="s">
-        <v>4308</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>4309</v>
+        <v>4301</v>
       </c>
       <c r="B238" t="s">
-        <v>4310</v>
+        <v>4302</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>4311</v>
+        <v>4303</v>
       </c>
       <c r="B239" t="s">
-        <v>4312</v>
+        <v>4304</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>4313</v>
+        <v>4305</v>
       </c>
       <c r="B240" t="s">
-        <v>4314</v>
+        <v>4306</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>4315</v>
+        <v>4307</v>
       </c>
       <c r="B241" t="s">
-        <v>4316</v>
+        <v>4308</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>4317</v>
+        <v>4309</v>
       </c>
       <c r="B242" t="s">
-        <v>4318</v>
+        <v>4310</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>4319</v>
+        <v>4311</v>
       </c>
       <c r="B243" t="s">
-        <v>4320</v>
+        <v>4312</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>4321</v>
+        <v>4313</v>
       </c>
       <c r="B244" t="s">
-        <v>3872</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>4322</v>
+        <v>4314</v>
       </c>
       <c r="B245" t="s">
-        <v>4323</v>
+        <v>4315</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>4324</v>
+        <v>4316</v>
       </c>
       <c r="B246" t="s">
-        <v>4325</v>
+        <v>4317</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>4326</v>
+        <v>4318</v>
       </c>
       <c r="B247" t="s">
-        <v>4327</v>
+        <v>4319</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>4328</v>
+        <v>4320</v>
       </c>
       <c r="B248" t="s">
-        <v>4329</v>
+        <v>4321</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>4330</v>
+        <v>4322</v>
       </c>
       <c r="B249" t="s">
-        <v>4331</v>
+        <v>4323</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>4332</v>
+        <v>4324</v>
       </c>
       <c r="B250" t="s">
-        <v>4333</v>
+        <v>4325</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>4334</v>
+        <v>4326</v>
       </c>
       <c r="B251" t="s">
-        <v>4335</v>
+        <v>4327</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>4336</v>
+        <v>4328</v>
       </c>
       <c r="B252" t="s">
-        <v>4337</v>
+        <v>4329</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>4338</v>
+        <v>4330</v>
       </c>
       <c r="B253" t="s">
-        <v>4339</v>
+        <v>4331</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>4340</v>
+        <v>4332</v>
       </c>
       <c r="B254" t="s">
-        <v>4341</v>
+        <v>4333</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>4342</v>
+        <v>4334</v>
       </c>
       <c r="B255" t="s">
-        <v>4343</v>
+        <v>4335</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>4344</v>
+        <v>4336</v>
       </c>
       <c r="B256" t="s">
-        <v>4345</v>
+        <v>4337</v>
       </c>
     </row>
   </sheetData>
@@ -44348,7 +44969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
